--- a/research/traditional_assets/database/data/malaysia/malaysia_recreation.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_recreation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="klse_owg" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.343</v>
+        <v>-0.0472</v>
       </c>
       <c r="G2">
-        <v>-0.8579136690647482</v>
+        <v>0.1587939698492462</v>
       </c>
       <c r="H2">
-        <v>-0.8579136690647482</v>
+        <v>0.1587939698492462</v>
       </c>
       <c r="I2">
-        <v>-2.073741007194245</v>
+        <v>0.06834170854271358</v>
       </c>
       <c r="J2">
-        <v>-2.073741007194245</v>
+        <v>0.06834170854271358</v>
       </c>
       <c r="K2">
-        <v>-9.724</v>
+        <v>-0.826</v>
       </c>
       <c r="L2">
-        <v>-1.748920863309353</v>
+        <v>-0.04150753768844221</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.864</v>
+        <v>2.03</v>
       </c>
       <c r="V2">
-        <v>0.02721167883211679</v>
+        <v>0.03555166374781085</v>
       </c>
       <c r="W2">
-        <v>-0.06504560311284047</v>
+        <v>-0.01799564270152505</v>
       </c>
       <c r="X2">
-        <v>0.09421981671705917</v>
+        <v>0.1509200439387884</v>
       </c>
       <c r="Y2">
-        <v>-0.1592654198298996</v>
+        <v>-0.1689156866403134</v>
       </c>
       <c r="Z2">
-        <v>0.05222618823971446</v>
+        <v>0.2404833836858006</v>
       </c>
       <c r="AA2">
-        <v>-0.1241465578947427</v>
+        <v>0.01643504531722054</v>
       </c>
       <c r="AB2">
-        <v>0.06904260459358995</v>
+        <v>0.1160879771440165</v>
       </c>
       <c r="AC2">
-        <v>-0.1931891624883326</v>
+        <v>-0.09965293182679597</v>
       </c>
       <c r="AD2">
-        <v>48.40000000000001</v>
+        <v>31.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>48.40000000000001</v>
+        <v>31.5</v>
       </c>
       <c r="AG2">
-        <v>46.53600000000001</v>
+        <v>29.47</v>
       </c>
       <c r="AH2">
-        <v>0.4140290846877673</v>
+        <v>0.3555304740406321</v>
       </c>
       <c r="AI2">
-        <v>0.4444444444444445</v>
+        <v>0.4222520107238606</v>
       </c>
       <c r="AJ2">
-        <v>0.4045342327619181</v>
+        <v>0.3404181587154904</v>
       </c>
       <c r="AK2">
-        <v>0.4347696102245974</v>
+        <v>0.4060906710762023</v>
       </c>
       <c r="AL2">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="AM2">
-        <v>2.441</v>
+        <v>1.962</v>
       </c>
       <c r="AN2">
-        <v>-8.736462093862817</v>
+        <v>5.545774647887324</v>
       </c>
       <c r="AO2">
-        <v>-4.350943396226415</v>
+        <v>0.6415094339622641</v>
       </c>
       <c r="AP2">
-        <v>-8.400000000000002</v>
+        <v>5.188380281690141</v>
       </c>
       <c r="AQ2">
-        <v>-4.723473986071283</v>
+        <v>0.6931702344546381</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.343</v>
+        <v>-0.0472</v>
       </c>
       <c r="G3">
-        <v>-1.19672131147541</v>
+        <v>0.1587939698492462</v>
       </c>
       <c r="H3">
-        <v>-1.19672131147541</v>
+        <v>0.1587939698492462</v>
       </c>
       <c r="I3">
-        <v>-3.016393442622951</v>
+        <v>0.06834170854271358</v>
       </c>
       <c r="J3">
-        <v>-3.016393442622951</v>
+        <v>0.06834170854271358</v>
       </c>
       <c r="K3">
-        <v>-10.7</v>
+        <v>-0.826</v>
       </c>
       <c r="L3">
-        <v>-3.508196721311475</v>
+        <v>-0.04150753768844221</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,198 +760,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.25</v>
+        <v>2.03</v>
       </c>
       <c r="V3">
-        <v>0.02688172043010753</v>
+        <v>0.03555166374781085</v>
       </c>
       <c r="W3">
-        <v>-0.2081712062256809</v>
+        <v>-0.01799564270152505</v>
       </c>
       <c r="X3">
-        <v>0.1013093613556351</v>
+        <v>0.1509200439387884</v>
       </c>
       <c r="Y3">
-        <v>-0.309480567581316</v>
+        <v>-0.1689156866403134</v>
       </c>
       <c r="Z3">
-        <v>0.0336718922499448</v>
+        <v>0.2404833836858006</v>
       </c>
       <c r="AA3">
-        <v>-0.1015676749834401</v>
+        <v>0.01643504531722054</v>
       </c>
       <c r="AB3">
-        <v>0.06874974447758797</v>
+        <v>0.1160879771440165</v>
       </c>
       <c r="AC3">
-        <v>-0.170317419461028</v>
+        <v>-0.09965293182679597</v>
       </c>
       <c r="AD3">
-        <v>38.1</v>
+        <v>31.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>38.1</v>
+        <v>31.5</v>
       </c>
       <c r="AG3">
-        <v>36.85</v>
+        <v>29.47</v>
       </c>
       <c r="AH3">
-        <v>0.4503546099290781</v>
+        <v>0.3555304740406321</v>
       </c>
       <c r="AI3">
-        <v>0.4514218009478673</v>
+        <v>0.4222520107238606</v>
       </c>
       <c r="AJ3">
-        <v>0.4421115776844631</v>
+        <v>0.3404181587154904</v>
       </c>
       <c r="AK3">
-        <v>0.4431749849669272</v>
+        <v>0.4060906710762023</v>
       </c>
       <c r="AL3">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AM3">
-        <v>1.881</v>
+        <v>1.962</v>
       </c>
       <c r="AN3">
-        <v>-8.943661971830986</v>
+        <v>5.545774647887324</v>
       </c>
       <c r="AO3">
-        <v>-4.401913875598086</v>
+        <v>0.6415094339622641</v>
       </c>
       <c r="AP3">
-        <v>-8.650234741784038</v>
+        <v>5.188380281690141</v>
       </c>
       <c r="AQ3">
-        <v>-4.891015417331207</v>
+        <v>0.6931702344546381</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Only World Group Holdings Berhad (KLSE:OWG)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KLSE:OWG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.355530474040632</v>
+      </c>
+      <c r="F2">
+        <v>0.06</v>
+      </c>
+      <c r="G2">
+        <v>57.1</v>
+      </c>
+      <c r="H2">
+        <v>82.4485516841831</v>
+      </c>
+      <c r="I2">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="J2">
+        <v>85.7345516841831</v>
+      </c>
+      <c r="K2">
+        <v>31.5</v>
+      </c>
+      <c r="L2">
+        <v>5.316</v>
+      </c>
+      <c r="M2">
+        <v>0.116087977144017</v>
+      </c>
+      <c r="N2">
+        <v>0.116841117028339</v>
+      </c>
+      <c r="O2">
+        <v>0.0529479449541284</v>
+      </c>
+      <c r="P2">
+        <v>0.0418</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.150920043938788</v>
+      </c>
+      <c r="T2">
+        <v>0.121630975562063</v>
+      </c>
+      <c r="U2">
+        <v>1.40441582669767</v>
+      </c>
+      <c r="V2">
+        <v>1.0375409153753</v>
+      </c>
+      <c r="W2">
+        <v>4.651480949449348</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>57.1</v>
+      </c>
+      <c r="AB2">
+        <v>0.07983393650755573</v>
+      </c>
+      <c r="AC2">
+        <v>0.06966834862385321</v>
+      </c>
+      <c r="AD2">
+        <v>0.24</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>5.68</v>
+      </c>
+      <c r="AH2">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="AI2">
+        <v>4.595</v>
+      </c>
+      <c r="AJ2">
+        <v>31.5</v>
+      </c>
+      <c r="AK2">
+        <v>31.5</v>
+      </c>
+      <c r="AL2">
+        <v>2.12</v>
+      </c>
+      <c r="AM2">
+        <v>31.5</v>
+      </c>
+      <c r="AN2">
+        <v>2.03</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1177986982836231</v>
+      </c>
+      <c r="C2">
+        <v>86.72532190689975</v>
+      </c>
+      <c r="D2">
+        <v>84.69532190689975</v>
+      </c>
+      <c r="E2">
+        <v>-31.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2.03</v>
+      </c>
+      <c r="H2">
+        <v>57.1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>5.68</v>
+      </c>
+      <c r="K2">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L2">
+        <v>1.36</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.36</v>
+      </c>
+      <c r="O2">
+        <v>0.3264000000000001</v>
+      </c>
+      <c r="P2">
+        <v>1.0336</v>
+      </c>
+      <c r="Q2">
+        <v>5.3536</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1177986982836231</v>
+      </c>
+      <c r="T2">
+        <v>0.9895378048425111</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1175684214077424</v>
+      </c>
+      <c r="C3">
+        <v>86.08692588044485</v>
+      </c>
+      <c r="D3">
+        <v>84.94292588044485</v>
+      </c>
+      <c r="E3">
+        <v>-30.614</v>
+      </c>
+      <c r="F3">
+        <v>0.886</v>
+      </c>
+      <c r="G3">
+        <v>2.03</v>
+      </c>
+      <c r="H3">
+        <v>57.1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>5.68</v>
+      </c>
+      <c r="K3">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L3">
+        <v>1.36</v>
+      </c>
+      <c r="M3">
+        <v>0.0404902</v>
+      </c>
+      <c r="N3">
+        <v>1.3195098</v>
+      </c>
+      <c r="O3">
+        <v>0.3166823520000001</v>
+      </c>
+      <c r="P3">
+        <v>1.002827448</v>
+      </c>
+      <c r="Q3">
+        <v>5.322827448</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1184051529371135</v>
+      </c>
+      <c r="T3">
+        <v>0.9971342566776658</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>33.58837447085962</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Sim Leisure Group Ltd. (Catalist:URR)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1173381445318617</v>
+      </c>
+      <c r="C4">
+        <v>85.44998182283446</v>
+      </c>
+      <c r="D4">
+        <v>85.19198182283446</v>
+      </c>
+      <c r="E4">
+        <v>-29.728</v>
+      </c>
+      <c r="F4">
+        <v>1.772</v>
       </c>
       <c r="G4">
-        <v>-0.4462151394422312</v>
+        <v>2.03</v>
       </c>
       <c r="H4">
-        <v>-0.4462151394422312</v>
+        <v>57.1</v>
       </c>
       <c r="I4">
-        <v>-0.9282868525896415</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>-0.9282868525896415</v>
+        <v>5.68</v>
       </c>
       <c r="K4">
-        <v>0.976</v>
+        <v>4.319999999999999</v>
       </c>
       <c r="L4">
-        <v>0.3888446215139442</v>
+        <v>1.36</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.08098040000000001</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>1.2790196</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.306964704</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.9720548960000002</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>5.292054896</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.1190239842161854</v>
+      </c>
+      <c r="T4">
+        <v>1.004885738142109</v>
       </c>
       <c r="U4">
-        <v>0.614</v>
+        <v>0.0457</v>
       </c>
       <c r="V4">
-        <v>0.02790909090909091</v>
+        <v>0.24</v>
       </c>
       <c r="W4">
-        <v>0.07808</v>
-      </c>
-      <c r="X4">
-        <v>0.08713027207848321</v>
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y4">
-        <v>-0.009050272078483218</v>
+        <v>16.79418723542981</v>
       </c>
       <c r="Z4">
-        <v>0.1580604534005038</v>
-      </c>
-      <c r="AA4">
-        <v>-0.1467254408060454</v>
-      </c>
-      <c r="AB4">
-        <v>0.06933546470959193</v>
-      </c>
-      <c r="AC4">
-        <v>-0.2160609055156373</v>
-      </c>
-      <c r="AD4">
-        <v>10.3</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>10.3</v>
-      </c>
-      <c r="AG4">
-        <v>9.686</v>
-      </c>
-      <c r="AH4">
-        <v>0.3188854489164087</v>
-      </c>
-      <c r="AI4">
-        <v>0.4204081632653062</v>
-      </c>
-      <c r="AJ4">
-        <v>0.3056870542195291</v>
-      </c>
-      <c r="AK4">
-        <v>0.4055095034748388</v>
-      </c>
-      <c r="AL4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.117144347655981</v>
+      </c>
+      <c r="C5">
+        <v>84.77471738221196</v>
+      </c>
+      <c r="D5">
+        <v>85.40271738221196</v>
+      </c>
+      <c r="E5">
+        <v>-28.842</v>
+      </c>
+      <c r="F5">
+        <v>2.658</v>
+      </c>
+      <c r="G5">
+        <v>2.03</v>
+      </c>
+      <c r="H5">
+        <v>57.1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>5.68</v>
+      </c>
+      <c r="K5">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L5">
+        <v>1.36</v>
+      </c>
+      <c r="M5">
+        <v>0.1257234</v>
+      </c>
+      <c r="N5">
+        <v>1.2342766</v>
+      </c>
+      <c r="O5">
+        <v>0.2962263840000001</v>
+      </c>
+      <c r="P5">
+        <v>0.9380502160000002</v>
+      </c>
+      <c r="Q5">
+        <v>5.258050215999999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1196555749030732</v>
+      </c>
+      <c r="T5">
+        <v>1.012797043966644</v>
+      </c>
+      <c r="U5">
+        <v>0.0473</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.035948</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>10.81739755685895</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1170995107801003</v>
+      </c>
+      <c r="C6">
+        <v>83.93762178788437</v>
+      </c>
+      <c r="D6">
+        <v>85.45162178788436</v>
+      </c>
+      <c r="E6">
+        <v>-27.956</v>
+      </c>
+      <c r="F6">
+        <v>3.544</v>
+      </c>
+      <c r="G6">
+        <v>2.03</v>
+      </c>
+      <c r="H6">
+        <v>57.1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>5.68</v>
+      </c>
+      <c r="K6">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L6">
+        <v>1.36</v>
+      </c>
+      <c r="M6">
+        <v>0.187832</v>
+      </c>
+      <c r="N6">
+        <v>1.172168</v>
+      </c>
+      <c r="O6">
+        <v>0.2813203200000001</v>
+      </c>
+      <c r="P6">
+        <v>0.8908476800000003</v>
+      </c>
+      <c r="Q6">
+        <v>5.21084768</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1203003237292712</v>
+      </c>
+      <c r="T6">
+        <v>1.020873168662524</v>
+      </c>
+      <c r="U6">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.04028</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>7.240512798671154</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1170007139042196</v>
+      </c>
+      <c r="C7">
+        <v>83.15957928405152</v>
+      </c>
+      <c r="D7">
+        <v>85.55957928405151</v>
+      </c>
+      <c r="E7">
+        <v>-27.07</v>
+      </c>
+      <c r="F7">
+        <v>4.43</v>
+      </c>
+      <c r="G7">
+        <v>2.03</v>
+      </c>
+      <c r="H7">
+        <v>57.1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>5.68</v>
+      </c>
+      <c r="K7">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L7">
+        <v>1.36</v>
+      </c>
+      <c r="M7">
+        <v>0.24365</v>
+      </c>
+      <c r="N7">
+        <v>1.11635</v>
+      </c>
+      <c r="O7">
+        <v>0.2679240000000001</v>
+      </c>
+      <c r="P7">
+        <v>0.8484260000000003</v>
+      </c>
+      <c r="Q7">
+        <v>5.168426</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.120958646214968</v>
+      </c>
+      <c r="T7">
+        <v>1.029119317036212</v>
+      </c>
+      <c r="U7">
+        <v>0.055</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.0418</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>5.581777139339218</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1168411170283389</v>
+      </c>
+      <c r="C8">
+        <v>82.44855168418314</v>
+      </c>
+      <c r="D8">
+        <v>85.73455168418315</v>
+      </c>
+      <c r="E8">
+        <v>-26.184</v>
+      </c>
+      <c r="F8">
+        <v>5.316</v>
+      </c>
+      <c r="G8">
+        <v>2.03</v>
+      </c>
+      <c r="H8">
+        <v>57.1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>5.68</v>
+      </c>
+      <c r="K8">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L8">
+        <v>1.36</v>
+      </c>
+      <c r="M8">
+        <v>0.29238</v>
+      </c>
+      <c r="N8">
+        <v>1.06762</v>
+      </c>
+      <c r="O8">
+        <v>0.2562288</v>
+      </c>
+      <c r="P8">
+        <v>0.8113912000000002</v>
+      </c>
+      <c r="Q8">
+        <v>5.131391199999999</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1216309755620627</v>
+      </c>
+      <c r="T8">
+        <v>1.037540915375297</v>
+      </c>
+      <c r="U8">
+        <v>0.055</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.0418</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>4.651480949449348</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1174848401524582</v>
+      </c>
+      <c r="C9">
+        <v>80.86115465080064</v>
+      </c>
+      <c r="D9">
+        <v>85.03315465080064</v>
+      </c>
+      <c r="E9">
+        <v>-25.298</v>
+      </c>
+      <c r="F9">
+        <v>6.202</v>
+      </c>
+      <c r="G9">
+        <v>2.03</v>
+      </c>
+      <c r="H9">
+        <v>57.1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>5.68</v>
+      </c>
+      <c r="K9">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L9">
+        <v>1.36</v>
+      </c>
+      <c r="M9">
+        <v>0.4347602</v>
+      </c>
+      <c r="N9">
+        <v>0.9252398000000004</v>
+      </c>
+      <c r="O9">
+        <v>0.2220575520000001</v>
+      </c>
+      <c r="P9">
+        <v>0.7031822480000003</v>
+      </c>
+      <c r="Q9">
+        <v>5.023182247999999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1223177636047938</v>
+      </c>
+      <c r="T9">
+        <v>1.046143623356083</v>
+      </c>
+      <c r="U9">
+        <v>0.0701</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.053276</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>3.128161225429559</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1187350432765775</v>
+      </c>
+      <c r="C10">
+        <v>78.64521584998809</v>
+      </c>
+      <c r="D10">
+        <v>83.70321584998808</v>
+      </c>
+      <c r="E10">
+        <v>-24.412</v>
+      </c>
+      <c r="F10">
+        <v>7.088</v>
+      </c>
+      <c r="G10">
+        <v>2.03</v>
+      </c>
+      <c r="H10">
+        <v>57.1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>5.68</v>
+      </c>
+      <c r="K10">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L10">
+        <v>1.36</v>
+      </c>
+      <c r="M10">
+        <v>0.6478432000000001</v>
+      </c>
+      <c r="N10">
+        <v>0.7121568000000003</v>
+      </c>
+      <c r="O10">
+        <v>0.170917632</v>
+      </c>
+      <c r="P10">
+        <v>0.5412391680000002</v>
+      </c>
+      <c r="Q10">
+        <v>4.861239167999999</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1230194818223669</v>
+      </c>
+      <c r="T10">
+        <v>1.054933346727755</v>
+      </c>
+      <c r="U10">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>2.099273404428726</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1202953264006968</v>
+      </c>
+      <c r="C11">
+        <v>76.15666118957586</v>
+      </c>
+      <c r="D11">
+        <v>82.10066118957586</v>
+      </c>
+      <c r="E11">
+        <v>-23.526</v>
+      </c>
+      <c r="F11">
+        <v>7.973999999999999</v>
+      </c>
+      <c r="G11">
+        <v>2.03</v>
+      </c>
+      <c r="H11">
+        <v>57.1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>5.68</v>
+      </c>
+      <c r="K11">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L11">
+        <v>1.36</v>
+      </c>
+      <c r="M11">
+        <v>0.897075</v>
+      </c>
+      <c r="N11">
+        <v>0.4629250000000004</v>
+      </c>
+      <c r="O11">
+        <v>0.1111020000000001</v>
+      </c>
+      <c r="P11">
+        <v>0.3518230000000003</v>
+      </c>
+      <c r="Q11">
+        <v>4.671823</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1237366224183482</v>
+      </c>
+      <c r="T11">
+        <v>1.063916250832871</v>
+      </c>
+      <c r="U11">
+        <v>0.1125</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>1.516038235376084</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1302535043026355</v>
+      </c>
+      <c r="C12">
+        <v>66.33089451549527</v>
+      </c>
+      <c r="D12">
+        <v>73.16089451549527</v>
+      </c>
+      <c r="E12">
+        <v>-22.64</v>
+      </c>
+      <c r="F12">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="G12">
+        <v>2.03</v>
+      </c>
+      <c r="H12">
+        <v>57.1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>5.68</v>
+      </c>
+      <c r="K12">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L12">
+        <v>1.36</v>
+      </c>
+      <c r="M12">
+        <v>1.894268</v>
+      </c>
+      <c r="N12">
+        <v>-0.5342679999999995</v>
+      </c>
+      <c r="O12">
+        <v>-0.1282243199999999</v>
+      </c>
+      <c r="P12">
+        <v>-0.4060436799999996</v>
+      </c>
+      <c r="Q12">
+        <v>3.91395632</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1250638635717771</v>
+      </c>
+      <c r="T12">
+        <v>1.080541275371192</v>
+      </c>
+      <c r="U12">
+        <v>0.2138</v>
+      </c>
+      <c r="V12">
+        <v>0.1723093036465801</v>
+      </c>
+      <c r="W12">
+        <v>0.1769602708803611</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.7179554318607506</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1320035043026355</v>
+      </c>
+      <c r="C13">
+        <v>64.07121692300485</v>
+      </c>
+      <c r="D13">
+        <v>71.78721692300485</v>
+      </c>
+      <c r="E13">
+        <v>-21.754</v>
+      </c>
+      <c r="F13">
+        <v>9.745999999999999</v>
+      </c>
+      <c r="G13">
+        <v>2.03</v>
+      </c>
+      <c r="H13">
+        <v>57.1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>5.68</v>
+      </c>
+      <c r="K13">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L13">
+        <v>1.36</v>
+      </c>
+      <c r="M13">
+        <v>2.0836948</v>
+      </c>
+      <c r="N13">
+        <v>-0.7236947999999992</v>
+      </c>
+      <c r="O13">
+        <v>-0.1736867519999998</v>
+      </c>
+      <c r="P13">
+        <v>-0.5500080479999994</v>
+      </c>
+      <c r="Q13">
+        <v>3.769991952</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.126033120465842</v>
+      </c>
+      <c r="T13">
+        <v>1.09268218857761</v>
+      </c>
+      <c r="U13">
+        <v>0.2138</v>
+      </c>
+      <c r="V13">
+        <v>0.1566448214968911</v>
+      </c>
+      <c r="W13">
+        <v>0.1803093371639647</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.6526867562370462</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1337535043026355</v>
+      </c>
+      <c r="C14">
+        <v>61.86217328667036</v>
+      </c>
+      <c r="D14">
+        <v>70.46417328667036</v>
+      </c>
+      <c r="E14">
+        <v>-20.868</v>
+      </c>
+      <c r="F14">
+        <v>10.632</v>
+      </c>
+      <c r="G14">
+        <v>2.03</v>
+      </c>
+      <c r="H14">
+        <v>57.1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>5.68</v>
+      </c>
+      <c r="K14">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L14">
+        <v>1.36</v>
+      </c>
+      <c r="M14">
+        <v>2.2731216</v>
+      </c>
+      <c r="N14">
+        <v>-0.9131215999999993</v>
+      </c>
+      <c r="O14">
+        <v>-0.2191491839999998</v>
+      </c>
+      <c r="P14">
+        <v>-0.6939724159999995</v>
+      </c>
+      <c r="Q14">
+        <v>3.626027584</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1270244059256811</v>
+      </c>
+      <c r="T14">
+        <v>1.105099031629629</v>
+      </c>
+      <c r="U14">
+        <v>0.2138</v>
+      </c>
+      <c r="V14">
+        <v>0.1435910863721501</v>
+      </c>
+      <c r="W14">
+        <v>0.1831002257336343</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.5982961932172923</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1355035043026355</v>
+      </c>
+      <c r="C15">
+        <v>59.70101470642116</v>
+      </c>
+      <c r="D15">
+        <v>69.18901470642116</v>
+      </c>
+      <c r="E15">
+        <v>-19.982</v>
+      </c>
+      <c r="F15">
+        <v>11.518</v>
+      </c>
+      <c r="G15">
+        <v>2.03</v>
+      </c>
+      <c r="H15">
+        <v>57.1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>5.68</v>
+      </c>
+      <c r="K15">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L15">
+        <v>1.36</v>
+      </c>
+      <c r="M15">
+        <v>2.4625484</v>
+      </c>
+      <c r="N15">
+        <v>-1.102548399999999</v>
+      </c>
+      <c r="O15">
+        <v>-0.2646116159999998</v>
+      </c>
+      <c r="P15">
+        <v>-0.8379367839999996</v>
+      </c>
+      <c r="Q15">
+        <v>3.482063216</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1280384795570108</v>
+      </c>
+      <c r="T15">
+        <v>1.117801319349509</v>
+      </c>
+      <c r="U15">
+        <v>0.2138</v>
+      </c>
+      <c r="V15">
+        <v>0.1325456181896771</v>
+      </c>
+      <c r="W15">
+        <v>0.185461746831047</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.5522734091236543</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1372535043026355</v>
+      </c>
+      <c r="C16">
+        <v>57.58518772774858</v>
+      </c>
+      <c r="D16">
+        <v>67.95918772774857</v>
+      </c>
+      <c r="E16">
+        <v>-19.096</v>
+      </c>
+      <c r="F16">
+        <v>12.404</v>
+      </c>
+      <c r="G16">
+        <v>2.03</v>
+      </c>
+      <c r="H16">
+        <v>57.1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>5.68</v>
+      </c>
+      <c r="K16">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L16">
+        <v>1.36</v>
+      </c>
+      <c r="M16">
+        <v>2.6519752</v>
+      </c>
+      <c r="N16">
+        <v>-1.2919752</v>
+      </c>
+      <c r="O16">
+        <v>-0.3100740479999999</v>
+      </c>
+      <c r="P16">
+        <v>-0.9819011519999996</v>
+      </c>
+      <c r="Q16">
+        <v>3.338098848</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1290761362960458</v>
+      </c>
+      <c r="T16">
+        <v>1.130799009109388</v>
+      </c>
+      <c r="U16">
+        <v>0.2138</v>
+      </c>
+      <c r="V16">
+        <v>0.1230780740332715</v>
+      </c>
+      <c r="W16">
+        <v>0.1874859077716865</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.5128253084719647</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1428960106959588</v>
+      </c>
+      <c r="C17">
+        <v>53.01547162109701</v>
+      </c>
+      <c r="D17">
+        <v>64.27547162109701</v>
+      </c>
+      <c r="E17">
+        <v>-18.21</v>
+      </c>
+      <c r="F17">
+        <v>13.29</v>
+      </c>
+      <c r="G17">
+        <v>2.03</v>
+      </c>
+      <c r="H17">
+        <v>57.1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>5.68</v>
+      </c>
+      <c r="K17">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L17">
+        <v>1.36</v>
+      </c>
+      <c r="M17">
+        <v>3.173652</v>
+      </c>
+      <c r="N17">
+        <v>-1.813652</v>
+      </c>
+      <c r="O17">
+        <v>-0.43527648</v>
+      </c>
+      <c r="P17">
+        <v>-1.37837552</v>
+      </c>
+      <c r="Q17">
+        <v>2.94162448</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1303058630681443</v>
+      </c>
+      <c r="T17">
+        <v>1.146202568371207</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.1028468149626992</v>
+      </c>
+      <c r="W17">
+        <v>0.2142401805869075</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.4285283956779131</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1448960106959588</v>
+      </c>
+      <c r="C18">
+        <v>50.91782433672752</v>
+      </c>
+      <c r="D18">
+        <v>63.06382433672753</v>
+      </c>
+      <c r="E18">
+        <v>-17.324</v>
+      </c>
+      <c r="F18">
+        <v>14.176</v>
+      </c>
+      <c r="G18">
+        <v>2.03</v>
+      </c>
+      <c r="H18">
+        <v>57.1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>5.68</v>
+      </c>
+      <c r="K18">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L18">
+        <v>1.36</v>
+      </c>
+      <c r="M18">
+        <v>3.3852288</v>
+      </c>
+      <c r="N18">
+        <v>-2.0252288</v>
+      </c>
+      <c r="O18">
+        <v>-0.486054912</v>
+      </c>
+      <c r="P18">
+        <v>-1.539173888</v>
+      </c>
+      <c r="Q18">
+        <v>2.780826112</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1313952185808603</v>
+      </c>
+      <c r="T18">
+        <v>1.159847837042293</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.09641888902753044</v>
+      </c>
+      <c r="W18">
+        <v>0.2157751693002257</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.4017453709480435</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1468960106959587</v>
+      </c>
+      <c r="C19">
+        <v>48.86501301907205</v>
+      </c>
+      <c r="D19">
+        <v>61.89701301907205</v>
+      </c>
+      <c r="E19">
+        <v>-16.438</v>
+      </c>
+      <c r="F19">
+        <v>15.062</v>
+      </c>
+      <c r="G19">
+        <v>2.03</v>
+      </c>
+      <c r="H19">
+        <v>57.1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>5.68</v>
+      </c>
+      <c r="K19">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L19">
+        <v>1.36</v>
+      </c>
+      <c r="M19">
+        <v>3.5968056</v>
+      </c>
+      <c r="N19">
+        <v>-2.2368056</v>
+      </c>
+      <c r="O19">
+        <v>-0.5368333439999999</v>
+      </c>
+      <c r="P19">
+        <v>-1.699972256</v>
+      </c>
+      <c r="Q19">
+        <v>2.620027744</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1325108236240032</v>
+      </c>
+      <c r="T19">
+        <v>1.173821907368104</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.09074718967296982</v>
+      </c>
+      <c r="W19">
+        <v>0.2171295711060948</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.3781132903040409</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1488960106959588</v>
+      </c>
+      <c r="C20">
+        <v>46.85459420266265</v>
+      </c>
+      <c r="D20">
+        <v>60.77259420266265</v>
+      </c>
+      <c r="E20">
+        <v>-15.552</v>
+      </c>
+      <c r="F20">
+        <v>15.948</v>
+      </c>
+      <c r="G20">
+        <v>2.03</v>
+      </c>
+      <c r="H20">
+        <v>57.1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>5.68</v>
+      </c>
+      <c r="K20">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L20">
+        <v>1.36</v>
+      </c>
+      <c r="M20">
+        <v>3.8083824</v>
+      </c>
+      <c r="N20">
+        <v>-2.448382399999999</v>
+      </c>
+      <c r="O20">
+        <v>-0.5876117759999998</v>
+      </c>
+      <c r="P20">
+        <v>-1.860770624</v>
+      </c>
+      <c r="Q20">
+        <v>2.459229376</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1336536385462471</v>
+      </c>
+      <c r="T20">
+        <v>1.188136808677471</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.08570567913558262</v>
+      </c>
+      <c r="W20">
+        <v>0.2183334838224229</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.3571069963982609</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1508960106959588</v>
+      </c>
+      <c r="C21">
+        <v>44.88429880579081</v>
+      </c>
+      <c r="D21">
+        <v>59.6882988057908</v>
+      </c>
+      <c r="E21">
+        <v>-14.666</v>
+      </c>
+      <c r="F21">
+        <v>16.834</v>
+      </c>
+      <c r="G21">
+        <v>2.03</v>
+      </c>
+      <c r="H21">
+        <v>57.1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>5.68</v>
+      </c>
+      <c r="K21">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L21">
+        <v>1.36</v>
+      </c>
+      <c r="M21">
+        <v>4.0199592</v>
+      </c>
+      <c r="N21">
+        <v>-2.659959199999999</v>
+      </c>
+      <c r="O21">
+        <v>-0.6383902079999998</v>
+      </c>
+      <c r="P21">
+        <v>-2.021568992</v>
+      </c>
+      <c r="Q21">
+        <v>2.298431008</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1348246711208921</v>
+      </c>
+      <c r="T21">
+        <v>1.202805164340156</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.08119485391792038</v>
+      </c>
+      <c r="W21">
+        <v>0.2194106688844006</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.3383118913246683</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1528960106959588</v>
+      </c>
+      <c r="C22">
+        <v>42.95201684655829</v>
+      </c>
+      <c r="D22">
+        <v>58.64201684655829</v>
+      </c>
+      <c r="E22">
+        <v>-13.78</v>
+      </c>
+      <c r="F22">
+        <v>17.72</v>
+      </c>
+      <c r="G22">
+        <v>2.03</v>
+      </c>
+      <c r="H22">
+        <v>57.1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>5.68</v>
+      </c>
+      <c r="K22">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L22">
+        <v>1.36</v>
+      </c>
+      <c r="M22">
+        <v>4.231536</v>
+      </c>
+      <c r="N22">
+        <v>-2.871536</v>
+      </c>
+      <c r="O22">
+        <v>-0.6891686399999999</v>
+      </c>
+      <c r="P22">
+        <v>-2.18236736</v>
+      </c>
+      <c r="Q22">
+        <v>2.13763264</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1360249795099033</v>
+      </c>
+      <c r="T22">
+        <v>1.217840228894407</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.07713511122202436</v>
+      </c>
+      <c r="W22">
+        <v>0.2203801354401806</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.3213962967584348</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1548960106959587</v>
+      </c>
+      <c r="C23">
+        <v>41.05578373871906</v>
+      </c>
+      <c r="D23">
+        <v>57.63178373871905</v>
+      </c>
+      <c r="E23">
+        <v>-12.894</v>
+      </c>
+      <c r="F23">
+        <v>18.606</v>
+      </c>
+      <c r="G23">
+        <v>2.03</v>
+      </c>
+      <c r="H23">
+        <v>57.1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>5.68</v>
+      </c>
+      <c r="K23">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L23">
+        <v>1.36</v>
+      </c>
+      <c r="M23">
+        <v>4.4431128</v>
+      </c>
+      <c r="N23">
+        <v>-3.083112799999999</v>
+      </c>
+      <c r="O23">
+        <v>-0.7399470719999999</v>
+      </c>
+      <c r="P23">
+        <v>-2.343165728</v>
+      </c>
+      <c r="Q23">
+        <v>1.976834272</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1372556754530666</v>
+      </c>
+      <c r="T23">
+        <v>1.233255927994337</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.07346201068764224</v>
+      </c>
+      <c r="W23">
+        <v>0.221257271847791</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.3060917111985094</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1568960106959587</v>
+      </c>
+      <c r="C24">
+        <v>39.1937679800311</v>
+      </c>
+      <c r="D24">
+        <v>56.65576798003109</v>
+      </c>
+      <c r="E24">
+        <v>-12.008</v>
+      </c>
+      <c r="F24">
+        <v>19.492</v>
+      </c>
+      <c r="G24">
+        <v>2.03</v>
+      </c>
+      <c r="H24">
+        <v>57.1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>5.68</v>
+      </c>
+      <c r="K24">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L24">
+        <v>1.36</v>
+      </c>
+      <c r="M24">
+        <v>4.654689599999999</v>
+      </c>
+      <c r="N24">
+        <v>-3.294689599999999</v>
+      </c>
+      <c r="O24">
+        <v>-0.7907255039999997</v>
+      </c>
+      <c r="P24">
+        <v>-2.503964095999999</v>
+      </c>
+      <c r="Q24">
+        <v>1.816035904</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1385179277024649</v>
+      </c>
+      <c r="T24">
+        <v>1.249066901430162</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.07012282838365852</v>
+      </c>
+      <c r="W24">
+        <v>0.2220546685819823</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.2921784515985771</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1588960106959587</v>
+      </c>
+      <c r="C25">
+        <v>37.36426007078899</v>
+      </c>
+      <c r="D25">
+        <v>55.71226007078899</v>
+      </c>
+      <c r="E25">
+        <v>-11.122</v>
+      </c>
+      <c r="F25">
+        <v>20.378</v>
+      </c>
+      <c r="G25">
+        <v>2.03</v>
+      </c>
+      <c r="H25">
+        <v>57.1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>5.68</v>
+      </c>
+      <c r="K25">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L25">
+        <v>1.36</v>
+      </c>
+      <c r="M25">
+        <v>4.866266400000001</v>
+      </c>
+      <c r="N25">
+        <v>-3.5062664</v>
+      </c>
+      <c r="O25">
+        <v>-0.8415039360000001</v>
+      </c>
+      <c r="P25">
+        <v>-2.664762464</v>
+      </c>
+      <c r="Q25">
+        <v>1.655237535999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1398129657245748</v>
+      </c>
+      <c r="T25">
+        <v>1.265288549500683</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.06707400975828204</v>
+      </c>
+      <c r="W25">
+        <v>0.2227827264697222</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.2794750406595086</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1608960106959587</v>
+      </c>
+      <c r="C26">
+        <v>35.56566252147967</v>
+      </c>
+      <c r="D26">
+        <v>54.79966252147966</v>
+      </c>
+      <c r="E26">
+        <v>-10.236</v>
+      </c>
+      <c r="F26">
+        <v>21.264</v>
+      </c>
+      <c r="G26">
+        <v>2.03</v>
+      </c>
+      <c r="H26">
+        <v>57.1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>5.68</v>
+      </c>
+      <c r="K26">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L26">
+        <v>1.36</v>
+      </c>
+      <c r="M26">
+        <v>5.0778432</v>
+      </c>
+      <c r="N26">
+        <v>-3.7178432</v>
+      </c>
+      <c r="O26">
+        <v>-0.8922823679999999</v>
+      </c>
+      <c r="P26">
+        <v>-2.825560832</v>
+      </c>
+      <c r="Q26">
+        <v>1.494439168</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.141142083694635</v>
+      </c>
+      <c r="T26">
+        <v>1.281937083046745</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.06427925935168696</v>
+      </c>
+      <c r="W26">
+        <v>0.2234501128668172</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.2678302472986956</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1628960106959587</v>
+      </c>
+      <c r="C27">
+        <v>33.79648082669107</v>
+      </c>
+      <c r="D27">
+        <v>53.91648082669107</v>
+      </c>
+      <c r="E27">
+        <v>-9.350000000000001</v>
+      </c>
+      <c r="F27">
+        <v>22.15</v>
+      </c>
+      <c r="G27">
+        <v>2.03</v>
+      </c>
+      <c r="H27">
+        <v>57.1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>5.68</v>
+      </c>
+      <c r="K27">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L27">
+        <v>1.36</v>
+      </c>
+      <c r="M27">
+        <v>5.28942</v>
+      </c>
+      <c r="N27">
+        <v>-3.929419999999999</v>
+      </c>
+      <c r="O27">
+        <v>-0.9430607999999998</v>
+      </c>
+      <c r="P27">
+        <v>-2.9863592</v>
+      </c>
+      <c r="Q27">
+        <v>1.3336408</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1425066448105635</v>
+      </c>
+      <c r="T27">
+        <v>1.299029577487368</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.06170808897761949</v>
+      </c>
+      <c r="W27">
+        <v>0.2240641083521445</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.2571170374067479</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1648960106959587</v>
+      </c>
+      <c r="C28">
+        <v>32.05531529799414</v>
+      </c>
+      <c r="D28">
+        <v>53.06131529799414</v>
+      </c>
+      <c r="E28">
+        <v>-8.464000000000002</v>
+      </c>
+      <c r="F28">
+        <v>23.036</v>
+      </c>
+      <c r="G28">
+        <v>2.03</v>
+      </c>
+      <c r="H28">
+        <v>57.1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>5.68</v>
+      </c>
+      <c r="K28">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L28">
+        <v>1.36</v>
+      </c>
+      <c r="M28">
+        <v>5.500996799999999</v>
+      </c>
+      <c r="N28">
+        <v>-4.140996799999999</v>
+      </c>
+      <c r="O28">
+        <v>-0.9938392319999997</v>
+      </c>
+      <c r="P28">
+        <v>-3.147157567999999</v>
+      </c>
+      <c r="Q28">
+        <v>1.172842432</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1439080859566522</v>
+      </c>
+      <c r="T28">
+        <v>1.316584031237197</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.05933470094001875</v>
+      </c>
+      <c r="W28">
+        <v>0.2246308734155235</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.2472279205834115</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1668960106959587</v>
+      </c>
+      <c r="C29">
+        <v>30.34085366191811</v>
+      </c>
+      <c r="D29">
+        <v>52.23285366191811</v>
+      </c>
+      <c r="E29">
+        <v>-7.577999999999999</v>
+      </c>
+      <c r="F29">
+        <v>23.922</v>
+      </c>
+      <c r="G29">
+        <v>2.03</v>
+      </c>
+      <c r="H29">
+        <v>57.1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>5.68</v>
+      </c>
+      <c r="K29">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L29">
+        <v>1.36</v>
+      </c>
+      <c r="M29">
+        <v>5.712573600000001</v>
+      </c>
+      <c r="N29">
+        <v>-4.3525736</v>
+      </c>
+      <c r="O29">
+        <v>-1.044617664</v>
+      </c>
+      <c r="P29">
+        <v>-3.307955936</v>
+      </c>
+      <c r="Q29">
+        <v>1.012044063999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1453479227505789</v>
+      </c>
+      <c r="T29">
+        <v>1.334619428925378</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.05713711942372174</v>
+      </c>
+      <c r="W29">
+        <v>0.2251556558816152</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.2380713309321739</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1688960106959587</v>
+      </c>
+      <c r="C30">
+        <v>28.65186434068534</v>
+      </c>
+      <c r="D30">
+        <v>51.42986434068534</v>
+      </c>
+      <c r="E30">
+        <v>-6.692</v>
+      </c>
+      <c r="F30">
+        <v>24.808</v>
+      </c>
+      <c r="G30">
+        <v>2.03</v>
+      </c>
+      <c r="H30">
+        <v>57.1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>5.68</v>
+      </c>
+      <c r="K30">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L30">
+        <v>1.36</v>
+      </c>
+      <c r="M30">
+        <v>5.9241504</v>
+      </c>
+      <c r="N30">
+        <v>-4.5641504</v>
+      </c>
+      <c r="O30">
+        <v>-1.095396096</v>
+      </c>
+      <c r="P30">
+        <v>-3.468754304</v>
+      </c>
+      <c r="Q30">
+        <v>0.8512456959999994</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1468277550110036</v>
+      </c>
+      <c r="T30">
+        <v>1.353155809882675</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.05509650801573168</v>
+      </c>
+      <c r="W30">
+        <v>0.2256429538858433</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.229568783398882</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1708960106959587</v>
+      </c>
+      <c r="C31">
+        <v>26.98719034334474</v>
+      </c>
+      <c r="D31">
+        <v>50.65119034334473</v>
+      </c>
+      <c r="E31">
+        <v>-5.806000000000004</v>
+      </c>
+      <c r="F31">
+        <v>25.694</v>
+      </c>
+      <c r="G31">
+        <v>2.03</v>
+      </c>
+      <c r="H31">
+        <v>57.1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>5.68</v>
+      </c>
+      <c r="K31">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L31">
+        <v>1.36</v>
+      </c>
+      <c r="M31">
+        <v>6.135727199999999</v>
+      </c>
+      <c r="N31">
+        <v>-4.775727199999999</v>
+      </c>
+      <c r="O31">
+        <v>-1.146174528</v>
+      </c>
+      <c r="P31">
+        <v>-3.629552671999999</v>
+      </c>
+      <c r="Q31">
+        <v>0.6904473280000003</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.148349272687215</v>
+      </c>
+      <c r="T31">
+        <v>1.372214342416234</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.05319662842898232</v>
+      </c>
+      <c r="W31">
+        <v>0.226096645131159</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.221652618454093</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1728960106959587</v>
+      </c>
+      <c r="C32">
+        <v>25.34574370357574</v>
+      </c>
+      <c r="D32">
+        <v>49.89574370357574</v>
+      </c>
+      <c r="E32">
+        <v>-4.920000000000002</v>
+      </c>
+      <c r="F32">
+        <v>26.58</v>
+      </c>
+      <c r="G32">
+        <v>2.03</v>
+      </c>
+      <c r="H32">
+        <v>57.1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>5.68</v>
+      </c>
+      <c r="K32">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L32">
+        <v>1.36</v>
+      </c>
+      <c r="M32">
+        <v>6.347304</v>
+      </c>
+      <c r="N32">
+        <v>-4.987304</v>
+      </c>
+      <c r="O32">
+        <v>-1.19695296</v>
+      </c>
+      <c r="P32">
+        <v>-3.79035104</v>
+      </c>
+      <c r="Q32">
+        <v>0.5296489599999994</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1499142622970323</v>
+      </c>
+      <c r="T32">
+        <v>1.391817404450752</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.05142340748134958</v>
+      </c>
+      <c r="W32">
+        <v>0.2265200902934537</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.2142641978389566</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1748960106959587</v>
+      </c>
+      <c r="C33">
+        <v>23.72650040792847</v>
+      </c>
+      <c r="D33">
+        <v>49.16250040792846</v>
+      </c>
+      <c r="E33">
+        <v>-4.034000000000002</v>
+      </c>
+      <c r="F33">
+        <v>27.466</v>
+      </c>
+      <c r="G33">
+        <v>2.03</v>
+      </c>
+      <c r="H33">
+        <v>57.1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>5.68</v>
+      </c>
+      <c r="K33">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L33">
+        <v>1.36</v>
+      </c>
+      <c r="M33">
+        <v>6.5588808</v>
+      </c>
+      <c r="N33">
+        <v>-5.1988808</v>
+      </c>
+      <c r="O33">
+        <v>-1.247731392</v>
+      </c>
+      <c r="P33">
+        <v>-3.951149408</v>
+      </c>
+      <c r="Q33">
+        <v>0.3688505919999998</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1515246139245255</v>
+      </c>
+      <c r="T33">
+        <v>1.411988671181922</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.04976458788517701</v>
+      </c>
+      <c r="W33">
+        <v>0.2269162164130197</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2073524495215708</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1768960106959588</v>
+      </c>
+      <c r="C34">
+        <v>22.1284957647796</v>
+      </c>
+      <c r="D34">
+        <v>48.4504957647796</v>
+      </c>
+      <c r="E34">
+        <v>-3.148</v>
+      </c>
+      <c r="F34">
+        <v>28.352</v>
+      </c>
+      <c r="G34">
+        <v>2.03</v>
+      </c>
+      <c r="H34">
+        <v>57.1</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>5.68</v>
+      </c>
+      <c r="K34">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L34">
+        <v>1.36</v>
+      </c>
+      <c r="M34">
+        <v>6.7704576</v>
+      </c>
+      <c r="N34">
+        <v>-5.4104576</v>
+      </c>
+      <c r="O34">
+        <v>-1.298509824</v>
+      </c>
+      <c r="P34">
+        <v>-4.111947776</v>
+      </c>
+      <c r="Q34">
+        <v>0.2080522239999993</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1531823288351803</v>
+      </c>
+      <c r="T34">
+        <v>1.432753210464009</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.04820944451376522</v>
+      </c>
+      <c r="W34">
+        <v>0.2272875846501129</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2008726854740218</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1788960106959587</v>
+      </c>
+      <c r="C35">
+        <v>20.55082016996302</v>
+      </c>
+      <c r="D35">
+        <v>47.75882016996302</v>
+      </c>
+      <c r="E35">
+        <v>-2.262</v>
+      </c>
+      <c r="F35">
+        <v>29.238</v>
+      </c>
+      <c r="G35">
+        <v>2.03</v>
+      </c>
+      <c r="H35">
+        <v>57.1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>5.68</v>
+      </c>
+      <c r="K35">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L35">
+        <v>1.36</v>
+      </c>
+      <c r="M35">
+        <v>6.9820344</v>
+      </c>
+      <c r="N35">
+        <v>-5.6220344</v>
+      </c>
+      <c r="O35">
+        <v>-1.349288256</v>
+      </c>
+      <c r="P35">
+        <v>-4.272746143999999</v>
+      </c>
+      <c r="Q35">
+        <v>0.04725385600000021</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1548895277730188</v>
+      </c>
+      <c r="T35">
+        <v>1.454137586739591</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.04674855225577234</v>
+      </c>
+      <c r="W35">
+        <v>0.2276364457213216</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.1947856343990514</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1808960106959587</v>
+      </c>
+      <c r="C36">
+        <v>18.99261522999251</v>
+      </c>
+      <c r="D36">
+        <v>47.0866152299925</v>
+      </c>
+      <c r="E36">
+        <v>-1.376000000000001</v>
+      </c>
+      <c r="F36">
+        <v>30.124</v>
+      </c>
+      <c r="G36">
+        <v>2.03</v>
+      </c>
+      <c r="H36">
+        <v>57.1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>5.68</v>
+      </c>
+      <c r="K36">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L36">
+        <v>1.36</v>
+      </c>
+      <c r="M36">
+        <v>7.1936112</v>
+      </c>
+      <c r="N36">
+        <v>-5.8336112</v>
+      </c>
+      <c r="O36">
+        <v>-1.400066688</v>
+      </c>
+      <c r="P36">
+        <v>-4.433544512</v>
+      </c>
+      <c r="Q36">
+        <v>-0.1135445120000007</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.156648460012004</v>
+      </c>
+      <c r="T36">
+        <v>1.476169974417464</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.04537359483648491</v>
+      </c>
+      <c r="W36">
+        <v>0.2279647855530474</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.1890566451520205</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1828960106959587</v>
+      </c>
+      <c r="C37">
+        <v>17.4530702081342</v>
+      </c>
+      <c r="D37">
+        <v>46.4330702081342</v>
+      </c>
+      <c r="E37">
+        <v>-0.4899999999999984</v>
+      </c>
+      <c r="F37">
+        <v>31.01</v>
+      </c>
+      <c r="G37">
+        <v>2.03</v>
+      </c>
+      <c r="H37">
+        <v>57.1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>5.68</v>
+      </c>
+      <c r="K37">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L37">
+        <v>1.36</v>
+      </c>
+      <c r="M37">
+        <v>7.405188000000001</v>
+      </c>
+      <c r="N37">
+        <v>-6.045188</v>
+      </c>
+      <c r="O37">
+        <v>-1.45084512</v>
+      </c>
+      <c r="P37">
+        <v>-4.59434288</v>
+      </c>
+      <c r="Q37">
+        <v>-0.2743428800000007</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1584615132429579</v>
+      </c>
+      <c r="T37">
+        <v>1.498880281716194</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.04407720641258534</v>
+      </c>
+      <c r="W37">
+        <v>0.2282743631086746</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.1836550267191056</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1848960106959587</v>
+      </c>
+      <c r="C38">
+        <v>15.93141876239053</v>
+      </c>
+      <c r="D38">
+        <v>45.79741876239053</v>
+      </c>
+      <c r="E38">
+        <v>0.3959999999999972</v>
+      </c>
+      <c r="F38">
+        <v>31.896</v>
+      </c>
+      <c r="G38">
+        <v>2.03</v>
+      </c>
+      <c r="H38">
+        <v>57.1</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>5.68</v>
+      </c>
+      <c r="K38">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L38">
+        <v>1.36</v>
+      </c>
+      <c r="M38">
+        <v>7.616764799999999</v>
+      </c>
+      <c r="N38">
+        <v>-6.256764799999999</v>
+      </c>
+      <c r="O38">
+        <v>-1.501623552</v>
+      </c>
+      <c r="P38">
+        <v>-4.755141247999999</v>
+      </c>
+      <c r="Q38">
+        <v>-0.4351412479999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1603312243873791</v>
+      </c>
+      <c r="T38">
+        <v>1.522300286118009</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.04285283956779131</v>
+      </c>
+      <c r="W38">
+        <v>0.2285667419112115</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.1785534981991305</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1868960106959587</v>
+      </c>
+      <c r="C39">
+        <v>14.42693594780057</v>
+      </c>
+      <c r="D39">
+        <v>45.17893594780057</v>
+      </c>
+      <c r="E39">
+        <v>1.281999999999996</v>
+      </c>
+      <c r="F39">
+        <v>32.782</v>
+      </c>
+      <c r="G39">
+        <v>2.03</v>
+      </c>
+      <c r="H39">
+        <v>57.1</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>5.68</v>
+      </c>
+      <c r="K39">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L39">
+        <v>1.36</v>
+      </c>
+      <c r="M39">
+        <v>7.8283416</v>
+      </c>
+      <c r="N39">
+        <v>-6.4683416</v>
+      </c>
+      <c r="O39">
+        <v>-1.552401984</v>
+      </c>
+      <c r="P39">
+        <v>-4.915939615999999</v>
+      </c>
+      <c r="Q39">
+        <v>-0.5959396159999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.162260291441147</v>
+      </c>
+      <c r="T39">
+        <v>1.546463782723057</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.04169465471460777</v>
+      </c>
+      <c r="W39">
+        <v>0.2288433164541517</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.1737277279775323</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1888960106959587</v>
+      </c>
+      <c r="C40">
+        <v>12.93893545840293</v>
+      </c>
+      <c r="D40">
+        <v>44.57693545840293</v>
+      </c>
+      <c r="E40">
+        <v>2.167999999999999</v>
+      </c>
+      <c r="F40">
+        <v>33.668</v>
+      </c>
+      <c r="G40">
+        <v>2.03</v>
+      </c>
+      <c r="H40">
+        <v>57.1</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>5.68</v>
+      </c>
+      <c r="K40">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L40">
+        <v>1.36</v>
+      </c>
+      <c r="M40">
+        <v>8.039918399999999</v>
+      </c>
+      <c r="N40">
+        <v>-6.679918399999999</v>
+      </c>
+      <c r="O40">
+        <v>-1.603180416</v>
+      </c>
+      <c r="P40">
+        <v>-5.076737983999999</v>
+      </c>
+      <c r="Q40">
+        <v>-0.7567379839999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1642515864643913</v>
+      </c>
+      <c r="T40">
+        <v>1.571406746960526</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.04059742695896019</v>
+      </c>
+      <c r="W40">
+        <v>0.2291053344422003</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.1691559456623342</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1908960106959587</v>
+      </c>
+      <c r="C41">
+        <v>11.46676708680095</v>
+      </c>
+      <c r="D41">
+        <v>43.99076708680095</v>
+      </c>
+      <c r="E41">
+        <v>3.054000000000002</v>
+      </c>
+      <c r="F41">
+        <v>34.554</v>
+      </c>
+      <c r="G41">
+        <v>2.03</v>
+      </c>
+      <c r="H41">
+        <v>57.1</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>5.68</v>
+      </c>
+      <c r="K41">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L41">
+        <v>1.36</v>
+      </c>
+      <c r="M41">
+        <v>8.251495200000001</v>
+      </c>
+      <c r="N41">
+        <v>-6.8914952</v>
+      </c>
+      <c r="O41">
+        <v>-1.653958848</v>
+      </c>
+      <c r="P41">
+        <v>-5.237536352</v>
+      </c>
+      <c r="Q41">
+        <v>-0.9175363520000008</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1663081698490535</v>
+      </c>
+      <c r="T41">
+        <v>1.597167513304141</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.03955646729334582</v>
+      </c>
+      <c r="W41">
+        <v>0.229353915610349</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.1648186137222742</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1928960106959587</v>
+      </c>
+      <c r="C42">
+        <v>10.00981438156062</v>
+      </c>
+      <c r="D42">
+        <v>43.41981438156062</v>
+      </c>
+      <c r="E42">
+        <v>3.939999999999998</v>
+      </c>
+      <c r="F42">
+        <v>35.44</v>
+      </c>
+      <c r="G42">
+        <v>2.03</v>
+      </c>
+      <c r="H42">
+        <v>57.1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>5.68</v>
+      </c>
+      <c r="K42">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L42">
+        <v>1.36</v>
+      </c>
+      <c r="M42">
+        <v>8.463072</v>
+      </c>
+      <c r="N42">
+        <v>-7.103072</v>
+      </c>
+      <c r="O42">
+        <v>-1.70473728</v>
+      </c>
+      <c r="P42">
+        <v>-5.39833472</v>
+      </c>
+      <c r="Q42">
+        <v>-1.078334720000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1684333060132044</v>
+      </c>
+      <c r="T42">
+        <v>1.62378697185921</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.03856755561101218</v>
+      </c>
+      <c r="W42">
+        <v>0.2295900677200903</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.1606981483792174</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1948960106959587</v>
+      </c>
+      <c r="C43">
+        <v>8.567492484697631</v>
+      </c>
+      <c r="D43">
+        <v>42.86349248469763</v>
+      </c>
+      <c r="E43">
+        <v>4.826000000000001</v>
+      </c>
+      <c r="F43">
+        <v>36.326</v>
+      </c>
+      <c r="G43">
+        <v>2.03</v>
+      </c>
+      <c r="H43">
+        <v>57.1</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>5.68</v>
+      </c>
+      <c r="K43">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L43">
+        <v>1.36</v>
+      </c>
+      <c r="M43">
+        <v>8.6746488</v>
+      </c>
+      <c r="N43">
+        <v>-7.3146488</v>
+      </c>
+      <c r="O43">
+        <v>-1.755515712</v>
+      </c>
+      <c r="P43">
+        <v>-5.559133087999999</v>
+      </c>
+      <c r="Q43">
+        <v>-1.239133088</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1706304806913943</v>
+      </c>
+      <c r="T43">
+        <v>1.65130878494157</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.03762688352293871</v>
+      </c>
+      <c r="W43">
+        <v>0.2298147002147223</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1567786813455779</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1968960106959587</v>
+      </c>
+      <c r="C44">
+        <v>7.139246133306386</v>
+      </c>
+      <c r="D44">
+        <v>42.32124613330638</v>
+      </c>
+      <c r="E44">
+        <v>5.711999999999996</v>
+      </c>
+      <c r="F44">
+        <v>37.212</v>
+      </c>
+      <c r="G44">
+        <v>2.03</v>
+      </c>
+      <c r="H44">
+        <v>57.1</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>5.68</v>
+      </c>
+      <c r="K44">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L44">
+        <v>1.36</v>
+      </c>
+      <c r="M44">
+        <v>8.8862256</v>
+      </c>
+      <c r="N44">
+        <v>-7.526225599999999</v>
+      </c>
+      <c r="O44">
+        <v>-1.806294144</v>
+      </c>
+      <c r="P44">
+        <v>-5.719931455999999</v>
+      </c>
+      <c r="Q44">
+        <v>-1.399931456</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1729034200136597</v>
+      </c>
+      <c r="T44">
+        <v>1.679779626061252</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.03673100534382112</v>
+      </c>
+      <c r="W44">
+        <v>0.2300286359238955</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.1530458555992547</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1988960106959587</v>
+      </c>
+      <c r="C45">
+        <v>5.724547810976794</v>
+      </c>
+      <c r="D45">
+        <v>41.79254781097679</v>
+      </c>
+      <c r="E45">
+        <v>6.597999999999999</v>
+      </c>
+      <c r="F45">
+        <v>38.098</v>
+      </c>
+      <c r="G45">
+        <v>2.03</v>
+      </c>
+      <c r="H45">
+        <v>57.1</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>5.68</v>
+      </c>
+      <c r="K45">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L45">
+        <v>1.36</v>
+      </c>
+      <c r="M45">
+        <v>9.097802400000001</v>
+      </c>
+      <c r="N45">
+        <v>-7.737802400000001</v>
+      </c>
+      <c r="O45">
+        <v>-1.857072576</v>
+      </c>
+      <c r="P45">
+        <v>-5.880729824</v>
+      </c>
+      <c r="Q45">
+        <v>-1.560729824000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1752561115928467</v>
+      </c>
+      <c r="T45">
+        <v>1.709249444062326</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.03587679591722063</v>
+      </c>
+      <c r="W45">
+        <v>0.2302326211349677</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.149486649655086</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2008960106959587</v>
+      </c>
+      <c r="C46">
+        <v>4.322896036062161</v>
+      </c>
+      <c r="D46">
+        <v>41.27689603606215</v>
+      </c>
+      <c r="E46">
+        <v>7.483999999999995</v>
+      </c>
+      <c r="F46">
+        <v>38.98399999999999</v>
+      </c>
+      <c r="G46">
+        <v>2.03</v>
+      </c>
+      <c r="H46">
+        <v>57.1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>5.68</v>
+      </c>
+      <c r="K46">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L46">
+        <v>1.36</v>
+      </c>
+      <c r="M46">
+        <v>9.309379199999999</v>
+      </c>
+      <c r="N46">
+        <v>-7.949379199999998</v>
+      </c>
+      <c r="O46">
+        <v>-1.907851008</v>
+      </c>
+      <c r="P46">
+        <v>-6.041528191999999</v>
+      </c>
+      <c r="Q46">
+        <v>-1.721528191999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1776928278712904</v>
+      </c>
+      <c r="T46">
+        <v>1.739771755563439</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.03506141419182926</v>
+      </c>
+      <c r="W46">
+        <v>0.2304273342909912</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1460892257992886</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2028960106959588</v>
+      </c>
+      <c r="C47">
+        <v>2.933813775122353</v>
+      </c>
+      <c r="D47">
+        <v>40.77381377512235</v>
+      </c>
+      <c r="E47">
+        <v>8.369999999999997</v>
+      </c>
+      <c r="F47">
+        <v>39.87</v>
+      </c>
+      <c r="G47">
+        <v>2.03</v>
+      </c>
+      <c r="H47">
+        <v>57.1</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>5.68</v>
+      </c>
+      <c r="K47">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L47">
+        <v>1.36</v>
+      </c>
+      <c r="M47">
+        <v>9.520956</v>
+      </c>
+      <c r="N47">
+        <v>-8.160955999999999</v>
+      </c>
+      <c r="O47">
+        <v>-1.95862944</v>
+      </c>
+      <c r="P47">
+        <v>-6.202326559999999</v>
+      </c>
+      <c r="Q47">
+        <v>-1.88232656</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1802181520144047</v>
+      </c>
+      <c r="T47">
+        <v>1.771403969300956</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.03428227165423305</v>
+      </c>
+      <c r="W47">
+        <v>0.2306133935289692</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1428427985593045</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2048960106959588</v>
+      </c>
+      <c r="C48">
+        <v>1.556846970991707</v>
+      </c>
+      <c r="D48">
+        <v>40.28284697099171</v>
+      </c>
+      <c r="E48">
+        <v>9.256</v>
+      </c>
+      <c r="F48">
+        <v>40.756</v>
+      </c>
+      <c r="G48">
+        <v>2.03</v>
+      </c>
+      <c r="H48">
+        <v>57.1</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>5.68</v>
+      </c>
+      <c r="K48">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L48">
+        <v>1.36</v>
+      </c>
+      <c r="M48">
+        <v>9.732532800000001</v>
+      </c>
+      <c r="N48">
+        <v>-8.372532800000002</v>
+      </c>
+      <c r="O48">
+        <v>-2.009407872000001</v>
+      </c>
+      <c r="P48">
+        <v>-6.363124928000001</v>
+      </c>
+      <c r="Q48">
+        <v>-2.043124928000002</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1828370066813382</v>
+      </c>
+      <c r="T48">
+        <v>1.804207746510233</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.03353700487914102</v>
+      </c>
+      <c r="W48">
+        <v>0.2307913632348611</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1397375203297542</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2068960106959588</v>
+      </c>
+      <c r="C49">
+        <v>0.1915631759246992</v>
+      </c>
+      <c r="D49">
+        <v>39.8035631759247</v>
+      </c>
+      <c r="E49">
+        <v>10.142</v>
+      </c>
+      <c r="F49">
+        <v>41.642</v>
+      </c>
+      <c r="G49">
+        <v>2.03</v>
+      </c>
+      <c r="H49">
+        <v>57.1</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>5.68</v>
+      </c>
+      <c r="K49">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L49">
+        <v>1.36</v>
+      </c>
+      <c r="M49">
+        <v>9.944109600000001</v>
+      </c>
+      <c r="N49">
+        <v>-8.584109600000001</v>
+      </c>
+      <c r="O49">
+        <v>-2.060186304</v>
+      </c>
+      <c r="P49">
+        <v>-6.523923296000001</v>
+      </c>
+      <c r="Q49">
+        <v>-2.203923296000002</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1855546860526842</v>
+      </c>
+      <c r="T49">
+        <v>1.838249402104766</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.03282345158384015</v>
+      </c>
+      <c r="W49">
+        <v>0.230961759761779</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1367643815993339</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2088960106959587</v>
+      </c>
+      <c r="C50">
+        <v>-1.16244971882886</v>
+      </c>
+      <c r="D50">
+        <v>39.33555028117114</v>
+      </c>
+      <c r="E50">
+        <v>11.028</v>
+      </c>
+      <c r="F50">
+        <v>42.528</v>
+      </c>
+      <c r="G50">
+        <v>2.03</v>
+      </c>
+      <c r="H50">
+        <v>57.1</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>5.68</v>
+      </c>
+      <c r="K50">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L50">
+        <v>1.36</v>
+      </c>
+      <c r="M50">
+        <v>10.1556864</v>
+      </c>
+      <c r="N50">
+        <v>-8.795686400000001</v>
+      </c>
+      <c r="O50">
+        <v>-2.110964736</v>
+      </c>
+      <c r="P50">
+        <v>-6.684721664000001</v>
+      </c>
+      <c r="Q50">
+        <v>-2.364721664000002</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1883768915536973</v>
+      </c>
+      <c r="T50">
+        <v>1.873600352145242</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.03213962967584348</v>
+      </c>
+      <c r="W50">
+        <v>0.2311250564334086</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1339151236493478</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2108960106959587</v>
+      </c>
+      <c r="C51">
+        <v>-2.505584664863896</v>
+      </c>
+      <c r="D51">
+        <v>38.8784153351361</v>
+      </c>
+      <c r="E51">
+        <v>11.91399999999999</v>
+      </c>
+      <c r="F51">
+        <v>43.41399999999999</v>
+      </c>
+      <c r="G51">
+        <v>2.03</v>
+      </c>
+      <c r="H51">
+        <v>57.1</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>5.68</v>
+      </c>
+      <c r="K51">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L51">
+        <v>1.36</v>
+      </c>
+      <c r="M51">
+        <v>10.3672632</v>
+      </c>
+      <c r="N51">
+        <v>-9.007263200000001</v>
+      </c>
+      <c r="O51">
+        <v>-2.161743168</v>
+      </c>
+      <c r="P51">
+        <v>-6.845520032</v>
+      </c>
+      <c r="Q51">
+        <v>-2.525520032000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1913097717802404</v>
+      </c>
+      <c r="T51">
+        <v>1.910337613952012</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.03148371886613239</v>
+      </c>
+      <c r="W51">
+        <v>0.2312816879347676</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1311821619422182</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2128960106959587</v>
+      </c>
+      <c r="C52">
+        <v>-3.838216556998788</v>
+      </c>
+      <c r="D52">
+        <v>38.43178344300121</v>
+      </c>
+      <c r="E52">
+        <v>12.8</v>
+      </c>
+      <c r="F52">
+        <v>44.3</v>
+      </c>
+      <c r="G52">
+        <v>2.03</v>
+      </c>
+      <c r="H52">
+        <v>57.1</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>5.68</v>
+      </c>
+      <c r="K52">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L52">
+        <v>1.36</v>
+      </c>
+      <c r="M52">
+        <v>10.57884</v>
+      </c>
+      <c r="N52">
+        <v>-9.21884</v>
+      </c>
+      <c r="O52">
+        <v>-2.2125216</v>
+      </c>
+      <c r="P52">
+        <v>-7.0063184</v>
+      </c>
+      <c r="Q52">
+        <v>-2.6863184</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1943599672158452</v>
+      </c>
+      <c r="T52">
+        <v>1.948544366231052</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.03085404448880975</v>
+      </c>
+      <c r="W52">
+        <v>0.2314320541760722</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1285585187033739</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2148960106959588</v>
+      </c>
+      <c r="C53">
+        <v>-5.160703258669237</v>
+      </c>
+      <c r="D53">
+        <v>37.99529674133076</v>
+      </c>
+      <c r="E53">
+        <v>13.686</v>
+      </c>
+      <c r="F53">
+        <v>45.186</v>
+      </c>
+      <c r="G53">
+        <v>2.03</v>
+      </c>
+      <c r="H53">
+        <v>57.1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>5.68</v>
+      </c>
+      <c r="K53">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L53">
+        <v>1.36</v>
+      </c>
+      <c r="M53">
+        <v>10.7904168</v>
+      </c>
+      <c r="N53">
+        <v>-9.4304168</v>
+      </c>
+      <c r="O53">
+        <v>-2.263300032</v>
+      </c>
+      <c r="P53">
+        <v>-7.167116768</v>
+      </c>
+      <c r="Q53">
+        <v>-2.847116768</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1975346604243319</v>
+      </c>
+      <c r="T53">
+        <v>1.988310577786788</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.03024906322432327</v>
+      </c>
+      <c r="W53">
+        <v>0.2315765237020316</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1260377634346804</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2168960106959588</v>
+      </c>
+      <c r="C54">
+        <v>-6.473386558231695</v>
+      </c>
+      <c r="D54">
+        <v>37.5686134417683</v>
+      </c>
+      <c r="E54">
+        <v>14.572</v>
+      </c>
+      <c r="F54">
+        <v>46.072</v>
+      </c>
+      <c r="G54">
+        <v>2.03</v>
+      </c>
+      <c r="H54">
+        <v>57.1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>5.68</v>
+      </c>
+      <c r="K54">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L54">
+        <v>1.36</v>
+      </c>
+      <c r="M54">
+        <v>11.0019936</v>
+      </c>
+      <c r="N54">
+        <v>-9.641993599999999</v>
+      </c>
+      <c r="O54">
+        <v>-2.314078464</v>
+      </c>
+      <c r="P54">
+        <v>-7.327915136</v>
+      </c>
+      <c r="Q54">
+        <v>-3.007915136</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2008416325165055</v>
+      </c>
+      <c r="T54">
+        <v>2.029733714824013</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.02966735047000937</v>
+      </c>
+      <c r="W54">
+        <v>0.2317154367077618</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1236139602917057</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2188960106959587</v>
+      </c>
+      <c r="C55">
+        <v>-7.77659306154721</v>
+      </c>
+      <c r="D55">
+        <v>37.15140693845279</v>
+      </c>
+      <c r="E55">
+        <v>15.458</v>
+      </c>
+      <c r="F55">
+        <v>46.958</v>
+      </c>
+      <c r="G55">
+        <v>2.03</v>
+      </c>
+      <c r="H55">
+        <v>57.1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>5.68</v>
+      </c>
+      <c r="K55">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L55">
+        <v>1.36</v>
+      </c>
+      <c r="M55">
+        <v>11.2135704</v>
+      </c>
+      <c r="N55">
+        <v>-9.853570399999999</v>
+      </c>
+      <c r="O55">
+        <v>-2.364856896</v>
+      </c>
+      <c r="P55">
+        <v>-7.488713504</v>
+      </c>
+      <c r="Q55">
+        <v>-3.168713504</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2042893268253673</v>
+      </c>
+      <c r="T55">
+        <v>2.072919538543673</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.02910758914038655</v>
+      </c>
+      <c r="W55">
+        <v>0.2318491077132757</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1212816214182774</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2208960106959588</v>
+      </c>
+      <c r="C56">
+        <v>-9.070635025744714</v>
+      </c>
+      <c r="D56">
+        <v>36.74336497425529</v>
+      </c>
+      <c r="E56">
+        <v>16.344</v>
+      </c>
+      <c r="F56">
+        <v>47.844</v>
+      </c>
+      <c r="G56">
+        <v>2.03</v>
+      </c>
+      <c r="H56">
+        <v>57.1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>5.68</v>
+      </c>
+      <c r="K56">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L56">
+        <v>1.36</v>
+      </c>
+      <c r="M56">
+        <v>11.4251472</v>
+      </c>
+      <c r="N56">
+        <v>-10.0651472</v>
+      </c>
+      <c r="O56">
+        <v>-2.415635328</v>
+      </c>
+      <c r="P56">
+        <v>-7.649511872000001</v>
+      </c>
+      <c r="Q56">
+        <v>-3.329511872000002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2078869208867883</v>
+      </c>
+      <c r="T56">
+        <v>2.117983006772883</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.02856855971186087</v>
+      </c>
+      <c r="W56">
+        <v>0.2319778279408076</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1190356654660869</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2228960106959588</v>
+      </c>
+      <c r="C57">
+        <v>-10.35581113863657</v>
+      </c>
+      <c r="D57">
+        <v>36.34418886136343</v>
+      </c>
+      <c r="E57">
+        <v>17.23</v>
+      </c>
+      <c r="F57">
+        <v>48.73</v>
+      </c>
+      <c r="G57">
+        <v>2.03</v>
+      </c>
+      <c r="H57">
+        <v>57.1</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>5.68</v>
+      </c>
+      <c r="K57">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L57">
+        <v>1.36</v>
+      </c>
+      <c r="M57">
+        <v>11.636724</v>
+      </c>
+      <c r="N57">
+        <v>-10.276724</v>
+      </c>
+      <c r="O57">
+        <v>-2.46641376</v>
+      </c>
+      <c r="P57">
+        <v>-7.810310240000002</v>
+      </c>
+      <c r="Q57">
+        <v>-3.490310240000002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2116444080176059</v>
+      </c>
+      <c r="T57">
+        <v>2.165049295812281</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.0280491313534634</v>
+      </c>
+      <c r="W57">
+        <v>0.232101867432793</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1168713806394308</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AM4">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AN4">
-        <v>-8.046875</v>
-      </c>
-      <c r="AO4">
-        <v>-4.160714285714286</v>
-      </c>
-      <c r="AP4">
-        <v>-7.5671875</v>
-      </c>
-      <c r="AQ4">
-        <v>-4.160714285714286</v>
+      <c r="B58">
+        <v>0.2248960106959587</v>
+      </c>
+      <c r="C58">
+        <v>-11.63240724787548</v>
+      </c>
+      <c r="D58">
+        <v>35.95359275212451</v>
+      </c>
+      <c r="E58">
+        <v>18.116</v>
+      </c>
+      <c r="F58">
+        <v>49.616</v>
+      </c>
+      <c r="G58">
+        <v>2.03</v>
+      </c>
+      <c r="H58">
+        <v>57.1</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>5.68</v>
+      </c>
+      <c r="K58">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L58">
+        <v>1.36</v>
+      </c>
+      <c r="M58">
+        <v>11.8483008</v>
+      </c>
+      <c r="N58">
+        <v>-10.4883008</v>
+      </c>
+      <c r="O58">
+        <v>-2.517192192</v>
+      </c>
+      <c r="P58">
+        <v>-7.971108608000002</v>
+      </c>
+      <c r="Q58">
+        <v>-3.651108608000002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2155726900180059</v>
+      </c>
+      <c r="T58">
+        <v>2.214254961626196</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.02754825400786584</v>
+      </c>
+      <c r="W58">
+        <v>0.2322214769429216</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1147843916994409</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2268960106959587</v>
+      </c>
+      <c r="C59">
+        <v>-12.90069704359306</v>
+      </c>
+      <c r="D59">
+        <v>35.57130295640694</v>
+      </c>
+      <c r="E59">
+        <v>19.002</v>
+      </c>
+      <c r="F59">
+        <v>50.502</v>
+      </c>
+      <c r="G59">
+        <v>2.03</v>
+      </c>
+      <c r="H59">
+        <v>57.1</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>5.68</v>
+      </c>
+      <c r="K59">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L59">
+        <v>1.36</v>
+      </c>
+      <c r="M59">
+        <v>12.0598776</v>
+      </c>
+      <c r="N59">
+        <v>-10.6998776</v>
+      </c>
+      <c r="O59">
+        <v>-2.567970624</v>
+      </c>
+      <c r="P59">
+        <v>-8.131906976</v>
+      </c>
+      <c r="Q59">
+        <v>-3.811906976</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2196836828091224</v>
+      </c>
+      <c r="T59">
+        <v>2.265749263059363</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.02706495130597346</v>
+      </c>
+      <c r="W59">
+        <v>0.2323368896281336</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1127706304415561</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2288960106959587</v>
+      </c>
+      <c r="C60">
+        <v>-14.1609426979461</v>
+      </c>
+      <c r="D60">
+        <v>35.19705730205389</v>
+      </c>
+      <c r="E60">
+        <v>19.88799999999999</v>
+      </c>
+      <c r="F60">
+        <v>51.38799999999999</v>
+      </c>
+      <c r="G60">
+        <v>2.03</v>
+      </c>
+      <c r="H60">
+        <v>57.1</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>5.68</v>
+      </c>
+      <c r="K60">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L60">
+        <v>1.36</v>
+      </c>
+      <c r="M60">
+        <v>12.2714544</v>
+      </c>
+      <c r="N60">
+        <v>-10.9114544</v>
+      </c>
+      <c r="O60">
+        <v>-2.618749055999999</v>
+      </c>
+      <c r="P60">
+        <v>-8.292705343999998</v>
+      </c>
+      <c r="Q60">
+        <v>-3.972705343999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2239904371617205</v>
+      </c>
+      <c r="T60">
+        <v>2.319695674084586</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.02659831421449116</v>
+      </c>
+      <c r="W60">
+        <v>0.2324483225655795</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1108263092270466</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2308960106959587</v>
+      </c>
+      <c r="C61">
+        <v>-15.41339546471139</v>
+      </c>
+      <c r="D61">
+        <v>34.8306045352886</v>
+      </c>
+      <c r="E61">
+        <v>20.77399999999999</v>
+      </c>
+      <c r="F61">
+        <v>52.27399999999999</v>
+      </c>
+      <c r="G61">
+        <v>2.03</v>
+      </c>
+      <c r="H61">
+        <v>57.1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>5.68</v>
+      </c>
+      <c r="K61">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L61">
+        <v>1.36</v>
+      </c>
+      <c r="M61">
+        <v>12.4830312</v>
+      </c>
+      <c r="N61">
+        <v>-11.1230312</v>
+      </c>
+      <c r="O61">
+        <v>-2.669527488</v>
+      </c>
+      <c r="P61">
+        <v>-8.453503712</v>
+      </c>
+      <c r="Q61">
+        <v>-4.133503712</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2285072770924942</v>
+      </c>
+      <c r="T61">
+        <v>2.376273617354941</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.02614749532949978</v>
+      </c>
+      <c r="W61">
+        <v>0.2325559781153155</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.108947897206249</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2328960106959587</v>
+      </c>
+      <c r="C62">
+        <v>-16.6582962418103</v>
+      </c>
+      <c r="D62">
+        <v>34.4717037581897</v>
+      </c>
+      <c r="E62">
+        <v>21.66</v>
+      </c>
+      <c r="F62">
+        <v>53.16</v>
+      </c>
+      <c r="G62">
+        <v>2.03</v>
+      </c>
+      <c r="H62">
+        <v>57.1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>5.68</v>
+      </c>
+      <c r="K62">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L62">
+        <v>1.36</v>
+      </c>
+      <c r="M62">
+        <v>12.694608</v>
+      </c>
+      <c r="N62">
+        <v>-11.334608</v>
+      </c>
+      <c r="O62">
+        <v>-2.72030592</v>
+      </c>
+      <c r="P62">
+        <v>-8.61430208</v>
+      </c>
+      <c r="Q62">
+        <v>-4.29430208</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2332499590198065</v>
+      </c>
+      <c r="T62">
+        <v>2.435680457788815</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.02571170374067479</v>
+      </c>
+      <c r="W62">
+        <v>0.2326600451467269</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1071320989194784</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2348960106959587</v>
+      </c>
+      <c r="C63">
+        <v>-17.89587609941012</v>
+      </c>
+      <c r="D63">
+        <v>34.12012390058987</v>
+      </c>
+      <c r="E63">
+        <v>22.54599999999999</v>
+      </c>
+      <c r="F63">
+        <v>54.04599999999999</v>
+      </c>
+      <c r="G63">
+        <v>2.03</v>
+      </c>
+      <c r="H63">
+        <v>57.1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>5.68</v>
+      </c>
+      <c r="K63">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L63">
+        <v>1.36</v>
+      </c>
+      <c r="M63">
+        <v>12.9061848</v>
+      </c>
+      <c r="N63">
+        <v>-11.5461848</v>
+      </c>
+      <c r="O63">
+        <v>-2.771084351999999</v>
+      </c>
+      <c r="P63">
+        <v>-8.775100448</v>
+      </c>
+      <c r="Q63">
+        <v>-4.455100448</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2382358554049298</v>
+      </c>
+      <c r="T63">
+        <v>2.498133802860323</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.02529020040066373</v>
+      </c>
+      <c r="W63">
+        <v>0.2327607001443215</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1053758350027655</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2368960106959588</v>
+      </c>
+      <c r="C64">
+        <v>-19.12635677603475</v>
+      </c>
+      <c r="D64">
+        <v>33.77564322396525</v>
+      </c>
+      <c r="E64">
+        <v>23.432</v>
+      </c>
+      <c r="F64">
+        <v>54.932</v>
+      </c>
+      <c r="G64">
+        <v>2.03</v>
+      </c>
+      <c r="H64">
+        <v>57.1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>5.68</v>
+      </c>
+      <c r="K64">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L64">
+        <v>1.36</v>
+      </c>
+      <c r="M64">
+        <v>13.1177616</v>
+      </c>
+      <c r="N64">
+        <v>-11.7577616</v>
+      </c>
+      <c r="O64">
+        <v>-2.821862783999999</v>
+      </c>
+      <c r="P64">
+        <v>-8.935898815999998</v>
+      </c>
+      <c r="Q64">
+        <v>-4.615898815999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.24348416738927</v>
+      </c>
+      <c r="T64">
+        <v>2.563874166093489</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.0248822939425885</v>
+      </c>
+      <c r="W64">
+        <v>0.2328581082065099</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1036762247607855</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2388960106959587</v>
+      </c>
+      <c r="C65">
+        <v>-20.34995114492284</v>
+      </c>
+      <c r="D65">
+        <v>33.43804885507716</v>
+      </c>
+      <c r="E65">
+        <v>24.318</v>
+      </c>
+      <c r="F65">
+        <v>55.818</v>
+      </c>
+      <c r="G65">
+        <v>2.03</v>
+      </c>
+      <c r="H65">
+        <v>57.1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>5.68</v>
+      </c>
+      <c r="K65">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L65">
+        <v>1.36</v>
+      </c>
+      <c r="M65">
+        <v>13.3293384</v>
+      </c>
+      <c r="N65">
+        <v>-11.9693384</v>
+      </c>
+      <c r="O65">
+        <v>-2.872641216</v>
+      </c>
+      <c r="P65">
+        <v>-9.096697184000002</v>
+      </c>
+      <c r="Q65">
+        <v>-4.776697184000002</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2490161719133044</v>
+      </c>
+      <c r="T65">
+        <v>2.633168062474395</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.02448733689588075</v>
+      </c>
+      <c r="W65">
+        <v>0.2329524239492637</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.102030570399503</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2408960106959587</v>
+      </c>
+      <c r="C66">
+        <v>-21.56686365269504</v>
+      </c>
+      <c r="D66">
+        <v>33.10713634730496</v>
+      </c>
+      <c r="E66">
+        <v>25.204</v>
+      </c>
+      <c r="F66">
+        <v>56.704</v>
+      </c>
+      <c r="G66">
+        <v>2.03</v>
+      </c>
+      <c r="H66">
+        <v>57.1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>5.68</v>
+      </c>
+      <c r="K66">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L66">
+        <v>1.36</v>
+      </c>
+      <c r="M66">
+        <v>13.5409152</v>
+      </c>
+      <c r="N66">
+        <v>-12.1809152</v>
+      </c>
+      <c r="O66">
+        <v>-2.923419648</v>
+      </c>
+      <c r="P66">
+        <v>-9.257495552000002</v>
+      </c>
+      <c r="Q66">
+        <v>-4.937495552000002</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2548555100220073</v>
+      </c>
+      <c r="T66">
+        <v>2.706311619765351</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02410472225688261</v>
+      </c>
+      <c r="W66">
+        <v>0.2330437923250564</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1004363427370109</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2428960106959588</v>
+      </c>
+      <c r="C67">
+        <v>-22.77729073222893</v>
+      </c>
+      <c r="D67">
+        <v>32.78270926777106</v>
+      </c>
+      <c r="E67">
+        <v>26.09</v>
+      </c>
+      <c r="F67">
+        <v>57.59</v>
+      </c>
+      <c r="G67">
+        <v>2.03</v>
+      </c>
+      <c r="H67">
+        <v>57.1</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>5.68</v>
+      </c>
+      <c r="K67">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L67">
+        <v>1.36</v>
+      </c>
+      <c r="M67">
+        <v>13.752492</v>
+      </c>
+      <c r="N67">
+        <v>-12.392492</v>
+      </c>
+      <c r="O67">
+        <v>-2.97419808</v>
+      </c>
+      <c r="P67">
+        <v>-9.41829392</v>
+      </c>
+      <c r="Q67">
+        <v>-5.098293920000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2610285245940647</v>
+      </c>
+      <c r="T67">
+        <v>2.783634808901504</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.02373388037600749</v>
+      </c>
+      <c r="W67">
+        <v>0.2331323493662094</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.09889116823336452</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2448960106959587</v>
+      </c>
+      <c r="C68">
+        <v>-23.98142119149468</v>
+      </c>
+      <c r="D68">
+        <v>32.46457880850532</v>
+      </c>
+      <c r="E68">
+        <v>26.976</v>
+      </c>
+      <c r="F68">
+        <v>58.476</v>
+      </c>
+      <c r="G68">
+        <v>2.03</v>
+      </c>
+      <c r="H68">
+        <v>57.1</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>5.68</v>
+      </c>
+      <c r="K68">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L68">
+        <v>1.36</v>
+      </c>
+      <c r="M68">
+        <v>13.9640688</v>
+      </c>
+      <c r="N68">
+        <v>-12.6040688</v>
+      </c>
+      <c r="O68">
+        <v>-3.024976512</v>
+      </c>
+      <c r="P68">
+        <v>-9.579092288</v>
+      </c>
+      <c r="Q68">
+        <v>-5.259092288000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2675646576703607</v>
+      </c>
+      <c r="T68">
+        <v>2.865506420928019</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.02337427612788617</v>
+      </c>
+      <c r="W68">
+        <v>0.2332182228606608</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.09739281719952564</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2468960106959587</v>
+      </c>
+      <c r="C69">
+        <v>-25.17943657996782</v>
+      </c>
+      <c r="D69">
+        <v>32.15256342003218</v>
+      </c>
+      <c r="E69">
+        <v>27.862</v>
+      </c>
+      <c r="F69">
+        <v>59.362</v>
+      </c>
+      <c r="G69">
+        <v>2.03</v>
+      </c>
+      <c r="H69">
+        <v>57.1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>5.68</v>
+      </c>
+      <c r="K69">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L69">
+        <v>1.36</v>
+      </c>
+      <c r="M69">
+        <v>14.1756456</v>
+      </c>
+      <c r="N69">
+        <v>-12.8156456</v>
+      </c>
+      <c r="O69">
+        <v>-3.075754944</v>
+      </c>
+      <c r="P69">
+        <v>-9.739890656</v>
+      </c>
+      <c r="Q69">
+        <v>-5.419890656000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.274496920024008</v>
+      </c>
+      <c r="T69">
+        <v>2.952339948834928</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02302540633493264</v>
+      </c>
+      <c r="W69">
+        <v>0.2333015329672181</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.09593919306221943</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2488960106959588</v>
+      </c>
+      <c r="C70">
+        <v>-26.37151153411402</v>
+      </c>
+      <c r="D70">
+        <v>31.84648846588598</v>
+      </c>
+      <c r="E70">
+        <v>28.748</v>
+      </c>
+      <c r="F70">
+        <v>60.248</v>
+      </c>
+      <c r="G70">
+        <v>2.03</v>
+      </c>
+      <c r="H70">
+        <v>57.1</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>5.68</v>
+      </c>
+      <c r="K70">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L70">
+        <v>1.36</v>
+      </c>
+      <c r="M70">
+        <v>14.3872224</v>
+      </c>
+      <c r="N70">
+        <v>-13.0272224</v>
+      </c>
+      <c r="O70">
+        <v>-3.126533376</v>
+      </c>
+      <c r="P70">
+        <v>-9.900689024</v>
+      </c>
+      <c r="Q70">
+        <v>-5.580689024000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2818624487747582</v>
+      </c>
+      <c r="T70">
+        <v>3.044600572236019</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02268679741824246</v>
+      </c>
+      <c r="W70">
+        <v>0.2333823927765237</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.09452832257601029</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2508960106959587</v>
+      </c>
+      <c r="C71">
+        <v>-27.55781410332677</v>
+      </c>
+      <c r="D71">
+        <v>31.54618589667323</v>
+      </c>
+      <c r="E71">
+        <v>29.634</v>
+      </c>
+      <c r="F71">
+        <v>61.134</v>
+      </c>
+      <c r="G71">
+        <v>2.03</v>
+      </c>
+      <c r="H71">
+        <v>57.1</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>5.68</v>
+      </c>
+      <c r="K71">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L71">
+        <v>1.36</v>
+      </c>
+      <c r="M71">
+        <v>14.5987992</v>
+      </c>
+      <c r="N71">
+        <v>-13.2387992</v>
+      </c>
+      <c r="O71">
+        <v>-3.177311808</v>
+      </c>
+      <c r="P71">
+        <v>-10.061487392</v>
+      </c>
+      <c r="Q71">
+        <v>-5.741487392000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2897031729287827</v>
+      </c>
+      <c r="T71">
+        <v>3.142813493921052</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02235800325276068</v>
+      </c>
+      <c r="W71">
+        <v>0.2334609088232407</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.09315834688650293</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2528960106959587</v>
+      </c>
+      <c r="C72">
+        <v>-28.73850605759651</v>
+      </c>
+      <c r="D72">
+        <v>31.25149394240349</v>
+      </c>
+      <c r="E72">
+        <v>30.52</v>
+      </c>
+      <c r="F72">
+        <v>62.02</v>
+      </c>
+      <c r="G72">
+        <v>2.03</v>
+      </c>
+      <c r="H72">
+        <v>57.1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>5.68</v>
+      </c>
+      <c r="K72">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L72">
+        <v>1.36</v>
+      </c>
+      <c r="M72">
+        <v>14.810376</v>
+      </c>
+      <c r="N72">
+        <v>-13.450376</v>
+      </c>
+      <c r="O72">
+        <v>-3.22809024</v>
+      </c>
+      <c r="P72">
+        <v>-10.22228576</v>
+      </c>
+      <c r="Q72">
+        <v>-5.902285760000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2980666120264088</v>
+      </c>
+      <c r="T72">
+        <v>3.247573943718421</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.02203860320629267</v>
+      </c>
+      <c r="W72">
+        <v>0.2335371815543373</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.09182751335955275</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2548960106959587</v>
+      </c>
+      <c r="C73">
+        <v>-29.91374317809451</v>
+      </c>
+      <c r="D73">
+        <v>30.96225682190548</v>
+      </c>
+      <c r="E73">
+        <v>31.40599999999999</v>
+      </c>
+      <c r="F73">
+        <v>62.90599999999999</v>
+      </c>
+      <c r="G73">
+        <v>2.03</v>
+      </c>
+      <c r="H73">
+        <v>57.1</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>5.68</v>
+      </c>
+      <c r="K73">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L73">
+        <v>1.36</v>
+      </c>
+      <c r="M73">
+        <v>15.0219528</v>
+      </c>
+      <c r="N73">
+        <v>-13.6619528</v>
+      </c>
+      <c r="O73">
+        <v>-3.278868671999999</v>
+      </c>
+      <c r="P73">
+        <v>-10.383084128</v>
+      </c>
+      <c r="Q73">
+        <v>-6.063084127999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3070068400273193</v>
+      </c>
+      <c r="T73">
+        <v>3.359559252122503</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02172820034423222</v>
+      </c>
+      <c r="W73">
+        <v>0.2336113057577974</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.09053416810096759</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2568960106959587</v>
+      </c>
+      <c r="C74">
+        <v>-31.08367553176849</v>
+      </c>
+      <c r="D74">
+        <v>30.6783244682315</v>
+      </c>
+      <c r="E74">
+        <v>32.29199999999999</v>
+      </c>
+      <c r="F74">
+        <v>63.79199999999999</v>
+      </c>
+      <c r="G74">
+        <v>2.03</v>
+      </c>
+      <c r="H74">
+        <v>57.1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>5.68</v>
+      </c>
+      <c r="K74">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L74">
+        <v>1.36</v>
+      </c>
+      <c r="M74">
+        <v>15.2335296</v>
+      </c>
+      <c r="N74">
+        <v>-13.8735296</v>
+      </c>
+      <c r="O74">
+        <v>-3.329647103999999</v>
+      </c>
+      <c r="P74">
+        <v>-10.543882496</v>
+      </c>
+      <c r="Q74">
+        <v>-6.223882495999999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3165856557425807</v>
+      </c>
+      <c r="T74">
+        <v>3.479543511126878</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02142641978389566</v>
+      </c>
+      <c r="W74">
+        <v>0.2336833709556057</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.08927674909956529</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2588960106959587</v>
+      </c>
+      <c r="C75">
+        <v>-32.2484477309667</v>
+      </c>
+      <c r="D75">
+        <v>30.39955226903329</v>
+      </c>
+      <c r="E75">
+        <v>33.178</v>
+      </c>
+      <c r="F75">
+        <v>64.678</v>
+      </c>
+      <c r="G75">
+        <v>2.03</v>
+      </c>
+      <c r="H75">
+        <v>57.1</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>5.68</v>
+      </c>
+      <c r="K75">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L75">
+        <v>1.36</v>
+      </c>
+      <c r="M75">
+        <v>15.4451064</v>
+      </c>
+      <c r="N75">
+        <v>-14.0851064</v>
+      </c>
+      <c r="O75">
+        <v>-3.380425536</v>
+      </c>
+      <c r="P75">
+        <v>-10.704680864</v>
+      </c>
+      <c r="Q75">
+        <v>-6.384680864000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3268740133626763</v>
+      </c>
+      <c r="T75">
+        <v>3.608415493020466</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02113290718411626</v>
+      </c>
+      <c r="W75">
+        <v>0.233753461764433</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.08805377993381769</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2608960106959587</v>
+      </c>
+      <c r="C76">
+        <v>-33.40819917903436</v>
+      </c>
+      <c r="D76">
+        <v>30.12580082096564</v>
+      </c>
+      <c r="E76">
+        <v>34.06399999999999</v>
+      </c>
+      <c r="F76">
+        <v>65.56399999999999</v>
+      </c>
+      <c r="G76">
+        <v>2.03</v>
+      </c>
+      <c r="H76">
+        <v>57.1</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>5.68</v>
+      </c>
+      <c r="K76">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L76">
+        <v>1.36</v>
+      </c>
+      <c r="M76">
+        <v>15.6566832</v>
+      </c>
+      <c r="N76">
+        <v>-14.2966832</v>
+      </c>
+      <c r="O76">
+        <v>-3.431203968</v>
+      </c>
+      <c r="P76">
+        <v>-10.865479232</v>
+      </c>
+      <c r="Q76">
+        <v>-6.545479232000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3379537831073947</v>
+      </c>
+      <c r="T76">
+        <v>3.747200704290485</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02084732735730388</v>
+      </c>
+      <c r="W76">
+        <v>0.2338216582270758</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.08686386398876611</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2628960106959587</v>
+      </c>
+      <c r="C77">
+        <v>-34.56306430275882</v>
+      </c>
+      <c r="D77">
+        <v>29.85693569724117</v>
+      </c>
+      <c r="E77">
+        <v>34.94999999999999</v>
+      </c>
+      <c r="F77">
+        <v>66.44999999999999</v>
+      </c>
+      <c r="G77">
+        <v>2.03</v>
+      </c>
+      <c r="H77">
+        <v>57.1</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>5.68</v>
+      </c>
+      <c r="K77">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L77">
+        <v>1.36</v>
+      </c>
+      <c r="M77">
+        <v>15.86826</v>
+      </c>
+      <c r="N77">
+        <v>-14.50826</v>
+      </c>
+      <c r="O77">
+        <v>-3.481982399999999</v>
+      </c>
+      <c r="P77">
+        <v>-11.0262776</v>
+      </c>
+      <c r="Q77">
+        <v>-6.706277599999997</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3499199344316904</v>
+      </c>
+      <c r="T77">
+        <v>3.897088732462104</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.02056936299253983</v>
+      </c>
+      <c r="W77">
+        <v>0.2338880361173815</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.08570567913558269</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2648960106959588</v>
+      </c>
+      <c r="C78">
+        <v>-35.71317277247785</v>
+      </c>
+      <c r="D78">
+        <v>29.59282722752215</v>
+      </c>
+      <c r="E78">
+        <v>35.836</v>
+      </c>
+      <c r="F78">
+        <v>67.336</v>
+      </c>
+      <c r="G78">
+        <v>2.03</v>
+      </c>
+      <c r="H78">
+        <v>57.1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>5.68</v>
+      </c>
+      <c r="K78">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L78">
+        <v>1.36</v>
+      </c>
+      <c r="M78">
+        <v>16.0798368</v>
+      </c>
+      <c r="N78">
+        <v>-14.7198368</v>
+      </c>
+      <c r="O78">
+        <v>-3.532760832</v>
+      </c>
+      <c r="P78">
+        <v>-11.187075968</v>
+      </c>
+      <c r="Q78">
+        <v>-6.867075968000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.362883265033011</v>
+      </c>
+      <c r="T78">
+        <v>4.059467429648026</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02029871347948009</v>
+      </c>
+      <c r="W78">
+        <v>0.2339526672211002</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.08457797283116697</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2668960106959588</v>
+      </c>
+      <c r="C79">
+        <v>-36.85864971060779</v>
+      </c>
+      <c r="D79">
+        <v>29.3333502893922</v>
+      </c>
+      <c r="E79">
+        <v>36.72199999999999</v>
+      </c>
+      <c r="F79">
+        <v>68.22199999999999</v>
+      </c>
+      <c r="G79">
+        <v>2.03</v>
+      </c>
+      <c r="H79">
+        <v>57.1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>5.68</v>
+      </c>
+      <c r="K79">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L79">
+        <v>1.36</v>
+      </c>
+      <c r="M79">
+        <v>16.2914136</v>
+      </c>
+      <c r="N79">
+        <v>-14.9314136</v>
+      </c>
+      <c r="O79">
+        <v>-3.583539264</v>
+      </c>
+      <c r="P79">
+        <v>-11.347874336</v>
+      </c>
+      <c r="Q79">
+        <v>-7.027874336000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3769738417735767</v>
+      </c>
+      <c r="T79">
+        <v>4.235966013545767</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02003509382390243</v>
+      </c>
+      <c r="W79">
+        <v>0.2340156195948521</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.08347955759959347</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2688960106959588</v>
+      </c>
+      <c r="C80">
+        <v>-37.99961588929703</v>
+      </c>
+      <c r="D80">
+        <v>29.07838411070297</v>
+      </c>
+      <c r="E80">
+        <v>37.608</v>
+      </c>
+      <c r="F80">
+        <v>69.108</v>
+      </c>
+      <c r="G80">
+        <v>2.03</v>
+      </c>
+      <c r="H80">
+        <v>57.1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>5.68</v>
+      </c>
+      <c r="K80">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L80">
+        <v>1.36</v>
+      </c>
+      <c r="M80">
+        <v>16.5029904</v>
+      </c>
+      <c r="N80">
+        <v>-15.1429904</v>
+      </c>
+      <c r="O80">
+        <v>-3.634317696000001</v>
+      </c>
+      <c r="P80">
+        <v>-11.508672704</v>
+      </c>
+      <c r="Q80">
+        <v>-7.188672704000003</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3923453800360119</v>
+      </c>
+      <c r="T80">
+        <v>4.428509923252392</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.01977823364667291</v>
+      </c>
+      <c r="W80">
+        <v>0.2340769578051745</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.08240930686113712</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2708960106959588</v>
+      </c>
+      <c r="C81">
+        <v>-39.13618791785976</v>
+      </c>
+      <c r="D81">
+        <v>28.82781208214023</v>
+      </c>
+      <c r="E81">
+        <v>38.494</v>
+      </c>
+      <c r="F81">
+        <v>69.994</v>
+      </c>
+      <c r="G81">
+        <v>2.03</v>
+      </c>
+      <c r="H81">
+        <v>57.1</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>5.68</v>
+      </c>
+      <c r="K81">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L81">
+        <v>1.36</v>
+      </c>
+      <c r="M81">
+        <v>16.7145672</v>
+      </c>
+      <c r="N81">
+        <v>-15.3545672</v>
+      </c>
+      <c r="O81">
+        <v>-3.685096128</v>
+      </c>
+      <c r="P81">
+        <v>-11.669471072</v>
+      </c>
+      <c r="Q81">
+        <v>-7.349471072000003</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4091808743234411</v>
+      </c>
+      <c r="T81">
+        <v>4.639391348169173</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.01952787625874034</v>
+      </c>
+      <c r="W81">
+        <v>0.2341367431494128</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.08136615107808476</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2728960106959588</v>
+      </c>
+      <c r="C82">
+        <v>-40.26847842060209</v>
+      </c>
+      <c r="D82">
+        <v>28.5815215793979</v>
+      </c>
+      <c r="E82">
+        <v>39.38</v>
+      </c>
+      <c r="F82">
+        <v>70.88</v>
+      </c>
+      <c r="G82">
+        <v>2.03</v>
+      </c>
+      <c r="H82">
+        <v>57.1</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>5.68</v>
+      </c>
+      <c r="K82">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L82">
+        <v>1.36</v>
+      </c>
+      <c r="M82">
+        <v>16.926144</v>
+      </c>
+      <c r="N82">
+        <v>-15.566144</v>
+      </c>
+      <c r="O82">
+        <v>-3.73587456</v>
+      </c>
+      <c r="P82">
+        <v>-11.83026944</v>
+      </c>
+      <c r="Q82">
+        <v>-7.510269440000003</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4276999180396131</v>
+      </c>
+      <c r="T82">
+        <v>4.871360915577631</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.01928377780550609</v>
+      </c>
+      <c r="W82">
+        <v>0.2341950338600452</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.08034907418960868</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2748960106959588</v>
+      </c>
+      <c r="C83">
+        <v>-41.39659620560953</v>
+      </c>
+      <c r="D83">
+        <v>28.33940379439047</v>
+      </c>
+      <c r="E83">
+        <v>40.26600000000001</v>
+      </c>
+      <c r="F83">
+        <v>71.76600000000001</v>
+      </c>
+      <c r="G83">
+        <v>2.03</v>
+      </c>
+      <c r="H83">
+        <v>57.1</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>5.68</v>
+      </c>
+      <c r="K83">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L83">
+        <v>1.36</v>
+      </c>
+      <c r="M83">
+        <v>17.1377208</v>
+      </c>
+      <c r="N83">
+        <v>-15.7777208</v>
+      </c>
+      <c r="O83">
+        <v>-3.786652992000001</v>
+      </c>
+      <c r="P83">
+        <v>-11.991067808</v>
+      </c>
+      <c r="Q83">
+        <v>-7.671067808000005</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4481683347785402</v>
+      </c>
+      <c r="T83">
+        <v>5.127748332186981</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.01904570647457391</v>
+      </c>
+      <c r="W83">
+        <v>0.2342518852938718</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.07935711031072457</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2768960106959588</v>
+      </c>
+      <c r="C84">
+        <v>-42.52064642502777</v>
+      </c>
+      <c r="D84">
+        <v>28.10135357497223</v>
+      </c>
+      <c r="E84">
+        <v>41.152</v>
+      </c>
+      <c r="F84">
+        <v>72.652</v>
+      </c>
+      <c r="G84">
+        <v>2.03</v>
+      </c>
+      <c r="H84">
+        <v>57.1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>5.68</v>
+      </c>
+      <c r="K84">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L84">
+        <v>1.36</v>
+      </c>
+      <c r="M84">
+        <v>17.3492976</v>
+      </c>
+      <c r="N84">
+        <v>-15.9892976</v>
+      </c>
+      <c r="O84">
+        <v>-3.837431424</v>
+      </c>
+      <c r="P84">
+        <v>-12.151866176</v>
+      </c>
+      <c r="Q84">
+        <v>-7.831866176000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4709110200440147</v>
+      </c>
+      <c r="T84">
+        <v>5.412623239530703</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.01881344176146935</v>
+      </c>
+      <c r="W84">
+        <v>0.2343073501073611</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.07838934067278891</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2788960106959587</v>
+      </c>
+      <c r="C85">
+        <v>-43.64073072733262</v>
+      </c>
+      <c r="D85">
+        <v>27.86726927266737</v>
+      </c>
+      <c r="E85">
+        <v>42.038</v>
+      </c>
+      <c r="F85">
+        <v>73.538</v>
+      </c>
+      <c r="G85">
+        <v>2.03</v>
+      </c>
+      <c r="H85">
+        <v>57.1</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>5.68</v>
+      </c>
+      <c r="K85">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L85">
+        <v>1.36</v>
+      </c>
+      <c r="M85">
+        <v>17.5608744</v>
+      </c>
+      <c r="N85">
+        <v>-16.2008744</v>
+      </c>
+      <c r="O85">
+        <v>-3.888209856</v>
+      </c>
+      <c r="P85">
+        <v>-12.312664544</v>
+      </c>
+      <c r="Q85">
+        <v>-7.992664544000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4963293153407214</v>
+      </c>
+      <c r="T85">
+        <v>5.731012841856038</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.0185867737884396</v>
+      </c>
+      <c r="W85">
+        <v>0.2343614784193206</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.07744489078516492</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2808960106959588</v>
+      </c>
+      <c r="C86">
+        <v>-44.75694740205235</v>
+      </c>
+      <c r="D86">
+        <v>27.63705259794764</v>
+      </c>
+      <c r="E86">
+        <v>42.92399999999999</v>
+      </c>
+      <c r="F86">
+        <v>74.42399999999999</v>
+      </c>
+      <c r="G86">
+        <v>2.03</v>
+      </c>
+      <c r="H86">
+        <v>57.1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>5.68</v>
+      </c>
+      <c r="K86">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L86">
+        <v>1.36</v>
+      </c>
+      <c r="M86">
+        <v>17.7724512</v>
+      </c>
+      <c r="N86">
+        <v>-16.4124512</v>
+      </c>
+      <c r="O86">
+        <v>-3.938988288</v>
+      </c>
+      <c r="P86">
+        <v>-12.473462912</v>
+      </c>
+      <c r="Q86">
+        <v>-8.153462912000002</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5249248975495164</v>
+      </c>
+      <c r="T86">
+        <v>6.089201144472038</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.01836550267191056</v>
+      </c>
+      <c r="W86">
+        <v>0.2344143179619478</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.07652292779962733</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2828960106959588</v>
+      </c>
+      <c r="C87">
+        <v>-45.86939151737523</v>
+      </c>
+      <c r="D87">
+        <v>27.41060848262475</v>
+      </c>
+      <c r="E87">
+        <v>43.80999999999999</v>
+      </c>
+      <c r="F87">
+        <v>75.30999999999999</v>
+      </c>
+      <c r="G87">
+        <v>2.03</v>
+      </c>
+      <c r="H87">
+        <v>57.1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>5.68</v>
+      </c>
+      <c r="K87">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L87">
+        <v>1.36</v>
+      </c>
+      <c r="M87">
+        <v>17.984028</v>
+      </c>
+      <c r="N87">
+        <v>-16.624028</v>
+      </c>
+      <c r="O87">
+        <v>-3.98976672</v>
+      </c>
+      <c r="P87">
+        <v>-12.63426128</v>
+      </c>
+      <c r="Q87">
+        <v>-8.31426128</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5573332240528175</v>
+      </c>
+      <c r="T87">
+        <v>6.49514788743684</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.01814943793459397</v>
+      </c>
+      <c r="W87">
+        <v>0.234465914221219</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.07562265806080815</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2848960106959587</v>
+      </c>
+      <c r="C88">
+        <v>-46.97815505104739</v>
+      </c>
+      <c r="D88">
+        <v>27.1878449489526</v>
+      </c>
+      <c r="E88">
+        <v>44.696</v>
+      </c>
+      <c r="F88">
+        <v>76.196</v>
+      </c>
+      <c r="G88">
+        <v>2.03</v>
+      </c>
+      <c r="H88">
+        <v>57.1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>5.68</v>
+      </c>
+      <c r="K88">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L88">
+        <v>1.36</v>
+      </c>
+      <c r="M88">
+        <v>18.1956048</v>
+      </c>
+      <c r="N88">
+        <v>-16.8356048</v>
+      </c>
+      <c r="O88">
+        <v>-4.040545152</v>
+      </c>
+      <c r="P88">
+        <v>-12.795059648</v>
+      </c>
+      <c r="Q88">
+        <v>-8.475059648000002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5943713114851614</v>
+      </c>
+      <c r="T88">
+        <v>6.959087022253757</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01793839795861031</v>
+      </c>
+      <c r="W88">
+        <v>0.2345163105674839</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.07474332482754298</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2868960106959587</v>
+      </c>
+      <c r="C89">
+        <v>-48.08332701493899</v>
+      </c>
+      <c r="D89">
+        <v>26.968672985061</v>
+      </c>
+      <c r="E89">
+        <v>45.58199999999999</v>
+      </c>
+      <c r="F89">
+        <v>77.08199999999999</v>
+      </c>
+      <c r="G89">
+        <v>2.03</v>
+      </c>
+      <c r="H89">
+        <v>57.1</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>5.68</v>
+      </c>
+      <c r="K89">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L89">
+        <v>1.36</v>
+      </c>
+      <c r="M89">
+        <v>18.4071816</v>
+      </c>
+      <c r="N89">
+        <v>-17.0471816</v>
+      </c>
+      <c r="O89">
+        <v>-4.091323584</v>
+      </c>
+      <c r="P89">
+        <v>-12.955858016</v>
+      </c>
+      <c r="Q89">
+        <v>-8.635858016</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6371075662147894</v>
+      </c>
+      <c r="T89">
+        <v>7.49440140858097</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01773220947632744</v>
+      </c>
+      <c r="W89">
+        <v>0.234565548377053</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.07388420615136426</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2888960106959588</v>
+      </c>
+      <c r="C90">
+        <v>-49.1849935736339</v>
+      </c>
+      <c r="D90">
+        <v>26.75300642636609</v>
+      </c>
+      <c r="E90">
+        <v>46.46799999999999</v>
+      </c>
+      <c r="F90">
+        <v>77.96799999999999</v>
+      </c>
+      <c r="G90">
+        <v>2.03</v>
+      </c>
+      <c r="H90">
+        <v>57.1</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>5.68</v>
+      </c>
+      <c r="K90">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L90">
+        <v>1.36</v>
+      </c>
+      <c r="M90">
+        <v>18.6187584</v>
+      </c>
+      <c r="N90">
+        <v>-17.2587584</v>
+      </c>
+      <c r="O90">
+        <v>-4.142102015999999</v>
+      </c>
+      <c r="P90">
+        <v>-13.116656384</v>
+      </c>
+      <c r="Q90">
+        <v>-8.796656383999998</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6869665300660219</v>
+      </c>
+      <c r="T90">
+        <v>8.118934859296052</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.01753070709591463</v>
+      </c>
+      <c r="W90">
+        <v>0.2346136671454956</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.07304461289964426</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2908960106959587</v>
+      </c>
+      <c r="C91">
+        <v>-50.28323815737411</v>
+      </c>
+      <c r="D91">
+        <v>26.54076184262588</v>
+      </c>
+      <c r="E91">
+        <v>47.354</v>
+      </c>
+      <c r="F91">
+        <v>78.854</v>
+      </c>
+      <c r="G91">
+        <v>2.03</v>
+      </c>
+      <c r="H91">
+        <v>57.1</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>5.68</v>
+      </c>
+      <c r="K91">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L91">
+        <v>1.36</v>
+      </c>
+      <c r="M91">
+        <v>18.8303352</v>
+      </c>
+      <c r="N91">
+        <v>-17.4703352</v>
+      </c>
+      <c r="O91">
+        <v>-4.192880448</v>
+      </c>
+      <c r="P91">
+        <v>-13.277454752</v>
+      </c>
+      <c r="Q91">
+        <v>-8.957454752</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7458907600720237</v>
+      </c>
+      <c r="T91">
+        <v>8.857019846504782</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.01733373285888188</v>
+      </c>
+      <c r="W91">
+        <v>0.234660704593299</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.07222388691200776</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2928960106959587</v>
+      </c>
+      <c r="C92">
+        <v>-51.37814156967036</v>
+      </c>
+      <c r="D92">
+        <v>26.33185843032963</v>
+      </c>
+      <c r="E92">
+        <v>48.23999999999999</v>
+      </c>
+      <c r="F92">
+        <v>79.73999999999999</v>
+      </c>
+      <c r="G92">
+        <v>2.03</v>
+      </c>
+      <c r="H92">
+        <v>57.1</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>5.68</v>
+      </c>
+      <c r="K92">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L92">
+        <v>1.36</v>
+      </c>
+      <c r="M92">
+        <v>19.041912</v>
+      </c>
+      <c r="N92">
+        <v>-17.681912</v>
+      </c>
+      <c r="O92">
+        <v>-4.24365888</v>
+      </c>
+      <c r="P92">
+        <v>-13.43825312</v>
+      </c>
+      <c r="Q92">
+        <v>-9.118253120000002</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8165998360792261</v>
+      </c>
+      <c r="T92">
+        <v>9.742721831155261</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.01714113582711652</v>
+      </c>
+      <c r="W92">
+        <v>0.2347066967644846</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.07142139927965219</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2948960106959587</v>
+      </c>
+      <c r="C93">
+        <v>-52.46978208987035</v>
+      </c>
+      <c r="D93">
+        <v>26.12621791012964</v>
+      </c>
+      <c r="E93">
+        <v>49.12599999999999</v>
+      </c>
+      <c r="F93">
+        <v>80.62599999999999</v>
+      </c>
+      <c r="G93">
+        <v>2.03</v>
+      </c>
+      <c r="H93">
+        <v>57.1</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>5.68</v>
+      </c>
+      <c r="K93">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L93">
+        <v>1.36</v>
+      </c>
+      <c r="M93">
+        <v>19.2534888</v>
+      </c>
+      <c r="N93">
+        <v>-17.8934888</v>
+      </c>
+      <c r="O93">
+        <v>-4.294437311999999</v>
+      </c>
+      <c r="P93">
+        <v>-13.599051488</v>
+      </c>
+      <c r="Q93">
+        <v>-9.279051488</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9030220400880293</v>
+      </c>
+      <c r="T93">
+        <v>10.8252464790614</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01695277169714821</v>
+      </c>
+      <c r="W93">
+        <v>0.234751678118721</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.07063654873811753</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2968960106959588</v>
+      </c>
+      <c r="C94">
+        <v>-53.55823557095812</v>
+      </c>
+      <c r="D94">
+        <v>25.92376442904188</v>
+      </c>
+      <c r="E94">
+        <v>50.012</v>
+      </c>
+      <c r="F94">
+        <v>81.512</v>
+      </c>
+      <c r="G94">
+        <v>2.03</v>
+      </c>
+      <c r="H94">
+        <v>57.1</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>5.68</v>
+      </c>
+      <c r="K94">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L94">
+        <v>1.36</v>
+      </c>
+      <c r="M94">
+        <v>19.4650656</v>
+      </c>
+      <c r="N94">
+        <v>-18.1050656</v>
+      </c>
+      <c r="O94">
+        <v>-4.345215744000001</v>
+      </c>
+      <c r="P94">
+        <v>-13.759849856</v>
+      </c>
+      <c r="Q94">
+        <v>-9.439849856000002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.011049795099033</v>
+      </c>
+      <c r="T94">
+        <v>12.17840228894408</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01676850243957051</v>
+      </c>
+      <c r="W94">
+        <v>0.2347956816174306</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.06986876016487709</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2988960106959587</v>
+      </c>
+      <c r="C95">
+        <v>-54.64357553284123</v>
+      </c>
+      <c r="D95">
+        <v>25.72442446715877</v>
+      </c>
+      <c r="E95">
+        <v>50.898</v>
+      </c>
+      <c r="F95">
+        <v>82.398</v>
+      </c>
+      <c r="G95">
+        <v>2.03</v>
+      </c>
+      <c r="H95">
+        <v>57.1</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>5.68</v>
+      </c>
+      <c r="K95">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L95">
+        <v>1.36</v>
+      </c>
+      <c r="M95">
+        <v>19.6766424</v>
+      </c>
+      <c r="N95">
+        <v>-18.3166424</v>
+      </c>
+      <c r="O95">
+        <v>-4.395994175999999</v>
+      </c>
+      <c r="P95">
+        <v>-13.920648224</v>
+      </c>
+      <c r="Q95">
+        <v>-9.600648224</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.149942622970324</v>
+      </c>
+      <c r="T95">
+        <v>13.91817404450753</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01658819596172567</v>
+      </c>
+      <c r="W95">
+        <v>0.2348387388043399</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.06911748317385691</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3008960106959587</v>
+      </c>
+      <c r="C96">
+        <v>-55.725873251367</v>
+      </c>
+      <c r="D96">
+        <v>25.52812674863301</v>
+      </c>
+      <c r="E96">
+        <v>51.78400000000001</v>
+      </c>
+      <c r="F96">
+        <v>83.28400000000001</v>
+      </c>
+      <c r="G96">
+        <v>2.03</v>
+      </c>
+      <c r="H96">
+        <v>57.1</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>5.68</v>
+      </c>
+      <c r="K96">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L96">
+        <v>1.36</v>
+      </c>
+      <c r="M96">
+        <v>19.8882192</v>
+      </c>
+      <c r="N96">
+        <v>-18.5282192</v>
+      </c>
+      <c r="O96">
+        <v>-4.446772608000001</v>
+      </c>
+      <c r="P96">
+        <v>-14.081446592</v>
+      </c>
+      <c r="Q96">
+        <v>-9.761446592000002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.335133060132045</v>
+      </c>
+      <c r="T96">
+        <v>16.23786971859212</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01641172579192007</v>
+      </c>
+      <c r="W96">
+        <v>0.2348808798808895</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.0683821907996669</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3028960106959588</v>
+      </c>
+      <c r="C97">
+        <v>-56.8051978432937</v>
+      </c>
+      <c r="D97">
+        <v>25.33480215670631</v>
+      </c>
+      <c r="E97">
+        <v>52.67</v>
+      </c>
+      <c r="F97">
+        <v>84.17</v>
+      </c>
+      <c r="G97">
+        <v>2.03</v>
+      </c>
+      <c r="H97">
+        <v>57.1</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>5.68</v>
+      </c>
+      <c r="K97">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L97">
+        <v>1.36</v>
+      </c>
+      <c r="M97">
+        <v>20.099796</v>
+      </c>
+      <c r="N97">
+        <v>-18.739796</v>
+      </c>
+      <c r="O97">
+        <v>-4.49755104</v>
+      </c>
+      <c r="P97">
+        <v>-14.24224496</v>
+      </c>
+      <c r="Q97">
+        <v>-9.92224496</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.594399672158454</v>
+      </c>
+      <c r="T97">
+        <v>19.48544366231055</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01623897078358407</v>
+      </c>
+      <c r="W97">
+        <v>0.2349221337768801</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.0676623782649336</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3048960106959587</v>
+      </c>
+      <c r="C98">
+        <v>-57.88161634743018</v>
+      </c>
+      <c r="D98">
+        <v>25.14438365256981</v>
+      </c>
+      <c r="E98">
+        <v>53.556</v>
+      </c>
+      <c r="F98">
+        <v>85.056</v>
+      </c>
+      <c r="G98">
+        <v>2.03</v>
+      </c>
+      <c r="H98">
+        <v>57.1</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>5.68</v>
+      </c>
+      <c r="K98">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L98">
+        <v>1.36</v>
+      </c>
+      <c r="M98">
+        <v>20.3113728</v>
+      </c>
+      <c r="N98">
+        <v>-18.9513728</v>
+      </c>
+      <c r="O98">
+        <v>-4.548329472</v>
+      </c>
+      <c r="P98">
+        <v>-14.403043328</v>
+      </c>
+      <c r="Q98">
+        <v>-10.083043328</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.983299590198064</v>
+      </c>
+      <c r="T98">
+        <v>24.35680457788813</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01606981483792174</v>
+      </c>
+      <c r="W98">
+        <v>0.2349625282167043</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.06695756182467383</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3068960106959588</v>
+      </c>
+      <c r="C99">
+        <v>-58.95519380214348</v>
+      </c>
+      <c r="D99">
+        <v>24.9568061978565</v>
+      </c>
+      <c r="E99">
+        <v>54.44199999999999</v>
+      </c>
+      <c r="F99">
+        <v>85.94199999999999</v>
+      </c>
+      <c r="G99">
+        <v>2.03</v>
+      </c>
+      <c r="H99">
+        <v>57.1</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>5.68</v>
+      </c>
+      <c r="K99">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L99">
+        <v>1.36</v>
+      </c>
+      <c r="M99">
+        <v>20.5229496</v>
+      </c>
+      <c r="N99">
+        <v>-19.1629496</v>
+      </c>
+      <c r="O99">
+        <v>-4.599107904</v>
+      </c>
+      <c r="P99">
+        <v>-14.563841696</v>
+      </c>
+      <c r="Q99">
+        <v>-10.243841696</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.631466120264086</v>
+      </c>
+      <c r="T99">
+        <v>32.47573943718418</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01590414664371636</v>
+      </c>
+      <c r="W99">
+        <v>0.2350020897814805</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.06626727768215146</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3088960106959587</v>
+      </c>
+      <c r="C100">
+        <v>-60.02599331942291</v>
+      </c>
+      <c r="D100">
+        <v>24.77200668057708</v>
+      </c>
+      <c r="E100">
+        <v>55.32799999999999</v>
+      </c>
+      <c r="F100">
+        <v>86.82799999999999</v>
+      </c>
+      <c r="G100">
+        <v>2.03</v>
+      </c>
+      <c r="H100">
+        <v>57.1</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>5.68</v>
+      </c>
+      <c r="K100">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L100">
+        <v>1.36</v>
+      </c>
+      <c r="M100">
+        <v>20.7345264</v>
+      </c>
+      <c r="N100">
+        <v>-19.3745264</v>
+      </c>
+      <c r="O100">
+        <v>-4.649886336</v>
+      </c>
+      <c r="P100">
+        <v>-14.724640064</v>
+      </c>
+      <c r="Q100">
+        <v>-10.404640064</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.927799180396128</v>
+      </c>
+      <c r="T100">
+        <v>48.71360915577626</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01574185943306619</v>
+      </c>
+      <c r="W100">
+        <v>0.2350408439673838</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.06559108097110911</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3108960106959587</v>
+      </c>
+      <c r="C101">
+        <v>-61.09407615567778</v>
+      </c>
+      <c r="D101">
+        <v>24.58992384432222</v>
+      </c>
+      <c r="E101">
+        <v>56.214</v>
+      </c>
+      <c r="F101">
+        <v>87.714</v>
+      </c>
+      <c r="G101">
+        <v>2.03</v>
+      </c>
+      <c r="H101">
+        <v>57.1</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>5.68</v>
+      </c>
+      <c r="K101">
+        <v>4.319999999999999</v>
+      </c>
+      <c r="L101">
+        <v>1.36</v>
+      </c>
+      <c r="M101">
+        <v>20.9461032</v>
+      </c>
+      <c r="N101">
+        <v>-19.5861032</v>
+      </c>
+      <c r="O101">
+        <v>-4.700664768</v>
+      </c>
+      <c r="P101">
+        <v>-14.885438432</v>
+      </c>
+      <c r="Q101">
+        <v>-10.565438432</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.816798360792255</v>
+      </c>
+      <c r="T101">
+        <v>97.42721831155252</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01558285075192411</v>
+      </c>
+      <c r="W101">
+        <v>0.2350788152404405</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.0649285447996838</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malaysia/malaysia_recreation.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_recreation.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09899509739688325</v>
+        <v>0.09879170916313074</v>
       </c>
       <c r="C2">
-        <v>60.18898678883982</v>
+        <v>59.75845672397393</v>
       </c>
       <c r="D2">
-        <v>55.87898678883982</v>
+        <v>56.09345672397393</v>
       </c>
       <c r="E2">
-        <v>-32.7</v>
+        <v>-32.055</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.645</v>
       </c>
       <c r="G2">
         <v>4.31</v>
@@ -1445,28 +1445,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0324435</v>
       </c>
       <c r="N2">
-        <v>7.290000000000001</v>
+        <v>7.257556500000001</v>
       </c>
       <c r="O2">
-        <v>1.7496</v>
+        <v>1.74181356</v>
       </c>
       <c r="P2">
-        <v>5.540400000000001</v>
+        <v>5.515742940000001</v>
       </c>
       <c r="Q2">
-        <v>10.6004</v>
+        <v>10.57574294</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09899509739688325</v>
+        <v>0.09940346380114216</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378592</v>
+        <v>0.903831407581665</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>224.6983216977207</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09879170916313074</v>
+        <v>0.09858832092937822</v>
       </c>
       <c r="C3">
-        <v>59.75845672397393</v>
+        <v>59.32957932244463</v>
       </c>
       <c r="D3">
-        <v>56.09345672397393</v>
+        <v>56.30957932244463</v>
       </c>
       <c r="E3">
-        <v>-32.055</v>
+        <v>-31.41</v>
       </c>
       <c r="F3">
-        <v>0.645</v>
+        <v>1.29</v>
       </c>
       <c r="G3">
         <v>4.31</v>
@@ -1527,28 +1527,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M3">
-        <v>0.0324435</v>
+        <v>0.064887</v>
       </c>
       <c r="N3">
-        <v>7.257556500000001</v>
+        <v>7.225113000000001</v>
       </c>
       <c r="O3">
-        <v>1.74181356</v>
+        <v>1.73402712</v>
       </c>
       <c r="P3">
-        <v>5.515742940000001</v>
+        <v>5.491085880000001</v>
       </c>
       <c r="Q3">
-        <v>10.57574294</v>
+        <v>10.55108588</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09940346380114216</v>
+        <v>0.09982016421365125</v>
       </c>
       <c r="T3">
-        <v>0.903831407581665</v>
+        <v>0.9108575751773852</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>224.6983216977207</v>
+        <v>112.3491608488604</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09858832092937822</v>
+        <v>0.0983849326956257</v>
       </c>
       <c r="C4">
-        <v>59.32957932244463</v>
+        <v>58.90237376078746</v>
       </c>
       <c r="D4">
-        <v>56.30957932244463</v>
+        <v>56.52737376078746</v>
       </c>
       <c r="E4">
-        <v>-31.41</v>
+        <v>-30.765</v>
       </c>
       <c r="F4">
-        <v>1.29</v>
+        <v>1.935</v>
       </c>
       <c r="G4">
         <v>4.31</v>
@@ -1609,28 +1609,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M4">
-        <v>0.064887</v>
+        <v>0.09733049999999999</v>
       </c>
       <c r="N4">
-        <v>7.225113000000001</v>
+        <v>7.192669500000001</v>
       </c>
       <c r="O4">
-        <v>1.73402712</v>
+        <v>1.72624068</v>
       </c>
       <c r="P4">
-        <v>5.491085880000001</v>
+        <v>5.466428820000001</v>
       </c>
       <c r="Q4">
-        <v>10.55108588</v>
+        <v>10.52642882</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09982016421365125</v>
+        <v>0.100245456387243</v>
       </c>
       <c r="T4">
-        <v>0.9108575751773852</v>
+        <v>0.9180286122080689</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>112.3491608488604</v>
+        <v>74.8994405659069</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0983849326956257</v>
+        <v>0.09818154446187317</v>
       </c>
       <c r="C5">
-        <v>58.90237376078746</v>
+        <v>58.47685951337431</v>
       </c>
       <c r="D5">
-        <v>56.52737376078746</v>
+        <v>56.7468595133743</v>
       </c>
       <c r="E5">
-        <v>-30.765</v>
+        <v>-30.12</v>
       </c>
       <c r="F5">
-        <v>1.935</v>
+        <v>2.58</v>
       </c>
       <c r="G5">
         <v>4.31</v>
@@ -1691,28 +1691,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M5">
-        <v>0.09733049999999999</v>
+        <v>0.129774</v>
       </c>
       <c r="N5">
-        <v>7.192669500000001</v>
+        <v>7.160226000000001</v>
       </c>
       <c r="O5">
-        <v>1.72624068</v>
+        <v>1.71845424</v>
       </c>
       <c r="P5">
-        <v>5.466428820000001</v>
+        <v>5.441771760000001</v>
       </c>
       <c r="Q5">
-        <v>10.52642882</v>
+        <v>10.50177176</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.100245456387243</v>
+        <v>0.1006796088144512</v>
       </c>
       <c r="T5">
-        <v>0.9180286122080689</v>
+        <v>0.9253490458435581</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>74.8994405659069</v>
+        <v>56.17458042443017</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09818154446187317</v>
+        <v>0.09797815622812066</v>
       </c>
       <c r="C6">
-        <v>58.47685951337431</v>
+        <v>58.05305635821811</v>
       </c>
       <c r="D6">
-        <v>56.7468595133743</v>
+        <v>56.96805635821811</v>
       </c>
       <c r="E6">
-        <v>-30.12</v>
+        <v>-29.475</v>
       </c>
       <c r="F6">
-        <v>2.58</v>
+        <v>3.225</v>
       </c>
       <c r="G6">
         <v>4.31</v>
@@ -1773,28 +1773,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M6">
-        <v>0.129774</v>
+        <v>0.1622175</v>
       </c>
       <c r="N6">
-        <v>7.160226000000001</v>
+        <v>7.127782500000001</v>
       </c>
       <c r="O6">
-        <v>1.71845424</v>
+        <v>1.7106678</v>
       </c>
       <c r="P6">
-        <v>5.441771760000001</v>
+        <v>5.417114700000001</v>
       </c>
       <c r="Q6">
-        <v>10.50177176</v>
+        <v>10.4771147</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1006796088144512</v>
+        <v>0.1011229012927586</v>
       </c>
       <c r="T6">
-        <v>0.9253490458435581</v>
+        <v>0.9328235938713737</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.17458042443017</v>
+        <v>44.93966433954414</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09797815622812066</v>
+        <v>0.09777476799436814</v>
       </c>
       <c r="C7">
-        <v>58.05305635821811</v>
+        <v>57.630984382914</v>
       </c>
       <c r="D7">
-        <v>56.96805635821811</v>
+        <v>57.190984382914</v>
       </c>
       <c r="E7">
-        <v>-29.475</v>
+        <v>-28.83</v>
       </c>
       <c r="F7">
-        <v>3.225</v>
+        <v>3.87</v>
       </c>
       <c r="G7">
         <v>4.31</v>
@@ -1855,28 +1855,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M7">
-        <v>0.1622175</v>
+        <v>0.194661</v>
       </c>
       <c r="N7">
-        <v>7.127782500000001</v>
+        <v>7.095339000000001</v>
       </c>
       <c r="O7">
-        <v>1.7106678</v>
+        <v>1.70288136</v>
       </c>
       <c r="P7">
-        <v>5.417114700000001</v>
+        <v>5.392457640000001</v>
       </c>
       <c r="Q7">
-        <v>10.4771147</v>
+        <v>10.45245764</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1011229012927586</v>
+        <v>0.1015756255259236</v>
       </c>
       <c r="T7">
-        <v>0.9328235938713737</v>
+        <v>0.9404571748359511</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.93966433954414</v>
+        <v>37.44972028295345</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09777476799436814</v>
+        <v>0.09757137976061563</v>
       </c>
       <c r="C8">
-        <v>57.630984382914</v>
+        <v>57.21066399072034</v>
       </c>
       <c r="D8">
-        <v>57.190984382914</v>
+        <v>57.41566399072034</v>
       </c>
       <c r="E8">
-        <v>-28.83</v>
+        <v>-28.185</v>
       </c>
       <c r="F8">
-        <v>3.87</v>
+        <v>4.515</v>
       </c>
       <c r="G8">
         <v>4.31</v>
@@ -1937,28 +1937,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M8">
-        <v>0.194661</v>
+        <v>0.2271045</v>
       </c>
       <c r="N8">
-        <v>7.095339000000001</v>
+        <v>7.062895500000001</v>
       </c>
       <c r="O8">
-        <v>1.70288136</v>
+        <v>1.69509492</v>
       </c>
       <c r="P8">
-        <v>5.392457640000001</v>
+        <v>5.367800580000001</v>
       </c>
       <c r="Q8">
-        <v>10.45245764</v>
+        <v>10.42780058</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1015756255259236</v>
+        <v>0.1020380857641028</v>
       </c>
       <c r="T8">
-        <v>0.9404571748359511</v>
+        <v>0.948254918832025</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.44972028295345</v>
+        <v>32.09976024253153</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09757137976061561</v>
+        <v>0.0973679915268631</v>
       </c>
       <c r="C9">
-        <v>57.21066399072036</v>
+        <v>56.79211590678379</v>
       </c>
       <c r="D9">
-        <v>57.41566399072036</v>
+        <v>57.64211590678379</v>
       </c>
       <c r="E9">
-        <v>-28.185</v>
+        <v>-27.54</v>
       </c>
       <c r="F9">
-        <v>4.515000000000001</v>
+        <v>5.16</v>
       </c>
       <c r="G9">
         <v>4.31</v>
@@ -2019,28 +2019,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M9">
-        <v>0.2271045</v>
+        <v>0.259548</v>
       </c>
       <c r="N9">
-        <v>7.062895500000001</v>
+        <v>7.030452000000001</v>
       </c>
       <c r="O9">
-        <v>1.69509492</v>
+        <v>1.68730848</v>
       </c>
       <c r="P9">
-        <v>5.367800580000001</v>
+        <v>5.343143520000001</v>
       </c>
       <c r="Q9">
-        <v>10.42780058</v>
+        <v>10.40314352</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1020380857641028</v>
+        <v>0.1025105994857207</v>
       </c>
       <c r="T9">
-        <v>0.948254918832025</v>
+        <v>0.9562221790019264</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.09976024253152</v>
+        <v>28.08729021221509</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0973679915268631</v>
+        <v>0.09716460329311058</v>
       </c>
       <c r="C10">
-        <v>56.79211590678379</v>
+        <v>56.37536118451206</v>
       </c>
       <c r="D10">
-        <v>57.64211590678379</v>
+        <v>57.87036118451206</v>
       </c>
       <c r="E10">
-        <v>-27.54</v>
+        <v>-26.895</v>
       </c>
       <c r="F10">
-        <v>5.16</v>
+        <v>5.805</v>
       </c>
       <c r="G10">
         <v>4.31</v>
@@ -2101,28 +2101,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M10">
-        <v>0.259548</v>
+        <v>0.2919915</v>
       </c>
       <c r="N10">
-        <v>7.030452000000001</v>
+        <v>6.998008500000001</v>
       </c>
       <c r="O10">
-        <v>1.68730848</v>
+        <v>1.67952204</v>
       </c>
       <c r="P10">
-        <v>5.343143520000001</v>
+        <v>5.318486460000001</v>
       </c>
       <c r="Q10">
-        <v>10.40314352</v>
+        <v>10.37848646</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1025105994857207</v>
+        <v>0.1029934981242973</v>
       </c>
       <c r="T10">
-        <v>0.9562221790019264</v>
+        <v>0.9643645437909466</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.08729021221509</v>
+        <v>24.96648018863564</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09716460329311058</v>
+        <v>0.09696121505935806</v>
       </c>
       <c r="C11">
-        <v>56.37536118451206</v>
+        <v>55.96042121209902</v>
       </c>
       <c r="D11">
-        <v>57.87036118451206</v>
+        <v>58.10042121209901</v>
       </c>
       <c r="E11">
-        <v>-26.895</v>
+        <v>-26.25</v>
       </c>
       <c r="F11">
-        <v>5.805</v>
+        <v>6.449999999999999</v>
       </c>
       <c r="G11">
         <v>4.31</v>
@@ -2183,28 +2183,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M11">
-        <v>0.2919915</v>
+        <v>0.324435</v>
       </c>
       <c r="N11">
-        <v>6.998008500000001</v>
+        <v>6.965565000000001</v>
       </c>
       <c r="O11">
-        <v>1.67952204</v>
+        <v>1.6717356</v>
       </c>
       <c r="P11">
-        <v>5.318486460000001</v>
+        <v>5.293829400000001</v>
       </c>
       <c r="Q11">
-        <v>10.37848646</v>
+        <v>10.3538294</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1029934981242973</v>
+        <v>0.1034871278437312</v>
       </c>
       <c r="T11">
-        <v>0.9643645437909466</v>
+        <v>0.972687850019723</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.96648018863564</v>
+        <v>22.46983216977207</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09696121505935806</v>
+        <v>0.09675782682560555</v>
       </c>
       <c r="C12">
-        <v>55.96042121209901</v>
+        <v>55.54731771920572</v>
       </c>
       <c r="D12">
-        <v>58.10042121209901</v>
+        <v>58.33231771920572</v>
       </c>
       <c r="E12">
-        <v>-26.25</v>
+        <v>-25.605</v>
       </c>
       <c r="F12">
-        <v>6.45</v>
+        <v>7.095</v>
       </c>
       <c r="G12">
         <v>4.31</v>
@@ -2265,28 +2265,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M12">
-        <v>0.324435</v>
+        <v>0.3568785</v>
       </c>
       <c r="N12">
-        <v>6.965565000000001</v>
+        <v>6.933121500000001</v>
       </c>
       <c r="O12">
-        <v>1.6717356</v>
+        <v>1.66394916</v>
       </c>
       <c r="P12">
-        <v>5.293829400000001</v>
+        <v>5.269172340000001</v>
       </c>
       <c r="Q12">
-        <v>10.3538294</v>
+        <v>10.32917234</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1034871278437312</v>
+        <v>0.1039918503658489</v>
       </c>
       <c r="T12">
-        <v>0.972687850019723</v>
+        <v>0.9811981968379099</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.46983216977207</v>
+        <v>20.42712015433824</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09675782682560555</v>
+        <v>0.09655443859185302</v>
       </c>
       <c r="C13">
-        <v>55.54731771920572</v>
+        <v>55.13607278380227</v>
       </c>
       <c r="D13">
-        <v>58.33231771920572</v>
+        <v>58.56607278380227</v>
       </c>
       <c r="E13">
-        <v>-25.605</v>
+        <v>-24.96</v>
       </c>
       <c r="F13">
-        <v>7.095</v>
+        <v>7.739999999999999</v>
       </c>
       <c r="G13">
         <v>4.31</v>
@@ -2347,28 +2347,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M13">
-        <v>0.3568785</v>
+        <v>0.3893219999999999</v>
       </c>
       <c r="N13">
-        <v>6.933121500000001</v>
+        <v>6.900678000000001</v>
       </c>
       <c r="O13">
-        <v>1.66394916</v>
+        <v>1.65616272</v>
       </c>
       <c r="P13">
-        <v>5.269172340000001</v>
+        <v>5.244515280000001</v>
       </c>
       <c r="Q13">
-        <v>10.32917234</v>
+        <v>10.30451528</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1039918503658489</v>
+        <v>0.1045080438543784</v>
       </c>
       <c r="T13">
-        <v>0.9811981968379099</v>
+        <v>0.9899019606292373</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.42712015433824</v>
+        <v>18.72486014147673</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09655443859185302</v>
+        <v>0.09635105035810049</v>
       </c>
       <c r="C14">
-        <v>55.13607278380227</v>
+        <v>54.72670883917478</v>
       </c>
       <c r="D14">
-        <v>58.56607278380227</v>
+        <v>58.80170883917477</v>
       </c>
       <c r="E14">
-        <v>-24.96</v>
+        <v>-24.315</v>
       </c>
       <c r="F14">
-        <v>7.739999999999999</v>
+        <v>8.385</v>
       </c>
       <c r="G14">
         <v>4.31</v>
@@ -2429,28 +2429,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M14">
-        <v>0.3893219999999999</v>
+        <v>0.4217655</v>
       </c>
       <c r="N14">
-        <v>6.900678000000001</v>
+        <v>6.868234500000001</v>
       </c>
       <c r="O14">
-        <v>1.65616272</v>
+        <v>1.64837628</v>
       </c>
       <c r="P14">
-        <v>5.244515280000001</v>
+        <v>5.219858220000001</v>
       </c>
       <c r="Q14">
-        <v>10.30451528</v>
+        <v>10.27985822</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1045080438543784</v>
+        <v>0.1050361038598856</v>
       </c>
       <c r="T14">
-        <v>0.9899019606292373</v>
+        <v>0.9988058109445035</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.72486014147673</v>
+        <v>17.28448628444005</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09635105035810049</v>
+        <v>0.09614766212434797</v>
       </c>
       <c r="C15">
-        <v>54.72670883917478</v>
+        <v>54.31924868110213</v>
       </c>
       <c r="D15">
-        <v>58.80170883917477</v>
+        <v>59.03924868110213</v>
       </c>
       <c r="E15">
-        <v>-24.315</v>
+        <v>-23.67</v>
       </c>
       <c r="F15">
-        <v>8.385</v>
+        <v>9.030000000000001</v>
       </c>
       <c r="G15">
         <v>4.31</v>
@@ -2511,28 +2511,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M15">
-        <v>0.4217655</v>
+        <v>0.454209</v>
       </c>
       <c r="N15">
-        <v>6.868234500000001</v>
+        <v>6.835791000000001</v>
       </c>
       <c r="O15">
-        <v>1.64837628</v>
+        <v>1.64058984</v>
       </c>
       <c r="P15">
-        <v>5.219858220000001</v>
+        <v>5.195201160000001</v>
       </c>
       <c r="Q15">
-        <v>10.27985822</v>
+        <v>10.25520116</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1050361038598856</v>
+        <v>0.1055764443306372</v>
       </c>
       <c r="T15">
-        <v>0.9988058109445035</v>
+        <v>1.007916727546171</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.28448628444005</v>
+        <v>16.04988012126577</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09614766212434797</v>
+        <v>0.09594427389059547</v>
       </c>
       <c r="C16">
-        <v>54.31924868110213</v>
+        <v>53.91371547520754</v>
       </c>
       <c r="D16">
-        <v>59.03924868110213</v>
+        <v>59.27871547520753</v>
       </c>
       <c r="E16">
-        <v>-23.67</v>
+        <v>-23.025</v>
       </c>
       <c r="F16">
-        <v>9.030000000000001</v>
+        <v>9.675000000000001</v>
       </c>
       <c r="G16">
         <v>4.31</v>
@@ -2593,28 +2593,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M16">
-        <v>0.454209</v>
+        <v>0.4866525</v>
       </c>
       <c r="N16">
-        <v>6.835791000000001</v>
+        <v>6.803347500000001</v>
       </c>
       <c r="O16">
-        <v>1.64058984</v>
+        <v>1.6328034</v>
       </c>
       <c r="P16">
-        <v>5.195201160000001</v>
+        <v>5.170544100000001</v>
       </c>
       <c r="Q16">
-        <v>10.25520116</v>
+        <v>10.2305441</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1055764443306372</v>
+        <v>0.1061294986948182</v>
       </c>
       <c r="T16">
-        <v>1.007916727546171</v>
+        <v>1.017242018656114</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.04988012126577</v>
+        <v>14.97988811318138</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09594427389059546</v>
+        <v>0.09574088565684293</v>
       </c>
       <c r="C17">
-        <v>53.91371547520755</v>
+        <v>53.51013276448963</v>
       </c>
       <c r="D17">
-        <v>59.27871547520755</v>
+        <v>59.52013276448962</v>
       </c>
       <c r="E17">
-        <v>-23.02500000000001</v>
+        <v>-22.38</v>
       </c>
       <c r="F17">
-        <v>9.674999999999999</v>
+        <v>10.32</v>
       </c>
       <c r="G17">
         <v>4.31</v>
@@ -2675,28 +2675,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M17">
-        <v>0.4866524999999999</v>
+        <v>0.519096</v>
       </c>
       <c r="N17">
-        <v>6.803347500000001</v>
+        <v>6.770904000000001</v>
       </c>
       <c r="O17">
-        <v>1.6328034</v>
+        <v>1.62501696</v>
       </c>
       <c r="P17">
-        <v>5.170544100000001</v>
+        <v>5.145887040000001</v>
       </c>
       <c r="Q17">
-        <v>10.2305441</v>
+        <v>10.20588704</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1061294986948182</v>
+        <v>0.1066957210200511</v>
       </c>
       <c r="T17">
-        <v>1.017242018656113</v>
+        <v>1.026789340506769</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.97988811318138</v>
+        <v>14.04364510610754</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09574088565684293</v>
+        <v>0.09553749742309044</v>
       </c>
       <c r="C18">
-        <v>53.51013276448963</v>
+        <v>53.10852447703813</v>
       </c>
       <c r="D18">
-        <v>59.52013276448962</v>
+        <v>59.76352447703814</v>
       </c>
       <c r="E18">
-        <v>-22.38</v>
+        <v>-21.735</v>
       </c>
       <c r="F18">
-        <v>10.32</v>
+        <v>10.965</v>
       </c>
       <c r="G18">
         <v>4.31</v>
@@ -2757,28 +2757,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M18">
-        <v>0.519096</v>
+        <v>0.5515395000000001</v>
       </c>
       <c r="N18">
-        <v>6.770904000000001</v>
+        <v>6.7384605</v>
       </c>
       <c r="O18">
-        <v>1.62501696</v>
+        <v>1.61723052</v>
       </c>
       <c r="P18">
-        <v>5.145887040000001</v>
+        <v>5.121229980000001</v>
       </c>
       <c r="Q18">
-        <v>10.20588704</v>
+        <v>10.18122998</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1066957210200511</v>
+        <v>0.1072755872567355</v>
       </c>
       <c r="T18">
-        <v>1.026789340506769</v>
+        <v>1.036566718305632</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.04364510610754</v>
+        <v>13.21754833516004</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09553749742309044</v>
+        <v>0.0955393091893379</v>
       </c>
       <c r="C19">
-        <v>53.10852447703813</v>
+        <v>52.4613475763485</v>
       </c>
       <c r="D19">
-        <v>59.76352447703814</v>
+        <v>59.7613475763485</v>
       </c>
       <c r="E19">
-        <v>-21.735</v>
+        <v>-21.09</v>
       </c>
       <c r="F19">
-        <v>10.965</v>
+        <v>11.61</v>
       </c>
       <c r="G19">
         <v>4.31</v>
@@ -2839,45 +2839,45 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M19">
-        <v>0.5515395000000001</v>
+        <v>0.6013980000000001</v>
       </c>
       <c r="N19">
-        <v>6.7384605</v>
+        <v>6.688602000000001</v>
       </c>
       <c r="O19">
-        <v>1.61723052</v>
+        <v>1.60526448</v>
       </c>
       <c r="P19">
-        <v>5.121229980000001</v>
+        <v>5.083337520000001</v>
       </c>
       <c r="Q19">
-        <v>10.18122998</v>
+        <v>10.14333752</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1072755872567355</v>
+        <v>0.1078695965723633</v>
       </c>
       <c r="T19">
-        <v>1.036566718305632</v>
+        <v>1.046582568733736</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.21754833516004</v>
+        <v>12.12175630780282</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0955393091893379</v>
+        <v>0.09534732095558539</v>
       </c>
       <c r="C20">
-        <v>52.4613475763485</v>
+        <v>52.0479135893351</v>
       </c>
       <c r="D20">
-        <v>59.7613475763485</v>
+        <v>59.9929135893351</v>
       </c>
       <c r="E20">
-        <v>-21.09</v>
+        <v>-20.445</v>
       </c>
       <c r="F20">
-        <v>11.61</v>
+        <v>12.255</v>
       </c>
       <c r="G20">
         <v>4.31</v>
@@ -2921,28 +2921,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M20">
-        <v>0.601398</v>
+        <v>0.6348090000000001</v>
       </c>
       <c r="N20">
-        <v>6.688602000000001</v>
+        <v>6.655191000000001</v>
       </c>
       <c r="O20">
-        <v>1.60526448</v>
+        <v>1.59724584</v>
       </c>
       <c r="P20">
-        <v>5.083337520000001</v>
+        <v>5.057945160000001</v>
       </c>
       <c r="Q20">
-        <v>10.14333752</v>
+        <v>10.11794516</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1078695965723633</v>
+        <v>0.1084782727846733</v>
       </c>
       <c r="T20">
-        <v>1.046582568733736</v>
+        <v>1.056845724110683</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.12175630780282</v>
+        <v>11.48376913370793</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09534732095558539</v>
+        <v>0.09515533272183287</v>
       </c>
       <c r="C21">
-        <v>52.0479135893351</v>
+        <v>51.63628114826941</v>
       </c>
       <c r="D21">
-        <v>59.9929135893351</v>
+        <v>60.22628114826941</v>
       </c>
       <c r="E21">
-        <v>-20.445</v>
+        <v>-19.8</v>
       </c>
       <c r="F21">
-        <v>12.255</v>
+        <v>12.9</v>
       </c>
       <c r="G21">
         <v>4.31</v>
@@ -3003,28 +3003,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M21">
-        <v>0.6348090000000001</v>
+        <v>0.66822</v>
       </c>
       <c r="N21">
-        <v>6.655191000000001</v>
+        <v>6.621780000000001</v>
       </c>
       <c r="O21">
-        <v>1.59724584</v>
+        <v>1.5892272</v>
       </c>
       <c r="P21">
-        <v>5.057945160000001</v>
+        <v>5.032552800000001</v>
       </c>
       <c r="Q21">
-        <v>10.11794516</v>
+        <v>10.0925528</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1084782727846733</v>
+        <v>0.1091021659022911</v>
       </c>
       <c r="T21">
-        <v>1.056845724110683</v>
+        <v>1.067365458372052</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.48376913370793</v>
+        <v>10.90958067702254</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09515533272183287</v>
+        <v>0.09496334448808036</v>
       </c>
       <c r="C22">
-        <v>51.63628114826941</v>
+        <v>51.22647135885285</v>
       </c>
       <c r="D22">
-        <v>60.22628114826941</v>
+        <v>60.46147135885285</v>
       </c>
       <c r="E22">
-        <v>-19.8</v>
+        <v>-19.155</v>
       </c>
       <c r="F22">
-        <v>12.9</v>
+        <v>13.545</v>
       </c>
       <c r="G22">
         <v>4.31</v>
@@ -3085,28 +3085,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M22">
-        <v>0.66822</v>
+        <v>0.7016310000000001</v>
       </c>
       <c r="N22">
-        <v>6.621780000000001</v>
+        <v>6.588369000000001</v>
       </c>
       <c r="O22">
-        <v>1.5892272</v>
+        <v>1.58120856</v>
       </c>
       <c r="P22">
-        <v>5.032552800000001</v>
+        <v>5.007160440000001</v>
       </c>
       <c r="Q22">
-        <v>10.0925528</v>
+        <v>10.06716044</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1091021659022911</v>
+        <v>0.1097418537823802</v>
       </c>
       <c r="T22">
-        <v>1.067365458372052</v>
+        <v>1.078151515019786</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.90958067702254</v>
+        <v>10.39007683525956</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09496334448808036</v>
+        <v>0.09477135625432782</v>
       </c>
       <c r="C23">
-        <v>51.22647135885285</v>
+        <v>50.81850565775977</v>
       </c>
       <c r="D23">
-        <v>60.46147135885285</v>
+        <v>60.69850565775977</v>
       </c>
       <c r="E23">
-        <v>-19.155</v>
+        <v>-18.51000000000001</v>
       </c>
       <c r="F23">
-        <v>13.545</v>
+        <v>14.19</v>
       </c>
       <c r="G23">
         <v>4.31</v>
@@ -3167,28 +3167,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M23">
-        <v>0.701631</v>
+        <v>0.735042</v>
       </c>
       <c r="N23">
-        <v>6.588369000000001</v>
+        <v>6.554958000000001</v>
       </c>
       <c r="O23">
-        <v>1.58120856</v>
+        <v>1.57318992</v>
       </c>
       <c r="P23">
-        <v>5.007160440000001</v>
+        <v>4.981768080000001</v>
       </c>
       <c r="Q23">
-        <v>10.06716044</v>
+        <v>10.04176808</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1097418537823802</v>
+        <v>0.1103979439158049</v>
       </c>
       <c r="T23">
-        <v>1.078151515019786</v>
+        <v>1.08921413722259</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.39007683525956</v>
+        <v>9.917800615475036</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09477135625432782</v>
+        <v>0.09487652802057531</v>
       </c>
       <c r="C24">
-        <v>50.81850565775977</v>
+        <v>50.04342781187115</v>
       </c>
       <c r="D24">
-        <v>60.69850565775977</v>
+        <v>60.56842781187115</v>
       </c>
       <c r="E24">
-        <v>-18.51000000000001</v>
+        <v>-17.865</v>
       </c>
       <c r="F24">
-        <v>14.19</v>
+        <v>14.835</v>
       </c>
       <c r="G24">
         <v>4.31</v>
@@ -3249,45 +3249,45 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M24">
-        <v>0.735042</v>
+        <v>0.7936725</v>
       </c>
       <c r="N24">
-        <v>6.554958000000001</v>
+        <v>6.496327500000001</v>
       </c>
       <c r="O24">
-        <v>1.57318992</v>
+        <v>1.5591186</v>
       </c>
       <c r="P24">
-        <v>4.981768080000001</v>
+        <v>4.937208900000001</v>
       </c>
       <c r="Q24">
-        <v>10.04176808</v>
+        <v>9.9972089</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1103979439158049</v>
+        <v>0.1110710753513965</v>
       </c>
       <c r="T24">
-        <v>1.08921413722259</v>
+        <v>1.10056410026183</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.24</v>
       </c>
       <c r="W24">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>9.917800615475036</v>
+        <v>9.185148786180699</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09487652802057531</v>
+        <v>0.0946974597868228</v>
       </c>
       <c r="C25">
-        <v>50.04342781187115</v>
+        <v>49.62023649961733</v>
       </c>
       <c r="D25">
-        <v>60.56842781187115</v>
+        <v>60.79023649961734</v>
       </c>
       <c r="E25">
-        <v>-17.865</v>
+        <v>-17.22</v>
       </c>
       <c r="F25">
-        <v>14.835</v>
+        <v>15.48</v>
       </c>
       <c r="G25">
         <v>4.31</v>
@@ -3331,28 +3331,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M25">
-        <v>0.7936725</v>
+        <v>0.82818</v>
       </c>
       <c r="N25">
-        <v>6.496327500000001</v>
+        <v>6.461820000000001</v>
       </c>
       <c r="O25">
-        <v>1.5591186</v>
+        <v>1.5508368</v>
       </c>
       <c r="P25">
-        <v>4.937208900000001</v>
+        <v>4.9109832</v>
       </c>
       <c r="Q25">
-        <v>9.9972089</v>
+        <v>9.970983200000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1110710753513965</v>
+        <v>0.1117619207721353</v>
       </c>
       <c r="T25">
-        <v>1.10056410026183</v>
+        <v>1.112212746538946</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.185148786180699</v>
+        <v>8.80243425342317</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0946974597868228</v>
+        <v>0.09451839155307026</v>
       </c>
       <c r="C26">
-        <v>49.62023649961734</v>
+        <v>49.19867573749792</v>
       </c>
       <c r="D26">
-        <v>60.79023649961734</v>
+        <v>61.01367573749792</v>
       </c>
       <c r="E26">
-        <v>-17.22000000000001</v>
+        <v>-16.575</v>
       </c>
       <c r="F26">
-        <v>15.48</v>
+        <v>16.125</v>
       </c>
       <c r="G26">
         <v>4.31</v>
@@ -3413,28 +3413,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M26">
-        <v>0.8281799999999999</v>
+        <v>0.8626874999999999</v>
       </c>
       <c r="N26">
-        <v>6.461820000000001</v>
+        <v>6.427312500000001</v>
       </c>
       <c r="O26">
-        <v>1.5508368</v>
+        <v>1.542555</v>
       </c>
       <c r="P26">
-        <v>4.9109832</v>
+        <v>4.884757500000001</v>
       </c>
       <c r="Q26">
-        <v>9.970983200000001</v>
+        <v>9.944757500000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1117619207721353</v>
+        <v>0.112471188737427</v>
       </c>
       <c r="T26">
-        <v>1.112212746538946</v>
+        <v>1.12417202338345</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.802434253423172</v>
+        <v>8.450336883286244</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09451839155307026</v>
+        <v>0.09433932331931774</v>
       </c>
       <c r="C27">
-        <v>49.19867573749792</v>
+        <v>48.77876357148334</v>
       </c>
       <c r="D27">
-        <v>61.01367573749792</v>
+        <v>61.23876357148333</v>
       </c>
       <c r="E27">
-        <v>-16.575</v>
+        <v>-15.93</v>
       </c>
       <c r="F27">
-        <v>16.125</v>
+        <v>16.77</v>
       </c>
       <c r="G27">
         <v>4.31</v>
@@ -3495,28 +3495,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M27">
-        <v>0.8626874999999999</v>
+        <v>0.897195</v>
       </c>
       <c r="N27">
-        <v>6.427312500000001</v>
+        <v>6.392805000000001</v>
       </c>
       <c r="O27">
-        <v>1.542555</v>
+        <v>1.5342732</v>
       </c>
       <c r="P27">
-        <v>4.884757500000001</v>
+        <v>4.858531800000001</v>
       </c>
       <c r="Q27">
-        <v>9.944757500000001</v>
+        <v>9.9185318</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.112471188737427</v>
+        <v>0.1131996261071861</v>
       </c>
       <c r="T27">
-        <v>1.12417202338345</v>
+        <v>1.136454523926455</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.450336883286244</v>
+        <v>8.125323926236772</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09433932331931774</v>
+        <v>0.09416025508556522</v>
       </c>
       <c r="C28">
-        <v>48.77876357148334</v>
+        <v>48.36051831482642</v>
       </c>
       <c r="D28">
-        <v>61.23876357148333</v>
+        <v>61.46551831482643</v>
       </c>
       <c r="E28">
-        <v>-15.93</v>
+        <v>-15.285</v>
       </c>
       <c r="F28">
-        <v>16.77</v>
+        <v>17.415</v>
       </c>
       <c r="G28">
         <v>4.31</v>
@@ -3577,28 +3577,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M28">
-        <v>0.897195</v>
+        <v>0.9317025000000001</v>
       </c>
       <c r="N28">
-        <v>6.392805000000001</v>
+        <v>6.358297500000001</v>
       </c>
       <c r="O28">
-        <v>1.5342732</v>
+        <v>1.5259914</v>
       </c>
       <c r="P28">
-        <v>4.858531800000001</v>
+        <v>4.8323061</v>
       </c>
       <c r="Q28">
-        <v>9.9185318</v>
+        <v>9.892306100000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1131996261071861</v>
+        <v>0.1139480206651578</v>
       </c>
       <c r="T28">
-        <v>1.136454523926455</v>
+        <v>1.149073531333652</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.125323926236772</v>
+        <v>7.824386003042817</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09416025508556522</v>
+        <v>0.0941514268518127</v>
       </c>
       <c r="C29">
-        <v>48.36051831482642</v>
+        <v>47.72674098184443</v>
       </c>
       <c r="D29">
-        <v>61.46551831482643</v>
+        <v>61.47674098184443</v>
       </c>
       <c r="E29">
-        <v>-15.285</v>
+        <v>-14.64</v>
       </c>
       <c r="F29">
-        <v>17.415</v>
+        <v>18.06</v>
       </c>
       <c r="G29">
         <v>4.31</v>
@@ -3659,45 +3659,45 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M29">
-        <v>0.9317025000000001</v>
+        <v>0.9806580000000001</v>
       </c>
       <c r="N29">
-        <v>6.358297500000001</v>
+        <v>6.309342000000001</v>
       </c>
       <c r="O29">
-        <v>1.5259914</v>
+        <v>1.51424208</v>
       </c>
       <c r="P29">
-        <v>4.8323061</v>
+        <v>4.79509992</v>
       </c>
       <c r="Q29">
-        <v>9.892306100000001</v>
+        <v>9.855099920000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1139480206651578</v>
+        <v>0.114717203960851</v>
       </c>
       <c r="T29">
-        <v>1.149073531333652</v>
+        <v>1.162043066724382</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.24</v>
       </c>
       <c r="W29">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.824386003042817</v>
+        <v>7.433784255061398</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0941514268518127</v>
+        <v>0.09397843861806018</v>
       </c>
       <c r="C30">
-        <v>47.72674098184443</v>
+        <v>47.30247775008256</v>
       </c>
       <c r="D30">
-        <v>61.47674098184443</v>
+        <v>61.69747775008256</v>
       </c>
       <c r="E30">
-        <v>-14.64</v>
+        <v>-13.995</v>
       </c>
       <c r="F30">
-        <v>18.06</v>
+        <v>18.705</v>
       </c>
       <c r="G30">
         <v>4.31</v>
@@ -3741,28 +3741,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M30">
-        <v>0.9806580000000001</v>
+        <v>1.0156815</v>
       </c>
       <c r="N30">
-        <v>6.309342000000001</v>
+        <v>6.274318500000001</v>
       </c>
       <c r="O30">
-        <v>1.51424208</v>
+        <v>1.50583644</v>
       </c>
       <c r="P30">
-        <v>4.79509992</v>
+        <v>4.76848206</v>
       </c>
       <c r="Q30">
-        <v>9.855099920000001</v>
+        <v>9.828482060000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.114717203960851</v>
+        <v>0.1155080543916341</v>
       </c>
       <c r="T30">
-        <v>1.162043066724382</v>
+        <v>1.175377941140203</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.433784255061398</v>
+        <v>7.177446866955832</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09397843861806018</v>
+        <v>0.09380545038430765</v>
       </c>
       <c r="C31">
-        <v>47.30247775008256</v>
+        <v>46.87980537366553</v>
       </c>
       <c r="D31">
-        <v>61.69747775008256</v>
+        <v>61.91980537366553</v>
       </c>
       <c r="E31">
-        <v>-13.995</v>
+        <v>-13.35</v>
       </c>
       <c r="F31">
-        <v>18.705</v>
+        <v>19.35</v>
       </c>
       <c r="G31">
         <v>4.31</v>
@@ -3823,28 +3823,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M31">
-        <v>1.0156815</v>
+        <v>1.050705</v>
       </c>
       <c r="N31">
-        <v>6.274318500000001</v>
+        <v>6.239295000000001</v>
       </c>
       <c r="O31">
-        <v>1.50583644</v>
+        <v>1.4974308</v>
       </c>
       <c r="P31">
-        <v>4.768482060000001</v>
+        <v>4.741864200000001</v>
       </c>
       <c r="Q31">
-        <v>9.828482060000002</v>
+        <v>9.801864200000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1155080543916341</v>
+        <v>0.1163215005490109</v>
       </c>
       <c r="T31">
-        <v>1.175377941140203</v>
+        <v>1.189093811967905</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.177446866955834</v>
+        <v>6.938198638057306</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09380545038430765</v>
+        <v>0.09363246215055514</v>
       </c>
       <c r="C32">
-        <v>46.87980537366553</v>
+        <v>46.45874111279129</v>
       </c>
       <c r="D32">
-        <v>61.91980537366553</v>
+        <v>62.1437411127913</v>
       </c>
       <c r="E32">
-        <v>-13.35</v>
+        <v>-12.705</v>
       </c>
       <c r="F32">
-        <v>19.35</v>
+        <v>19.995</v>
       </c>
       <c r="G32">
         <v>4.31</v>
@@ -3905,28 +3905,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M32">
-        <v>1.050705</v>
+        <v>1.0857285</v>
       </c>
       <c r="N32">
-        <v>6.239295000000001</v>
+        <v>6.204271500000001</v>
       </c>
       <c r="O32">
-        <v>1.4974308</v>
+        <v>1.48902516</v>
       </c>
       <c r="P32">
-        <v>4.741864200000001</v>
+        <v>4.71524634</v>
       </c>
       <c r="Q32">
-        <v>9.801864200000001</v>
+        <v>9.775246340000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1163215005490109</v>
+        <v>0.117158524855877</v>
       </c>
       <c r="T32">
-        <v>1.189093811967905</v>
+        <v>1.203207244268873</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.938198638057306</v>
+        <v>6.714385778765133</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09363246215055514</v>
+        <v>0.09345947391680261</v>
       </c>
       <c r="C33">
-        <v>46.45874111279129</v>
+        <v>46.03930247825333</v>
       </c>
       <c r="D33">
-        <v>62.1437411127913</v>
+        <v>62.36930247825333</v>
       </c>
       <c r="E33">
-        <v>-12.705</v>
+        <v>-12.06</v>
       </c>
       <c r="F33">
-        <v>19.995</v>
+        <v>20.64</v>
       </c>
       <c r="G33">
         <v>4.31</v>
@@ -3987,28 +3987,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M33">
-        <v>1.0857285</v>
+        <v>1.120752</v>
       </c>
       <c r="N33">
-        <v>6.204271500000001</v>
+        <v>6.169248000000001</v>
       </c>
       <c r="O33">
-        <v>1.48902516</v>
+        <v>1.48061952</v>
       </c>
       <c r="P33">
-        <v>4.71524634</v>
+        <v>4.688628480000001</v>
       </c>
       <c r="Q33">
-        <v>9.775246340000001</v>
+        <v>9.748628480000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.117158524855877</v>
+        <v>0.1180201675247097</v>
       </c>
       <c r="T33">
-        <v>1.203207244268873</v>
+        <v>1.21773577751987</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.714385778765133</v>
+        <v>6.504561223178724</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09345947391680261</v>
+        <v>0.09328648568305009</v>
       </c>
       <c r="C34">
-        <v>46.03930247825333</v>
+        <v>45.62150723600487</v>
       </c>
       <c r="D34">
-        <v>62.36930247825333</v>
+        <v>62.59650723600487</v>
       </c>
       <c r="E34">
-        <v>-12.06</v>
+        <v>-11.415</v>
       </c>
       <c r="F34">
-        <v>20.64</v>
+        <v>21.285</v>
       </c>
       <c r="G34">
         <v>4.31</v>
@@ -4069,28 +4069,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M34">
-        <v>1.120752</v>
+        <v>1.1557755</v>
       </c>
       <c r="N34">
-        <v>6.169248000000001</v>
+        <v>6.134224500000001</v>
       </c>
       <c r="O34">
-        <v>1.48061952</v>
+        <v>1.47221388</v>
       </c>
       <c r="P34">
-        <v>4.688628480000001</v>
+        <v>4.662010620000001</v>
       </c>
       <c r="Q34">
-        <v>9.748628480000001</v>
+        <v>9.722010620000002</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1180201675247097</v>
+        <v>0.118907530870224</v>
       </c>
       <c r="T34">
-        <v>1.21773577751987</v>
+        <v>1.232697998330598</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.504561223178724</v>
+        <v>6.307453307324823</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09328648568305009</v>
+        <v>0.09311349744929756</v>
       </c>
       <c r="C35">
-        <v>45.62150723600487</v>
+        <v>45.20537341182369</v>
       </c>
       <c r="D35">
-        <v>62.59650723600487</v>
+        <v>62.82537341182369</v>
       </c>
       <c r="E35">
-        <v>-11.415</v>
+        <v>-10.77</v>
       </c>
       <c r="F35">
-        <v>21.285</v>
+        <v>21.93</v>
       </c>
       <c r="G35">
         <v>4.31</v>
@@ -4151,28 +4151,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M35">
-        <v>1.1557755</v>
+        <v>1.190799</v>
       </c>
       <c r="N35">
-        <v>6.134224500000001</v>
+        <v>6.099201000000001</v>
       </c>
       <c r="O35">
-        <v>1.47221388</v>
+        <v>1.46380824</v>
       </c>
       <c r="P35">
-        <v>4.662010620000001</v>
+        <v>4.63539276</v>
       </c>
       <c r="Q35">
-        <v>9.722010620000002</v>
+        <v>9.695392760000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.118907530870224</v>
+        <v>0.1198217840140872</v>
       </c>
       <c r="T35">
-        <v>1.232697998330598</v>
+        <v>1.248113619771954</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.307453307324823</v>
+        <v>6.121939974756445</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09311349744929756</v>
+        <v>0.09320650921554505</v>
       </c>
       <c r="C36">
-        <v>45.20537341182369</v>
+        <v>44.43710977054559</v>
       </c>
       <c r="D36">
-        <v>62.82537341182369</v>
+        <v>62.7021097705456</v>
       </c>
       <c r="E36">
-        <v>-10.77</v>
+        <v>-10.125</v>
       </c>
       <c r="F36">
-        <v>21.93</v>
+        <v>22.575</v>
       </c>
       <c r="G36">
         <v>4.31</v>
@@ -4233,45 +4233,45 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M36">
-        <v>1.190799</v>
+        <v>1.2483975</v>
       </c>
       <c r="N36">
-        <v>6.099201000000001</v>
+        <v>6.041602500000001</v>
       </c>
       <c r="O36">
-        <v>1.46380824</v>
+        <v>1.4499846</v>
       </c>
       <c r="P36">
-        <v>4.63539276</v>
+        <v>4.591617900000001</v>
       </c>
       <c r="Q36">
-        <v>9.695392760000001</v>
+        <v>9.651617900000002</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1198217840140872</v>
+        <v>0.1207641680239155</v>
       </c>
       <c r="T36">
-        <v>1.248113619771954</v>
+        <v>1.264003568026891</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.24</v>
       </c>
       <c r="W36">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.121939974756445</v>
+        <v>5.839486221335752</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09320650921554505</v>
+        <v>0.09304112098179255</v>
       </c>
       <c r="C37">
-        <v>44.43710977054559</v>
+        <v>44.01162596685901</v>
       </c>
       <c r="D37">
-        <v>62.7021097705456</v>
+        <v>62.92162596685902</v>
       </c>
       <c r="E37">
-        <v>-10.125</v>
+        <v>-9.48</v>
       </c>
       <c r="F37">
-        <v>22.575</v>
+        <v>23.22</v>
       </c>
       <c r="G37">
         <v>4.31</v>
@@ -4315,28 +4315,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M37">
-        <v>1.2483975</v>
+        <v>1.284066</v>
       </c>
       <c r="N37">
-        <v>6.041602500000001</v>
+        <v>6.005934000000001</v>
       </c>
       <c r="O37">
-        <v>1.4499846</v>
+        <v>1.44142416</v>
       </c>
       <c r="P37">
-        <v>4.591617900000001</v>
+        <v>4.56450984</v>
       </c>
       <c r="Q37">
-        <v>9.651617900000002</v>
+        <v>9.624509840000002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1207641680239155</v>
+        <v>0.1217360015340509</v>
       </c>
       <c r="T37">
-        <v>1.264003568026891</v>
+        <v>1.280390077164794</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.839486221335752</v>
+        <v>5.677278270743093</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09304112098179254</v>
+        <v>0.09287573274804002</v>
       </c>
       <c r="C38">
-        <v>44.01162596685903</v>
+        <v>43.58768458827643</v>
       </c>
       <c r="D38">
-        <v>62.92162596685903</v>
+        <v>63.14268458827642</v>
       </c>
       <c r="E38">
-        <v>-9.480000000000004</v>
+        <v>-8.835000000000004</v>
       </c>
       <c r="F38">
-        <v>23.22</v>
+        <v>23.865</v>
       </c>
       <c r="G38">
         <v>4.31</v>
@@ -4397,28 +4397,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M38">
-        <v>1.284066</v>
+        <v>1.3197345</v>
       </c>
       <c r="N38">
-        <v>6.005934000000001</v>
+        <v>5.970265500000001</v>
       </c>
       <c r="O38">
-        <v>1.44142416</v>
+        <v>1.43286372</v>
       </c>
       <c r="P38">
-        <v>4.56450984</v>
+        <v>4.537401780000001</v>
       </c>
       <c r="Q38">
-        <v>9.624509840000002</v>
+        <v>9.597401780000002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1217360015340508</v>
+        <v>0.1227386869016508</v>
       </c>
       <c r="T38">
-        <v>1.280390077164794</v>
+        <v>1.297296792941996</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.677278270743093</v>
+        <v>5.523838317479767</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09287573274804002</v>
+        <v>0.0927103445142875</v>
       </c>
       <c r="C39">
-        <v>43.58768458827643</v>
+        <v>43.16530194883038</v>
       </c>
       <c r="D39">
-        <v>63.14268458827642</v>
+        <v>63.36530194883039</v>
       </c>
       <c r="E39">
-        <v>-8.835000000000004</v>
+        <v>-8.190000000000001</v>
       </c>
       <c r="F39">
-        <v>23.865</v>
+        <v>24.51</v>
       </c>
       <c r="G39">
         <v>4.31</v>
@@ -4479,28 +4479,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M39">
-        <v>1.3197345</v>
+        <v>1.355403</v>
       </c>
       <c r="N39">
-        <v>5.970265500000001</v>
+        <v>5.934597000000001</v>
       </c>
       <c r="O39">
-        <v>1.43286372</v>
+        <v>1.42430328</v>
       </c>
       <c r="P39">
-        <v>4.537401780000001</v>
+        <v>4.510293720000001</v>
       </c>
       <c r="Q39">
-        <v>9.597401780000002</v>
+        <v>9.570293720000002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1227386869016508</v>
+        <v>0.1237737169585282</v>
       </c>
       <c r="T39">
-        <v>1.297296792941996</v>
+        <v>1.314748886647494</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.523838317479767</v>
+        <v>5.378474151230298</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0927103445142875</v>
+        <v>0.09254495628053498</v>
       </c>
       <c r="C40">
-        <v>43.16530194883038</v>
+        <v>42.74449459343612</v>
       </c>
       <c r="D40">
-        <v>63.36530194883039</v>
+        <v>63.58949459343611</v>
       </c>
       <c r="E40">
-        <v>-8.190000000000001</v>
+        <v>-7.545000000000002</v>
       </c>
       <c r="F40">
-        <v>24.51</v>
+        <v>25.155</v>
       </c>
       <c r="G40">
         <v>4.31</v>
@@ -4561,28 +4561,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M40">
-        <v>1.355403</v>
+        <v>1.3910715</v>
       </c>
       <c r="N40">
-        <v>5.934597000000001</v>
+        <v>5.898928500000001</v>
       </c>
       <c r="O40">
-        <v>1.42430328</v>
+        <v>1.41574284</v>
       </c>
       <c r="P40">
-        <v>4.510293720000001</v>
+        <v>4.483185660000001</v>
       </c>
       <c r="Q40">
-        <v>9.570293720000002</v>
+        <v>9.543185660000002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1237737169585282</v>
+        <v>0.1248426824271065</v>
       </c>
       <c r="T40">
-        <v>1.314748886647494</v>
+        <v>1.332773180146616</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.378474151230298</v>
+        <v>5.24056455760901</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09254495628053498</v>
+        <v>0.09237956804678248</v>
       </c>
       <c r="C41">
-        <v>42.74449459343612</v>
+        <v>42.32527930199031</v>
       </c>
       <c r="D41">
-        <v>63.58949459343611</v>
+        <v>63.8152793019903</v>
       </c>
       <c r="E41">
-        <v>-7.545000000000002</v>
+        <v>-6.900000000000002</v>
       </c>
       <c r="F41">
-        <v>25.155</v>
+        <v>25.8</v>
       </c>
       <c r="G41">
         <v>4.31</v>
@@ -4643,28 +4643,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M41">
-        <v>1.3910715</v>
+        <v>1.42674</v>
       </c>
       <c r="N41">
-        <v>5.898928500000001</v>
+        <v>5.86326</v>
       </c>
       <c r="O41">
-        <v>1.41574284</v>
+        <v>1.4071824</v>
       </c>
       <c r="P41">
-        <v>4.483185660000001</v>
+        <v>4.4560776</v>
       </c>
       <c r="Q41">
-        <v>9.543185660000002</v>
+        <v>9.516077600000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1248426824271065</v>
+        <v>0.1259472800779708</v>
       </c>
       <c r="T41">
-        <v>1.332773180146616</v>
+        <v>1.351398283429041</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.24056455760901</v>
+        <v>5.109550443668783</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09237956804678248</v>
+        <v>0.09221417981302996</v>
       </c>
       <c r="C42">
-        <v>42.32527930199031</v>
+        <v>41.9076730935578</v>
       </c>
       <c r="D42">
-        <v>63.8152793019903</v>
+        <v>64.0426730935578</v>
       </c>
       <c r="E42">
-        <v>-6.900000000000002</v>
+        <v>-6.255000000000003</v>
       </c>
       <c r="F42">
-        <v>25.8</v>
+        <v>26.445</v>
       </c>
       <c r="G42">
         <v>4.31</v>
@@ -4725,28 +4725,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M42">
-        <v>1.42674</v>
+        <v>1.4624085</v>
       </c>
       <c r="N42">
-        <v>5.86326</v>
+        <v>5.8275915</v>
       </c>
       <c r="O42">
-        <v>1.4071824</v>
+        <v>1.39862196</v>
       </c>
       <c r="P42">
-        <v>4.4560776</v>
+        <v>4.428969540000001</v>
       </c>
       <c r="Q42">
-        <v>9.516077600000001</v>
+        <v>9.488969540000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1259472800779708</v>
+        <v>0.1270893217169999</v>
       </c>
       <c r="T42">
-        <v>1.351398283429041</v>
+        <v>1.370654746144769</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.109550443668783</v>
+        <v>4.984927262115887</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09221417981302996</v>
+        <v>0.09204879157927742</v>
       </c>
       <c r="C43">
-        <v>41.9076730935578</v>
+        <v>41.49169323064783</v>
       </c>
       <c r="D43">
-        <v>64.0426730935578</v>
+        <v>64.27169323064783</v>
       </c>
       <c r="E43">
-        <v>-6.255000000000003</v>
+        <v>-5.609999999999999</v>
       </c>
       <c r="F43">
-        <v>26.445</v>
+        <v>27.09</v>
       </c>
       <c r="G43">
         <v>4.31</v>
@@ -4807,28 +4807,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M43">
-        <v>1.4624085</v>
+        <v>1.498077</v>
       </c>
       <c r="N43">
-        <v>5.8275915</v>
+        <v>5.791923000000001</v>
       </c>
       <c r="O43">
-        <v>1.39862196</v>
+        <v>1.39006152</v>
       </c>
       <c r="P43">
-        <v>4.428969540000001</v>
+        <v>4.401861480000001</v>
       </c>
       <c r="Q43">
-        <v>9.488969540000001</v>
+        <v>9.461861480000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1270893217169999</v>
+        <v>0.1282707441022025</v>
       </c>
       <c r="T43">
-        <v>1.370654746144769</v>
+        <v>1.390575224816212</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.984927262115887</v>
+        <v>4.866238517779793</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09204879157927744</v>
+        <v>0.09188340334552492</v>
       </c>
       <c r="C44">
-        <v>41.49169323064781</v>
+        <v>41.07735722358254</v>
       </c>
       <c r="D44">
-        <v>64.27169323064781</v>
+        <v>64.50235722358254</v>
       </c>
       <c r="E44">
-        <v>-5.610000000000003</v>
+        <v>-4.965000000000003</v>
       </c>
       <c r="F44">
-        <v>27.09</v>
+        <v>27.735</v>
       </c>
       <c r="G44">
         <v>4.31</v>
@@ -4889,28 +4889,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M44">
-        <v>1.498077</v>
+        <v>1.5337455</v>
       </c>
       <c r="N44">
-        <v>5.791923000000001</v>
+        <v>5.756254500000001</v>
       </c>
       <c r="O44">
-        <v>1.39006152</v>
+        <v>1.38150108</v>
       </c>
       <c r="P44">
-        <v>4.401861480000001</v>
+        <v>4.374753420000001</v>
       </c>
       <c r="Q44">
-        <v>9.461861480000001</v>
+        <v>9.434753420000002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1282707441022025</v>
+        <v>0.1294936199044297</v>
       </c>
       <c r="T44">
-        <v>1.390575224816212</v>
+        <v>1.411194667651565</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.866238517779793</v>
+        <v>4.753070180157009</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09188340334552492</v>
+        <v>0.0917180151117724</v>
       </c>
       <c r="C45">
-        <v>41.07735722358254</v>
+        <v>40.66468283496</v>
       </c>
       <c r="D45">
-        <v>64.50235722358254</v>
+        <v>64.73468283496</v>
       </c>
       <c r="E45">
-        <v>-4.965000000000003</v>
+        <v>-4.320000000000004</v>
       </c>
       <c r="F45">
-        <v>27.735</v>
+        <v>28.38</v>
       </c>
       <c r="G45">
         <v>4.31</v>
@@ -4971,28 +4971,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M45">
-        <v>1.5337455</v>
+        <v>1.569414</v>
       </c>
       <c r="N45">
-        <v>5.756254500000001</v>
+        <v>5.720586000000001</v>
       </c>
       <c r="O45">
-        <v>1.38150108</v>
+        <v>1.37294064</v>
       </c>
       <c r="P45">
-        <v>4.374753420000001</v>
+        <v>4.34764536</v>
       </c>
       <c r="Q45">
-        <v>9.434753420000002</v>
+        <v>9.40764536</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1294936199044297</v>
+        <v>0.1307601698424507</v>
       </c>
       <c r="T45">
-        <v>1.411194667651565</v>
+        <v>1.432550519159609</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.753070180157009</v>
+        <v>4.645045857880712</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0917180151117724</v>
+        <v>0.09155262687801988</v>
       </c>
       <c r="C46">
-        <v>40.66468283496</v>
+        <v>40.25368808421372</v>
       </c>
       <c r="D46">
-        <v>64.73468283496</v>
+        <v>64.96868808421372</v>
       </c>
       <c r="E46">
-        <v>-4.320000000000004</v>
+        <v>-3.675000000000001</v>
       </c>
       <c r="F46">
-        <v>28.38</v>
+        <v>29.025</v>
       </c>
       <c r="G46">
         <v>4.31</v>
@@ -5053,28 +5053,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M46">
-        <v>1.569414</v>
+        <v>1.6050825</v>
       </c>
       <c r="N46">
-        <v>5.720586000000001</v>
+        <v>5.684917500000001</v>
       </c>
       <c r="O46">
-        <v>1.37294064</v>
+        <v>1.3643802</v>
       </c>
       <c r="P46">
-        <v>4.34764536</v>
+        <v>4.320537300000001</v>
       </c>
       <c r="Q46">
-        <v>9.40764536</v>
+        <v>9.3805373</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1307601698424507</v>
+        <v>0.1320727761418543</v>
       </c>
       <c r="T46">
-        <v>1.432550519159609</v>
+        <v>1.454682947086128</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.645045857880712</v>
+        <v>4.541822616594475</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09155262687801988</v>
+        <v>0.09226123864426734</v>
       </c>
       <c r="C47">
-        <v>40.25368808421372</v>
+        <v>38.61780669238033</v>
       </c>
       <c r="D47">
-        <v>64.96868808421372</v>
+        <v>63.97780669238033</v>
       </c>
       <c r="E47">
-        <v>-3.675000000000001</v>
+        <v>-3.030000000000001</v>
       </c>
       <c r="F47">
-        <v>29.025</v>
+        <v>29.67</v>
       </c>
       <c r="G47">
         <v>4.31</v>
@@ -5135,45 +5135,45 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M47">
-        <v>1.6050825</v>
+        <v>1.714926</v>
       </c>
       <c r="N47">
-        <v>5.684917500000001</v>
+        <v>5.575074000000001</v>
       </c>
       <c r="O47">
-        <v>1.3643802</v>
+        <v>1.33801776</v>
       </c>
       <c r="P47">
-        <v>4.320537300000001</v>
+        <v>4.237056240000001</v>
       </c>
       <c r="Q47">
-        <v>9.3805373</v>
+        <v>9.297056240000002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1320727761418543</v>
+        <v>0.133433997489384</v>
       </c>
       <c r="T47">
-        <v>1.454682947086128</v>
+        <v>1.477635094565481</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.24</v>
       </c>
       <c r="W47">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.541822616594475</v>
+        <v>4.250912284261828</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09226123864426734</v>
+        <v>0.09211485041051484</v>
       </c>
       <c r="C48">
-        <v>38.61780669238033</v>
+        <v>38.17502256996698</v>
       </c>
       <c r="D48">
-        <v>63.97780669238033</v>
+        <v>64.18002256996698</v>
       </c>
       <c r="E48">
-        <v>-3.030000000000001</v>
+        <v>-2.385000000000002</v>
       </c>
       <c r="F48">
-        <v>29.67</v>
+        <v>30.315</v>
       </c>
       <c r="G48">
         <v>4.31</v>
@@ -5217,28 +5217,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M48">
-        <v>1.714926</v>
+        <v>1.752207</v>
       </c>
       <c r="N48">
-        <v>5.575074000000001</v>
+        <v>5.537793000000001</v>
       </c>
       <c r="O48">
-        <v>1.33801776</v>
+        <v>1.32907032</v>
       </c>
       <c r="P48">
-        <v>4.237056240000001</v>
+        <v>4.208722680000001</v>
       </c>
       <c r="Q48">
-        <v>9.297056240000002</v>
+        <v>9.268722680000002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.133433997489384</v>
+        <v>0.1348465856802167</v>
       </c>
       <c r="T48">
-        <v>1.477635094565481</v>
+        <v>1.501453360817639</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.250912284261828</v>
+        <v>4.160467342043491</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09211485041051484</v>
+        <v>0.0919684621767623</v>
       </c>
       <c r="C49">
-        <v>38.17502256996698</v>
+        <v>37.73352079588242</v>
       </c>
       <c r="D49">
-        <v>64.18002256996698</v>
+        <v>64.38352079588242</v>
       </c>
       <c r="E49">
-        <v>-2.385000000000002</v>
+        <v>-1.740000000000002</v>
       </c>
       <c r="F49">
-        <v>30.315</v>
+        <v>30.96</v>
       </c>
       <c r="G49">
         <v>4.31</v>
@@ -5299,28 +5299,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M49">
-        <v>1.752207</v>
+        <v>1.789488</v>
       </c>
       <c r="N49">
-        <v>5.537793000000001</v>
+        <v>5.500512000000001</v>
       </c>
       <c r="O49">
-        <v>1.32907032</v>
+        <v>1.32012288</v>
       </c>
       <c r="P49">
-        <v>4.208722680000001</v>
+        <v>4.180389120000001</v>
       </c>
       <c r="Q49">
-        <v>9.268722680000002</v>
+        <v>9.240389120000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1348465856802167</v>
+        <v>0.1363135041860813</v>
       </c>
       <c r="T49">
-        <v>1.501453360817639</v>
+        <v>1.526187714233342</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.160467342043491</v>
+        <v>4.073790939084252</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0919684621767623</v>
+        <v>0.09312547394300977</v>
       </c>
       <c r="C50">
-        <v>37.73352079588243</v>
+        <v>35.51447441225868</v>
       </c>
       <c r="D50">
-        <v>64.38352079588242</v>
+        <v>62.80947441225868</v>
       </c>
       <c r="E50">
-        <v>-1.740000000000006</v>
+        <v>-1.095000000000002</v>
       </c>
       <c r="F50">
-        <v>30.96</v>
+        <v>31.605</v>
       </c>
       <c r="G50">
         <v>4.31</v>
@@ -5381,45 +5381,45 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M50">
-        <v>1.789488</v>
+        <v>1.9373865</v>
       </c>
       <c r="N50">
-        <v>5.500512000000001</v>
+        <v>5.3526135</v>
       </c>
       <c r="O50">
-        <v>1.32012288</v>
+        <v>1.28462724</v>
       </c>
       <c r="P50">
-        <v>4.180389120000001</v>
+        <v>4.067986260000001</v>
       </c>
       <c r="Q50">
-        <v>9.240389120000001</v>
+        <v>9.12798626</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1363135041860813</v>
+        <v>0.1378379489078623</v>
       </c>
       <c r="T50">
-        <v>1.526187714233342</v>
+        <v>1.551892042292798</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.24</v>
       </c>
       <c r="W50">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.073790939084253</v>
+        <v>3.762801072475729</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09312547394300977</v>
+        <v>0.09300568570925727</v>
       </c>
       <c r="C51">
-        <v>35.51447441225868</v>
+        <v>35.02885851800193</v>
       </c>
       <c r="D51">
-        <v>62.80947441225868</v>
+        <v>62.96885851800193</v>
       </c>
       <c r="E51">
-        <v>-1.095000000000002</v>
+        <v>-0.4500000000000028</v>
       </c>
       <c r="F51">
-        <v>31.605</v>
+        <v>32.25</v>
       </c>
       <c r="G51">
         <v>4.31</v>
@@ -5463,28 +5463,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M51">
-        <v>1.9373865</v>
+        <v>1.976925</v>
       </c>
       <c r="N51">
-        <v>5.3526135</v>
+        <v>5.313075000000001</v>
       </c>
       <c r="O51">
-        <v>1.28462724</v>
+        <v>1.275138</v>
       </c>
       <c r="P51">
-        <v>4.067986260000001</v>
+        <v>4.037937000000001</v>
       </c>
       <c r="Q51">
-        <v>9.12798626</v>
+        <v>9.097937000000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1378379489078623</v>
+        <v>0.1394233714185145</v>
       </c>
       <c r="T51">
-        <v>1.551892042292798</v>
+        <v>1.578624543474632</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.762801072475729</v>
+        <v>3.687545051026216</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09300568570925727</v>
+        <v>0.09288589747550476</v>
       </c>
       <c r="C52">
-        <v>35.02885851800193</v>
+        <v>34.5440535816557</v>
       </c>
       <c r="D52">
-        <v>62.96885851800193</v>
+        <v>63.1290535816557</v>
       </c>
       <c r="E52">
-        <v>-0.4500000000000028</v>
+        <v>0.1950000000000003</v>
       </c>
       <c r="F52">
-        <v>32.25</v>
+        <v>32.895</v>
       </c>
       <c r="G52">
         <v>4.31</v>
@@ -5545,28 +5545,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M52">
-        <v>1.976925</v>
+        <v>2.0164635</v>
       </c>
       <c r="N52">
-        <v>5.313075000000001</v>
+        <v>5.273536500000001</v>
       </c>
       <c r="O52">
-        <v>1.275138</v>
+        <v>1.26564876</v>
       </c>
       <c r="P52">
-        <v>4.037937000000001</v>
+        <v>4.00788774</v>
       </c>
       <c r="Q52">
-        <v>9.097937000000002</v>
+        <v>9.06788774</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1394233714185145</v>
+        <v>0.1410735050520505</v>
       </c>
       <c r="T52">
-        <v>1.578624543474632</v>
+        <v>1.606448167153684</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.687545051026216</v>
+        <v>3.615240246104132</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09288589747550476</v>
+        <v>0.09276610924175223</v>
       </c>
       <c r="C53">
-        <v>34.5440535816557</v>
+        <v>34.06006580832516</v>
       </c>
       <c r="D53">
-        <v>63.1290535816557</v>
+        <v>63.29006580832516</v>
       </c>
       <c r="E53">
-        <v>0.1950000000000003</v>
+        <v>0.8399999999999963</v>
       </c>
       <c r="F53">
-        <v>32.895</v>
+        <v>33.54</v>
       </c>
       <c r="G53">
         <v>4.31</v>
@@ -5627,28 +5627,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M53">
-        <v>2.0164635</v>
+        <v>2.056002</v>
       </c>
       <c r="N53">
-        <v>5.273536500000001</v>
+        <v>5.233998000000001</v>
       </c>
       <c r="O53">
-        <v>1.26564876</v>
+        <v>1.25615952</v>
       </c>
       <c r="P53">
-        <v>4.00788774</v>
+        <v>3.977838480000001</v>
       </c>
       <c r="Q53">
-        <v>9.06788774</v>
+        <v>9.037838480000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1410735050520505</v>
+        <v>0.1427923942536505</v>
       </c>
       <c r="T53">
-        <v>1.606448167153684</v>
+        <v>1.63543110848603</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.615240246104132</v>
+        <v>3.545716395217515</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09276610924175223</v>
+        <v>0.09377416100799971</v>
       </c>
       <c r="C54">
-        <v>34.06006580832516</v>
+        <v>32.08519028192747</v>
       </c>
       <c r="D54">
-        <v>63.29006580832516</v>
+        <v>61.96019028192747</v>
       </c>
       <c r="E54">
-        <v>0.8399999999999963</v>
+        <v>1.484999999999999</v>
       </c>
       <c r="F54">
-        <v>33.54</v>
+        <v>34.185</v>
       </c>
       <c r="G54">
         <v>4.31</v>
@@ -5709,45 +5709,45 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M54">
-        <v>2.056002</v>
+        <v>2.1912585</v>
       </c>
       <c r="N54">
-        <v>5.233998000000001</v>
+        <v>5.098741500000001</v>
       </c>
       <c r="O54">
-        <v>1.25615952</v>
+        <v>1.22369796</v>
       </c>
       <c r="P54">
-        <v>3.977838480000001</v>
+        <v>3.875043540000001</v>
       </c>
       <c r="Q54">
-        <v>9.037838480000001</v>
+        <v>8.935043540000002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1427923942536505</v>
+        <v>0.1445844276765951</v>
       </c>
       <c r="T54">
-        <v>1.63543110848603</v>
+        <v>1.665647366470816</v>
       </c>
       <c r="U54">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.24</v>
       </c>
       <c r="W54">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.545716395217515</v>
+        <v>3.326855320812218</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09377416100799971</v>
+        <v>0.09367565277424719</v>
       </c>
       <c r="C55">
-        <v>32.08519028192747</v>
+        <v>31.56767865135864</v>
       </c>
       <c r="D55">
-        <v>61.96019028192747</v>
+        <v>62.08767865135864</v>
       </c>
       <c r="E55">
-        <v>1.484999999999999</v>
+        <v>2.130000000000003</v>
       </c>
       <c r="F55">
-        <v>34.185</v>
+        <v>34.83000000000001</v>
       </c>
       <c r="G55">
         <v>4.31</v>
@@ -5791,28 +5791,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M55">
-        <v>2.1912585</v>
+        <v>2.232603000000001</v>
       </c>
       <c r="N55">
-        <v>5.098741500000001</v>
+        <v>5.057397</v>
       </c>
       <c r="O55">
-        <v>1.22369796</v>
+        <v>1.21377528</v>
       </c>
       <c r="P55">
-        <v>3.875043540000001</v>
+        <v>3.84362172</v>
       </c>
       <c r="Q55">
-        <v>8.935043540000002</v>
+        <v>8.90362172</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1445844276765951</v>
+        <v>0.1464543755961895</v>
       </c>
       <c r="T55">
-        <v>1.665647366470816</v>
+        <v>1.697177374802767</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.326855320812218</v>
+        <v>3.265246888945325</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09367565277424719</v>
+        <v>0.09357714454049466</v>
       </c>
       <c r="C56">
-        <v>31.56767865135864</v>
+        <v>31.05069273885933</v>
       </c>
       <c r="D56">
-        <v>62.08767865135864</v>
+        <v>62.21569273885934</v>
       </c>
       <c r="E56">
-        <v>2.130000000000003</v>
+        <v>2.774999999999999</v>
       </c>
       <c r="F56">
-        <v>34.83000000000001</v>
+        <v>35.475</v>
       </c>
       <c r="G56">
         <v>4.31</v>
@@ -5873,28 +5873,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M56">
-        <v>2.232603000000001</v>
+        <v>2.2739475</v>
       </c>
       <c r="N56">
-        <v>5.057397</v>
+        <v>5.016052500000001</v>
       </c>
       <c r="O56">
-        <v>1.21377528</v>
+        <v>1.2038526</v>
       </c>
       <c r="P56">
-        <v>3.84362172</v>
+        <v>3.8121999</v>
       </c>
       <c r="Q56">
-        <v>8.90362172</v>
+        <v>8.872199900000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1464543755961895</v>
+        <v>0.1484074323122104</v>
       </c>
       <c r="T56">
-        <v>1.697177374802767</v>
+        <v>1.73010871683836</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.265246888945325</v>
+        <v>3.205878763691774</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09357714454049466</v>
+        <v>0.09347863630674215</v>
       </c>
       <c r="C57">
-        <v>31.05069273885933</v>
+        <v>30.53423580296806</v>
       </c>
       <c r="D57">
-        <v>62.21569273885934</v>
+        <v>62.34423580296806</v>
       </c>
       <c r="E57">
-        <v>2.774999999999999</v>
+        <v>3.420000000000002</v>
       </c>
       <c r="F57">
-        <v>35.475</v>
+        <v>36.12</v>
       </c>
       <c r="G57">
         <v>4.31</v>
@@ -5955,28 +5955,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M57">
-        <v>2.2739475</v>
+        <v>2.315292</v>
       </c>
       <c r="N57">
-        <v>5.016052500000001</v>
+        <v>4.974708000000001</v>
       </c>
       <c r="O57">
-        <v>1.2038526</v>
+        <v>1.19392992</v>
       </c>
       <c r="P57">
-        <v>3.8121999</v>
+        <v>3.78077808</v>
       </c>
       <c r="Q57">
-        <v>8.872199900000002</v>
+        <v>8.84077808</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1484074323122104</v>
+        <v>0.1504492643335049</v>
       </c>
       <c r="T57">
-        <v>1.73010871683836</v>
+        <v>1.764536938057389</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.205878763691774</v>
+        <v>3.148630928625849</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09347863630674215</v>
+        <v>0.09338012807298962</v>
       </c>
       <c r="C58">
-        <v>30.53423580296806</v>
+        <v>30.01831112920888</v>
       </c>
       <c r="D58">
-        <v>62.34423580296806</v>
+        <v>62.47331112920889</v>
       </c>
       <c r="E58">
-        <v>3.420000000000002</v>
+        <v>4.064999999999998</v>
       </c>
       <c r="F58">
-        <v>36.12</v>
+        <v>36.765</v>
       </c>
       <c r="G58">
         <v>4.31</v>
@@ -6037,28 +6037,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M58">
-        <v>2.315292</v>
+        <v>2.3566365</v>
       </c>
       <c r="N58">
-        <v>4.974708000000001</v>
+        <v>4.9333635</v>
       </c>
       <c r="O58">
-        <v>1.19392992</v>
+        <v>1.18400724</v>
       </c>
       <c r="P58">
-        <v>3.78077808</v>
+        <v>3.74935626</v>
       </c>
       <c r="Q58">
-        <v>8.84077808</v>
+        <v>8.809356260000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1504492643335049</v>
+        <v>0.1525860652860224</v>
       </c>
       <c r="T58">
-        <v>1.764536938057389</v>
+        <v>1.800566471891256</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.148630928625849</v>
+        <v>3.09339178952715</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09338012807298962</v>
+        <v>0.09328161983923711</v>
       </c>
       <c r="C59">
-        <v>30.01831112920888</v>
+        <v>29.50292203037119</v>
       </c>
       <c r="D59">
-        <v>62.47331112920889</v>
+        <v>62.60292203037119</v>
       </c>
       <c r="E59">
-        <v>4.064999999999998</v>
+        <v>4.710000000000001</v>
       </c>
       <c r="F59">
-        <v>36.765</v>
+        <v>37.41</v>
       </c>
       <c r="G59">
         <v>4.31</v>
@@ -6119,28 +6119,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M59">
-        <v>2.3566365</v>
+        <v>2.397981000000001</v>
       </c>
       <c r="N59">
-        <v>4.9333635</v>
+        <v>4.892019</v>
       </c>
       <c r="O59">
-        <v>1.18400724</v>
+        <v>1.17408456</v>
       </c>
       <c r="P59">
-        <v>3.74935626</v>
+        <v>3.717934440000001</v>
       </c>
       <c r="Q59">
-        <v>8.809356260000001</v>
+        <v>8.777934440000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1525860652860224</v>
+        <v>0.1548246186648503</v>
       </c>
       <c r="T59">
-        <v>1.800566471891256</v>
+        <v>1.838311697812451</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.09339178952715</v>
+        <v>3.040057448328406</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09328161983923711</v>
+        <v>0.0966806316054846</v>
       </c>
       <c r="C60">
-        <v>29.5029220303712</v>
+        <v>24.67581850947527</v>
       </c>
       <c r="D60">
-        <v>62.60292203037119</v>
+        <v>58.42081850947527</v>
       </c>
       <c r="E60">
-        <v>4.709999999999994</v>
+        <v>5.354999999999997</v>
       </c>
       <c r="F60">
-        <v>37.41</v>
+        <v>38.055</v>
       </c>
       <c r="G60">
         <v>4.31</v>
@@ -6201,45 +6201,45 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M60">
-        <v>2.397981</v>
+        <v>2.7361545</v>
       </c>
       <c r="N60">
-        <v>4.892019000000001</v>
+        <v>4.553845500000001</v>
       </c>
       <c r="O60">
-        <v>1.17408456</v>
+        <v>1.09292292</v>
       </c>
       <c r="P60">
-        <v>3.717934440000001</v>
+        <v>3.460922580000001</v>
       </c>
       <c r="Q60">
-        <v>8.777934440000001</v>
+        <v>8.520922580000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1548246186648503</v>
+        <v>0.1571723697694746</v>
       </c>
       <c r="T60">
-        <v>1.838311697812451</v>
+        <v>1.877898154266386</v>
       </c>
       <c r="U60">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V60">
         <v>0.24</v>
       </c>
       <c r="W60">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.040057448328407</v>
+        <v>2.66432323174733</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0966806316054846</v>
+        <v>0.09664140337173208</v>
       </c>
       <c r="C61">
-        <v>24.67581850947527</v>
+        <v>24.07589487189877</v>
       </c>
       <c r="D61">
-        <v>58.42081850947527</v>
+        <v>58.46589487189876</v>
       </c>
       <c r="E61">
-        <v>5.354999999999997</v>
+        <v>5.999999999999993</v>
       </c>
       <c r="F61">
-        <v>38.055</v>
+        <v>38.7</v>
       </c>
       <c r="G61">
         <v>4.31</v>
@@ -6283,28 +6283,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M61">
-        <v>2.7361545</v>
+        <v>2.78253</v>
       </c>
       <c r="N61">
-        <v>4.553845500000001</v>
+        <v>4.507470000000001</v>
       </c>
       <c r="O61">
-        <v>1.09292292</v>
+        <v>1.0817928</v>
       </c>
       <c r="P61">
-        <v>3.460922580000001</v>
+        <v>3.425677200000001</v>
       </c>
       <c r="Q61">
-        <v>8.520922580000001</v>
+        <v>8.485677200000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1571723697694746</v>
+        <v>0.1596375084293302</v>
       </c>
       <c r="T61">
-        <v>1.877898154266386</v>
+        <v>1.919463933543019</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.66432323174733</v>
+        <v>2.619917844551542</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09664140337173208</v>
+        <v>0.09660217513797956</v>
       </c>
       <c r="C62">
-        <v>24.07589487189877</v>
+        <v>23.47604084811643</v>
       </c>
       <c r="D62">
-        <v>58.46589487189876</v>
+        <v>58.51104084811643</v>
       </c>
       <c r="E62">
-        <v>5.999999999999993</v>
+        <v>6.644999999999996</v>
       </c>
       <c r="F62">
-        <v>38.7</v>
+        <v>39.345</v>
       </c>
       <c r="G62">
         <v>4.31</v>
@@ -6365,28 +6365,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M62">
-        <v>2.78253</v>
+        <v>2.8289055</v>
       </c>
       <c r="N62">
-        <v>4.507470000000001</v>
+        <v>4.461094500000001</v>
       </c>
       <c r="O62">
-        <v>1.0817928</v>
+        <v>1.07066268</v>
       </c>
       <c r="P62">
-        <v>3.425677200000001</v>
+        <v>3.390431820000001</v>
       </c>
       <c r="Q62">
-        <v>8.485677200000001</v>
+        <v>8.450431820000002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1596375084293302</v>
+        <v>0.1622290644563578</v>
       </c>
       <c r="T62">
-        <v>1.919463933543019</v>
+        <v>1.963161291244094</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.619917844551542</v>
+        <v>2.57696837169004</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09660217513797956</v>
+        <v>0.09656294690422704</v>
       </c>
       <c r="C63">
-        <v>23.47604084811643</v>
+        <v>22.87625659951525</v>
       </c>
       <c r="D63">
-        <v>58.51104084811643</v>
+        <v>58.55625659951525</v>
       </c>
       <c r="E63">
-        <v>6.644999999999996</v>
+        <v>7.289999999999999</v>
       </c>
       <c r="F63">
-        <v>39.345</v>
+        <v>39.99</v>
       </c>
       <c r="G63">
         <v>4.31</v>
@@ -6447,28 +6447,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M63">
-        <v>2.8289055</v>
+        <v>2.875281</v>
       </c>
       <c r="N63">
-        <v>4.461094500000001</v>
+        <v>4.414719000000001</v>
       </c>
       <c r="O63">
-        <v>1.07066268</v>
+        <v>1.05953256</v>
       </c>
       <c r="P63">
-        <v>3.390431820000001</v>
+        <v>3.355186440000001</v>
       </c>
       <c r="Q63">
-        <v>8.450431820000002</v>
+        <v>8.415186440000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1622290644563578</v>
+        <v>0.1649570181690185</v>
       </c>
       <c r="T63">
-        <v>1.963161291244094</v>
+        <v>2.009158509876805</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.57696837169004</v>
+        <v>2.53540436569504</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09656294690422704</v>
+        <v>0.09839103867047451</v>
       </c>
       <c r="C64">
-        <v>22.87625659951525</v>
+        <v>20.19581076581382</v>
       </c>
       <c r="D64">
-        <v>58.55625659951525</v>
+        <v>56.52081076581382</v>
       </c>
       <c r="E64">
-        <v>7.289999999999999</v>
+        <v>7.934999999999995</v>
       </c>
       <c r="F64">
-        <v>39.99</v>
+        <v>40.635</v>
       </c>
       <c r="G64">
         <v>4.31</v>
@@ -6529,45 +6529,45 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M64">
-        <v>2.875281</v>
+        <v>3.080133</v>
       </c>
       <c r="N64">
-        <v>4.414719000000001</v>
+        <v>4.209867000000001</v>
       </c>
       <c r="O64">
-        <v>1.05953256</v>
+        <v>1.01036808</v>
       </c>
       <c r="P64">
-        <v>3.355186440000001</v>
+        <v>3.199498920000001</v>
       </c>
       <c r="Q64">
-        <v>8.415186440000001</v>
+        <v>8.259498920000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1649570181690185</v>
+        <v>0.1678324288391203</v>
       </c>
       <c r="T64">
-        <v>2.009158509876805</v>
+        <v>2.057642064651824</v>
       </c>
       <c r="U64">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
         <v>0.24</v>
       </c>
       <c r="W64">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.53540436569504</v>
+        <v>2.36678091497997</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09839103867047451</v>
+        <v>0.098381450436722</v>
       </c>
       <c r="C65">
-        <v>20.19581076581382</v>
+        <v>19.56111734239174</v>
       </c>
       <c r="D65">
-        <v>56.52081076581382</v>
+        <v>56.53111734239174</v>
       </c>
       <c r="E65">
-        <v>7.934999999999995</v>
+        <v>8.579999999999998</v>
       </c>
       <c r="F65">
-        <v>40.635</v>
+        <v>41.28</v>
       </c>
       <c r="G65">
         <v>4.31</v>
@@ -6611,28 +6611,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M65">
-        <v>3.080133</v>
+        <v>3.129024</v>
       </c>
       <c r="N65">
-        <v>4.209867000000001</v>
+        <v>4.160976000000001</v>
       </c>
       <c r="O65">
-        <v>1.01036808</v>
+        <v>0.9986342400000001</v>
       </c>
       <c r="P65">
-        <v>3.199498920000001</v>
+        <v>3.16234176</v>
       </c>
       <c r="Q65">
-        <v>8.259498920000002</v>
+        <v>8.222341760000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1678324288391203</v>
+        <v>0.17086758454645</v>
       </c>
       <c r="T65">
-        <v>2.057642064651824</v>
+        <v>2.108819150247678</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.36678091497997</v>
+        <v>2.329799963183408</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.098381450436722</v>
+        <v>0.09837186220296948</v>
       </c>
       <c r="C66">
-        <v>19.56111734239174</v>
+        <v>18.92642767846614</v>
       </c>
       <c r="D66">
-        <v>56.53111734239174</v>
+        <v>56.54142767846614</v>
       </c>
       <c r="E66">
-        <v>8.579999999999998</v>
+        <v>9.225000000000001</v>
       </c>
       <c r="F66">
-        <v>41.28</v>
+        <v>41.925</v>
       </c>
       <c r="G66">
         <v>4.31</v>
@@ -6693,28 +6693,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M66">
-        <v>3.129024</v>
+        <v>3.177915</v>
       </c>
       <c r="N66">
-        <v>4.160976000000001</v>
+        <v>4.112085</v>
       </c>
       <c r="O66">
-        <v>0.9986342400000001</v>
+        <v>0.9869004000000001</v>
       </c>
       <c r="P66">
-        <v>3.16234176</v>
+        <v>3.1251846</v>
       </c>
       <c r="Q66">
-        <v>8.222341760000001</v>
+        <v>8.185184600000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.17086758454645</v>
+        <v>0.17407617772277</v>
       </c>
       <c r="T66">
-        <v>2.108819150247678</v>
+        <v>2.162920640734724</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.329799963183408</v>
+        <v>2.29395688682674</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09837186220296948</v>
+        <v>0.09836227396921696</v>
       </c>
       <c r="C67">
-        <v>18.92642767846614</v>
+        <v>18.29174177609442</v>
       </c>
       <c r="D67">
-        <v>56.54142767846614</v>
+        <v>56.55174177609442</v>
       </c>
       <c r="E67">
-        <v>9.225000000000001</v>
+        <v>9.869999999999997</v>
       </c>
       <c r="F67">
-        <v>41.925</v>
+        <v>42.57</v>
       </c>
       <c r="G67">
         <v>4.31</v>
@@ -6775,28 +6775,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M67">
-        <v>3.177915</v>
+        <v>3.226806</v>
       </c>
       <c r="N67">
-        <v>4.112085</v>
+        <v>4.063194000000001</v>
       </c>
       <c r="O67">
-        <v>0.9869004000000001</v>
+        <v>0.9751665600000002</v>
       </c>
       <c r="P67">
-        <v>3.1251846</v>
+        <v>3.088027440000001</v>
       </c>
       <c r="Q67">
-        <v>8.185184600000001</v>
+        <v>8.148027440000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.17407617772277</v>
+        <v>0.1774735116741675</v>
       </c>
       <c r="T67">
-        <v>2.162920640734724</v>
+        <v>2.220204571838654</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.29395688682674</v>
+        <v>2.259199964299063</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09836227396921696</v>
+        <v>0.09835268573546443</v>
       </c>
       <c r="C68">
-        <v>18.29174177609442</v>
+        <v>17.65705963733544</v>
       </c>
       <c r="D68">
-        <v>56.55174177609442</v>
+        <v>56.56205963733544</v>
       </c>
       <c r="E68">
-        <v>9.869999999999997</v>
+        <v>10.515</v>
       </c>
       <c r="F68">
-        <v>42.57</v>
+        <v>43.215</v>
       </c>
       <c r="G68">
         <v>4.31</v>
@@ -6857,28 +6857,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M68">
-        <v>3.226806</v>
+        <v>3.275697000000001</v>
       </c>
       <c r="N68">
-        <v>4.063194000000001</v>
+        <v>4.014303</v>
       </c>
       <c r="O68">
-        <v>0.9751665600000002</v>
+        <v>0.9634327199999999</v>
       </c>
       <c r="P68">
-        <v>3.088027440000001</v>
+        <v>3.05087028</v>
       </c>
       <c r="Q68">
-        <v>8.148027440000002</v>
+        <v>8.11087028</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1774735116741675</v>
+        <v>0.1810767446529225</v>
       </c>
       <c r="T68">
-        <v>2.220204571838654</v>
+        <v>2.280960256342823</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.259199964299063</v>
+        <v>2.225480561846837</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09835268573546443</v>
+        <v>0.09834309750171191</v>
       </c>
       <c r="C69">
-        <v>17.65705963733544</v>
+        <v>17.02238126424959</v>
       </c>
       <c r="D69">
-        <v>56.56205963733544</v>
+        <v>56.57238126424959</v>
       </c>
       <c r="E69">
-        <v>10.515</v>
+        <v>11.16</v>
       </c>
       <c r="F69">
-        <v>43.215</v>
+        <v>43.86000000000001</v>
       </c>
       <c r="G69">
         <v>4.31</v>
@@ -6939,28 +6939,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M69">
-        <v>3.275697000000001</v>
+        <v>3.324588000000001</v>
       </c>
       <c r="N69">
-        <v>4.014303</v>
+        <v>3.965412</v>
       </c>
       <c r="O69">
-        <v>0.9634327199999999</v>
+        <v>0.95169888</v>
       </c>
       <c r="P69">
-        <v>3.05087028</v>
+        <v>3.01371312</v>
       </c>
       <c r="Q69">
-        <v>8.11087028</v>
+        <v>8.073713120000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1810767446529225</v>
+        <v>0.1849051796928497</v>
       </c>
       <c r="T69">
-        <v>2.280960256342823</v>
+        <v>2.345513171128502</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.225480561846837</v>
+        <v>2.19275290652556</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09834309750171191</v>
+        <v>0.0983335092679594</v>
       </c>
       <c r="C70">
-        <v>17.02238126424959</v>
+        <v>16.38770665889876</v>
       </c>
       <c r="D70">
-        <v>56.57238126424959</v>
+        <v>56.58270665889876</v>
       </c>
       <c r="E70">
-        <v>11.16</v>
+        <v>11.805</v>
       </c>
       <c r="F70">
-        <v>43.86000000000001</v>
+        <v>44.505</v>
       </c>
       <c r="G70">
         <v>4.31</v>
@@ -7021,28 +7021,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M70">
-        <v>3.324588000000001</v>
+        <v>3.373479000000001</v>
       </c>
       <c r="N70">
-        <v>3.965412</v>
+        <v>3.916521</v>
       </c>
       <c r="O70">
-        <v>0.95169888</v>
+        <v>0.93996504</v>
       </c>
       <c r="P70">
-        <v>3.01371312</v>
+        <v>2.97655596</v>
       </c>
       <c r="Q70">
-        <v>8.073713120000001</v>
+        <v>8.036555960000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1849051796928497</v>
+        <v>0.1889806105418045</v>
       </c>
       <c r="T70">
-        <v>2.345513171128502</v>
+        <v>2.414230790093903</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.19275290652556</v>
+        <v>2.160973878894755</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0983335092679594</v>
+        <v>0.09832392103420688</v>
       </c>
       <c r="C71">
-        <v>16.38770665889876</v>
+        <v>15.75303582334638</v>
       </c>
       <c r="D71">
-        <v>56.58270665889876</v>
+        <v>56.59303582334638</v>
       </c>
       <c r="E71">
-        <v>11.805</v>
+        <v>12.45</v>
       </c>
       <c r="F71">
-        <v>44.505</v>
+        <v>45.15000000000001</v>
       </c>
       <c r="G71">
         <v>4.31</v>
@@ -7103,28 +7103,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M71">
-        <v>3.373479000000001</v>
+        <v>3.422370000000001</v>
       </c>
       <c r="N71">
-        <v>3.916521</v>
+        <v>3.86763</v>
       </c>
       <c r="O71">
-        <v>0.93996504</v>
+        <v>0.9282312</v>
       </c>
       <c r="P71">
-        <v>2.97655596</v>
+        <v>2.9393988</v>
       </c>
       <c r="Q71">
-        <v>8.036555960000001</v>
+        <v>7.999398800000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1889806105418045</v>
+        <v>0.1933277367806896</v>
       </c>
       <c r="T71">
-        <v>2.414230790093903</v>
+        <v>2.487529583656997</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.160973878894755</v>
+        <v>2.130102823481973</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09832392103420688</v>
+        <v>0.09831433280045436</v>
       </c>
       <c r="C72">
-        <v>15.75303582334638</v>
+        <v>15.11836875965733</v>
       </c>
       <c r="D72">
-        <v>56.59303582334638</v>
+        <v>56.60336875965733</v>
       </c>
       <c r="E72">
-        <v>12.45</v>
+        <v>13.095</v>
       </c>
       <c r="F72">
-        <v>45.15000000000001</v>
+        <v>45.795</v>
       </c>
       <c r="G72">
         <v>4.31</v>
@@ -7185,28 +7185,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M72">
-        <v>3.422370000000001</v>
+        <v>3.471261000000001</v>
       </c>
       <c r="N72">
-        <v>3.86763</v>
+        <v>3.818739</v>
       </c>
       <c r="O72">
-        <v>0.9282312</v>
+        <v>0.91649736</v>
       </c>
       <c r="P72">
-        <v>2.9393988</v>
+        <v>2.90224164</v>
       </c>
       <c r="Q72">
-        <v>7.999398800000001</v>
+        <v>7.96224164</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1933277367806896</v>
+        <v>0.197974664829153</v>
       </c>
       <c r="T72">
-        <v>2.487529583656997</v>
+        <v>2.565883466431339</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.130102823481973</v>
+        <v>2.100101375263917</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09831433280045437</v>
+        <v>0.09830474456670184</v>
       </c>
       <c r="C73">
-        <v>15.11836875965733</v>
+        <v>14.48370546989804</v>
       </c>
       <c r="D73">
-        <v>56.60336875965732</v>
+        <v>56.61370546989804</v>
       </c>
       <c r="E73">
-        <v>13.09499999999999</v>
+        <v>13.73999999999999</v>
       </c>
       <c r="F73">
-        <v>45.79499999999999</v>
+        <v>46.44</v>
       </c>
       <c r="G73">
         <v>4.31</v>
@@ -7267,28 +7267,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M73">
-        <v>3.471261</v>
+        <v>3.520152</v>
       </c>
       <c r="N73">
-        <v>3.818739000000001</v>
+        <v>3.769848000000001</v>
       </c>
       <c r="O73">
-        <v>0.9164973600000003</v>
+        <v>0.9047635200000002</v>
       </c>
       <c r="P73">
-        <v>2.902241640000001</v>
+        <v>2.865084480000001</v>
       </c>
       <c r="Q73">
-        <v>7.962241640000002</v>
+        <v>7.925084480000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.197974664829153</v>
+        <v>0.2029535163096494</v>
       </c>
       <c r="T73">
-        <v>2.565883466431338</v>
+        <v>2.649834055118133</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.100101375263917</v>
+        <v>2.070933300607474</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09830474456670184</v>
+        <v>0.09829515633294932</v>
       </c>
       <c r="C74">
-        <v>14.48370546989804</v>
+        <v>13.8490459561364</v>
       </c>
       <c r="D74">
-        <v>56.61370546989804</v>
+        <v>56.6240459561364</v>
       </c>
       <c r="E74">
-        <v>13.73999999999999</v>
+        <v>14.385</v>
       </c>
       <c r="F74">
-        <v>46.44</v>
+        <v>47.085</v>
       </c>
       <c r="G74">
         <v>4.31</v>
@@ -7349,28 +7349,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M74">
-        <v>3.520152</v>
+        <v>3.569043</v>
       </c>
       <c r="N74">
-        <v>3.769848000000001</v>
+        <v>3.720957000000001</v>
       </c>
       <c r="O74">
-        <v>0.9047635200000002</v>
+        <v>0.8930296800000002</v>
       </c>
       <c r="P74">
-        <v>2.865084480000001</v>
+        <v>2.827927320000001</v>
       </c>
       <c r="Q74">
-        <v>7.925084480000002</v>
+        <v>7.887927320000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2029535163096494</v>
+        <v>0.208301171603516</v>
       </c>
       <c r="T74">
-        <v>2.649834055118133</v>
+        <v>2.740003205929875</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.070933300607474</v>
+        <v>2.042564351284084</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09829515633294932</v>
+        <v>0.09828556809919679</v>
       </c>
       <c r="C75">
-        <v>13.8490459561364</v>
+        <v>13.21439022044188</v>
       </c>
       <c r="D75">
-        <v>56.6240459561364</v>
+        <v>56.63439022044187</v>
       </c>
       <c r="E75">
-        <v>14.385</v>
+        <v>15.02999999999999</v>
       </c>
       <c r="F75">
-        <v>47.085</v>
+        <v>47.73</v>
       </c>
       <c r="G75">
         <v>4.31</v>
@@ -7431,28 +7431,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M75">
-        <v>3.569043</v>
+        <v>3.617934</v>
       </c>
       <c r="N75">
-        <v>3.720957000000001</v>
+        <v>3.672066000000001</v>
       </c>
       <c r="O75">
-        <v>0.8930296800000002</v>
+        <v>0.8812958400000002</v>
       </c>
       <c r="P75">
-        <v>2.827927320000001</v>
+        <v>2.790770160000001</v>
       </c>
       <c r="Q75">
-        <v>7.887927320000001</v>
+        <v>7.850770160000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.208301171603516</v>
+        <v>0.2140601849969107</v>
       </c>
       <c r="T75">
-        <v>2.740003205929875</v>
+        <v>2.837108445265597</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.042564351284084</v>
+        <v>2.014962130320786</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09828556809919679</v>
+        <v>0.1063699798654443</v>
       </c>
       <c r="C76">
-        <v>13.21439022044188</v>
+        <v>5.010270476807911</v>
       </c>
       <c r="D76">
-        <v>56.63439022044187</v>
+        <v>49.07527047680791</v>
       </c>
       <c r="E76">
-        <v>15.02999999999999</v>
+        <v>15.675</v>
       </c>
       <c r="F76">
-        <v>47.73</v>
+        <v>48.375</v>
       </c>
       <c r="G76">
         <v>4.31</v>
@@ -7513,45 +7513,45 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M76">
-        <v>3.617934</v>
+        <v>4.35375</v>
       </c>
       <c r="N76">
-        <v>3.672066000000001</v>
+        <v>2.936250000000001</v>
       </c>
       <c r="O76">
-        <v>0.8812958400000002</v>
+        <v>0.7047000000000002</v>
       </c>
       <c r="P76">
-        <v>2.790770160000001</v>
+        <v>2.231550000000001</v>
       </c>
       <c r="Q76">
-        <v>7.850770160000001</v>
+        <v>7.291550000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2140601849969107</v>
+        <v>0.2202799194617771</v>
       </c>
       <c r="T76">
-        <v>2.837108445265597</v>
+        <v>2.941982103748178</v>
       </c>
       <c r="U76">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V76">
         <v>0.24</v>
       </c>
       <c r="W76">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.014962130320786</v>
+        <v>1.674418604651163</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1063699798654443</v>
+        <v>0.1064683116316918</v>
       </c>
       <c r="C77">
-        <v>5.010270476807911</v>
+        <v>4.285728819964817</v>
       </c>
       <c r="D77">
-        <v>49.07527047680791</v>
+        <v>48.99572881996482</v>
       </c>
       <c r="E77">
-        <v>15.675</v>
+        <v>16.32</v>
       </c>
       <c r="F77">
-        <v>48.375</v>
+        <v>49.02</v>
       </c>
       <c r="G77">
         <v>4.31</v>
@@ -7595,28 +7595,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M77">
-        <v>4.35375</v>
+        <v>4.4118</v>
       </c>
       <c r="N77">
-        <v>2.936250000000001</v>
+        <v>2.878200000000001</v>
       </c>
       <c r="O77">
-        <v>0.7047000000000002</v>
+        <v>0.690768</v>
       </c>
       <c r="P77">
-        <v>2.231550000000001</v>
+        <v>2.187432</v>
       </c>
       <c r="Q77">
-        <v>7.291550000000001</v>
+        <v>7.247432000000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2202799194617771</v>
+        <v>0.227017965132049</v>
       </c>
       <c r="T77">
-        <v>2.941982103748178</v>
+        <v>3.055595233770974</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.674418604651163</v>
+        <v>1.652386780905753</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1064683116316918</v>
+        <v>0.1065666433979392</v>
       </c>
       <c r="C78">
-        <v>4.285728819964817</v>
+        <v>3.56144458960344</v>
       </c>
       <c r="D78">
-        <v>48.99572881996482</v>
+        <v>48.91644458960344</v>
       </c>
       <c r="E78">
-        <v>16.32</v>
+        <v>16.965</v>
       </c>
       <c r="F78">
-        <v>49.02</v>
+        <v>49.665</v>
       </c>
       <c r="G78">
         <v>4.31</v>
@@ -7677,28 +7677,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M78">
-        <v>4.4118</v>
+        <v>4.46985</v>
       </c>
       <c r="N78">
-        <v>2.878200000000001</v>
+        <v>2.820150000000001</v>
       </c>
       <c r="O78">
-        <v>0.690768</v>
+        <v>0.6768360000000002</v>
       </c>
       <c r="P78">
-        <v>2.187432</v>
+        <v>2.143314000000001</v>
       </c>
       <c r="Q78">
-        <v>7.247432000000001</v>
+        <v>7.203314000000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.227017965132049</v>
+        <v>0.2343419278171271</v>
       </c>
       <c r="T78">
-        <v>3.055595233770974</v>
+        <v>3.179087766404447</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.652386780905753</v>
+        <v>1.630927212322561</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1065666433979392</v>
+        <v>0.1066649751641867</v>
       </c>
       <c r="C79">
-        <v>3.56144458960344</v>
+        <v>2.837416538050526</v>
       </c>
       <c r="D79">
-        <v>48.91644458960344</v>
+        <v>48.83741653805053</v>
       </c>
       <c r="E79">
-        <v>16.965</v>
+        <v>17.61</v>
       </c>
       <c r="F79">
-        <v>49.665</v>
+        <v>50.31</v>
       </c>
       <c r="G79">
         <v>4.31</v>
@@ -7759,28 +7759,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M79">
-        <v>4.46985</v>
+        <v>4.5279</v>
       </c>
       <c r="N79">
-        <v>2.820150000000001</v>
+        <v>2.762100000000001</v>
       </c>
       <c r="O79">
-        <v>0.6768360000000002</v>
+        <v>0.6629040000000003</v>
       </c>
       <c r="P79">
-        <v>2.143314000000001</v>
+        <v>2.099196000000001</v>
       </c>
       <c r="Q79">
-        <v>7.203314000000001</v>
+        <v>7.159196000000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2343419278171271</v>
+        <v>0.2423317052917578</v>
       </c>
       <c r="T79">
-        <v>3.179087766404447</v>
+        <v>3.313806892913691</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.630927212322561</v>
+        <v>1.610017889087657</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1066649751641867</v>
+        <v>0.1067633069304342</v>
       </c>
       <c r="C80">
-        <v>2.837416538050526</v>
+        <v>2.113643425682604</v>
       </c>
       <c r="D80">
-        <v>48.83741653805053</v>
+        <v>48.75864342568261</v>
       </c>
       <c r="E80">
-        <v>17.61</v>
+        <v>18.255</v>
       </c>
       <c r="F80">
-        <v>50.31</v>
+        <v>50.95500000000001</v>
       </c>
       <c r="G80">
         <v>4.31</v>
@@ -7841,28 +7841,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M80">
-        <v>4.5279</v>
+        <v>4.58595</v>
       </c>
       <c r="N80">
-        <v>2.762100000000001</v>
+        <v>2.704050000000001</v>
       </c>
       <c r="O80">
-        <v>0.6629040000000003</v>
+        <v>0.6489720000000001</v>
       </c>
       <c r="P80">
-        <v>2.099196000000001</v>
+        <v>2.055078</v>
       </c>
       <c r="Q80">
-        <v>7.159196000000001</v>
+        <v>7.115078</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2423317052917578</v>
+        <v>0.2510824139544486</v>
       </c>
       <c r="T80">
-        <v>3.313806892913691</v>
+        <v>3.461356412423815</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.610017889087657</v>
+        <v>1.589637915808066</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1067633069304342</v>
+        <v>0.1068616386966817</v>
       </c>
       <c r="C81">
-        <v>2.113643425682604</v>
+        <v>1.390124020861293</v>
       </c>
       <c r="D81">
-        <v>48.75864342568261</v>
+        <v>48.68012402086129</v>
       </c>
       <c r="E81">
-        <v>18.255</v>
+        <v>18.9</v>
       </c>
       <c r="F81">
-        <v>50.95500000000001</v>
+        <v>51.6</v>
       </c>
       <c r="G81">
         <v>4.31</v>
@@ -7923,28 +7923,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M81">
-        <v>4.58595</v>
+        <v>4.644</v>
       </c>
       <c r="N81">
-        <v>2.704050000000001</v>
+        <v>2.646000000000001</v>
       </c>
       <c r="O81">
-        <v>0.6489720000000001</v>
+        <v>0.6350400000000002</v>
       </c>
       <c r="P81">
-        <v>2.055078</v>
+        <v>2.010960000000001</v>
       </c>
       <c r="Q81">
-        <v>7.115078</v>
+        <v>7.070960000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2510824139544486</v>
+        <v>0.2607081934834084</v>
       </c>
       <c r="T81">
-        <v>3.461356412423815</v>
+        <v>3.623660883884952</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.589637915808066</v>
+        <v>1.569767441860465</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1068616386966817</v>
+        <v>0.1069599704629292</v>
       </c>
       <c r="C82">
-        <v>1.390124020861293</v>
+        <v>0.6668570998689205</v>
       </c>
       <c r="D82">
-        <v>48.68012402086129</v>
+        <v>48.60185709986892</v>
       </c>
       <c r="E82">
-        <v>18.9</v>
+        <v>19.545</v>
       </c>
       <c r="F82">
-        <v>51.6</v>
+        <v>52.245</v>
       </c>
       <c r="G82">
         <v>4.31</v>
@@ -8005,28 +8005,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M82">
-        <v>4.644</v>
+        <v>4.70205</v>
       </c>
       <c r="N82">
-        <v>2.646000000000001</v>
+        <v>2.587950000000001</v>
       </c>
       <c r="O82">
-        <v>0.6350400000000002</v>
+        <v>0.6211080000000002</v>
       </c>
       <c r="P82">
-        <v>2.010960000000001</v>
+        <v>1.966842000000001</v>
       </c>
       <c r="Q82">
-        <v>7.070960000000001</v>
+        <v>7.026842000000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2607081934834084</v>
+        <v>0.2713472129627851</v>
       </c>
       <c r="T82">
-        <v>3.623660883884952</v>
+        <v>3.803050036552524</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.569767441860465</v>
+        <v>1.550387596899225</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1069599704629292</v>
+        <v>0.1070583022291766</v>
       </c>
       <c r="C83">
-        <v>0.6668570998689205</v>
+        <v>-0.05615855315487295</v>
       </c>
       <c r="D83">
-        <v>48.60185709986892</v>
+        <v>48.52384144684513</v>
       </c>
       <c r="E83">
-        <v>19.545</v>
+        <v>20.19</v>
       </c>
       <c r="F83">
-        <v>52.245</v>
+        <v>52.89</v>
       </c>
       <c r="G83">
         <v>4.31</v>
@@ -8087,28 +8087,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M83">
-        <v>4.70205</v>
+        <v>4.7601</v>
       </c>
       <c r="N83">
-        <v>2.587950000000001</v>
+        <v>2.529900000000001</v>
       </c>
       <c r="O83">
-        <v>0.6211080000000002</v>
+        <v>0.6071760000000003</v>
       </c>
       <c r="P83">
-        <v>1.966842000000001</v>
+        <v>1.922724000000001</v>
       </c>
       <c r="Q83">
-        <v>7.026842000000001</v>
+        <v>6.982724000000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2713472129627851</v>
+        <v>0.283168345717648</v>
       </c>
       <c r="T83">
-        <v>3.803050036552524</v>
+        <v>4.002371317294271</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.550387596899225</v>
+        <v>1.531480431083381</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1070583022291766</v>
+        <v>0.1071566339954241</v>
       </c>
       <c r="C84">
-        <v>-0.05615855315487295</v>
+        <v>-0.7789241462761822</v>
       </c>
       <c r="D84">
-        <v>48.52384144684513</v>
+        <v>48.44607585372382</v>
       </c>
       <c r="E84">
-        <v>20.19</v>
+        <v>20.835</v>
       </c>
       <c r="F84">
-        <v>52.89</v>
+        <v>53.535</v>
       </c>
       <c r="G84">
         <v>4.31</v>
@@ -8169,28 +8169,28 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M84">
-        <v>4.7601</v>
+        <v>4.81815</v>
       </c>
       <c r="N84">
-        <v>2.529900000000001</v>
+        <v>2.471850000000001</v>
       </c>
       <c r="O84">
-        <v>0.6071760000000003</v>
+        <v>0.5932440000000002</v>
       </c>
       <c r="P84">
-        <v>1.922724000000001</v>
+        <v>1.878606</v>
       </c>
       <c r="Q84">
-        <v>6.982724000000001</v>
+        <v>6.938606000000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.283168345717648</v>
+        <v>0.2963801999730831</v>
       </c>
       <c r="T84">
-        <v>4.002371317294271</v>
+        <v>4.225142160476223</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.531480431083381</v>
+        <v>1.513028859624545</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1071566339954241</v>
+        <v>0.1468801703321021</v>
       </c>
       <c r="C85">
-        <v>-0.7789241462761822</v>
+        <v>-20.46276676221179</v>
       </c>
       <c r="D85">
-        <v>48.44607585372382</v>
+        <v>29.40723323778821</v>
       </c>
       <c r="E85">
-        <v>20.835</v>
+        <v>21.48</v>
       </c>
       <c r="F85">
-        <v>53.535</v>
+        <v>54.18000000000001</v>
       </c>
       <c r="G85">
         <v>4.31</v>
@@ -8251,45 +8251,45 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M85">
-        <v>4.81815</v>
+        <v>7.953624000000001</v>
       </c>
       <c r="N85">
-        <v>2.471850000000001</v>
+        <v>-0.6636240000000004</v>
       </c>
       <c r="O85">
-        <v>0.5932440000000002</v>
+        <v>-0.1592697600000001</v>
       </c>
       <c r="P85">
-        <v>1.878606</v>
+        <v>-0.5043542400000003</v>
       </c>
       <c r="Q85">
-        <v>6.938606000000001</v>
+        <v>4.55564576</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2963801999730831</v>
+        <v>0.3168359482965685</v>
       </c>
       <c r="T85">
-        <v>4.225142160476223</v>
+        <v>4.570055464380253</v>
       </c>
       <c r="U85">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.24</v>
+        <v>0.2199751962124435</v>
       </c>
       <c r="W85">
-        <v>0.0684</v>
+        <v>0.1145076411960133</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>1.513028859624545</v>
+        <v>0.9165633175518481</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1468801703321021</v>
+        <v>0.1478901703321021</v>
       </c>
       <c r="C86">
-        <v>-20.46276676221179</v>
+        <v>-21.3986988418973</v>
       </c>
       <c r="D86">
-        <v>29.40723323778821</v>
+        <v>29.1163011581027</v>
       </c>
       <c r="E86">
-        <v>21.48</v>
+        <v>22.12499999999999</v>
       </c>
       <c r="F86">
-        <v>54.18</v>
+        <v>54.825</v>
       </c>
       <c r="G86">
         <v>4.31</v>
@@ -8333,37 +8333,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M86">
-        <v>7.953624</v>
+        <v>8.048310000000001</v>
       </c>
       <c r="N86">
-        <v>-0.6636239999999995</v>
+        <v>-0.7583099999999998</v>
       </c>
       <c r="O86">
-        <v>-0.1592697599999999</v>
+        <v>-0.1819943999999999</v>
       </c>
       <c r="P86">
-        <v>-0.5043542399999996</v>
+        <v>-0.5763155999999998</v>
       </c>
       <c r="Q86">
-        <v>4.555645760000001</v>
+        <v>4.4836844</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3168359482965683</v>
+        <v>0.3349050115163395</v>
       </c>
       <c r="T86">
-        <v>4.570055464380251</v>
+        <v>4.874725828672267</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2199751962124435</v>
+        <v>0.2173872527275912</v>
       </c>
       <c r="W86">
-        <v>0.1145076411960133</v>
+        <v>0.1148875512995896</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9165633175518482</v>
+        <v>0.9057802196982969</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1478901703321021</v>
+        <v>0.1489001703321021</v>
       </c>
       <c r="C87">
-        <v>-21.3986988418973</v>
+        <v>-22.32893080683933</v>
       </c>
       <c r="D87">
-        <v>29.1163011581027</v>
+        <v>28.83106919316067</v>
       </c>
       <c r="E87">
-        <v>22.12499999999999</v>
+        <v>22.77</v>
       </c>
       <c r="F87">
-        <v>54.825</v>
+        <v>55.47</v>
       </c>
       <c r="G87">
         <v>4.31</v>
@@ -8415,37 +8415,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M87">
-        <v>8.048310000000001</v>
+        <v>8.142996</v>
       </c>
       <c r="N87">
-        <v>-0.7583099999999998</v>
+        <v>-0.8529959999999992</v>
       </c>
       <c r="O87">
-        <v>-0.1819943999999999</v>
+        <v>-0.2047190399999998</v>
       </c>
       <c r="P87">
-        <v>-0.5763155999999998</v>
+        <v>-0.6482769599999993</v>
       </c>
       <c r="Q87">
-        <v>4.4836844</v>
+        <v>4.411723040000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3349050115163395</v>
+        <v>0.3555553694817923</v>
       </c>
       <c r="T87">
-        <v>4.874725828672267</v>
+        <v>5.222920530720287</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2173872527275912</v>
+        <v>0.2148594939749449</v>
       </c>
       <c r="W87">
-        <v>0.1148875512995896</v>
+        <v>0.1152586262844781</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9057802196982969</v>
+        <v>0.8952478915622704</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1489001703321021</v>
+        <v>0.1499101703321021</v>
       </c>
       <c r="C88">
-        <v>-22.32893080683933</v>
+        <v>-23.25362855195111</v>
       </c>
       <c r="D88">
-        <v>28.83106919316067</v>
+        <v>28.55137144804889</v>
       </c>
       <c r="E88">
-        <v>22.77</v>
+        <v>23.415</v>
       </c>
       <c r="F88">
-        <v>55.47</v>
+        <v>56.115</v>
       </c>
       <c r="G88">
         <v>4.31</v>
@@ -8497,37 +8497,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M88">
-        <v>8.142996</v>
+        <v>8.237682000000001</v>
       </c>
       <c r="N88">
-        <v>-0.8529959999999992</v>
+        <v>-0.9476820000000004</v>
       </c>
       <c r="O88">
-        <v>-0.2047190399999998</v>
+        <v>-0.2274436800000001</v>
       </c>
       <c r="P88">
-        <v>-0.6482769599999993</v>
+        <v>-0.7202383200000003</v>
       </c>
       <c r="Q88">
-        <v>4.411723040000001</v>
+        <v>4.339761680000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3555553694817923</v>
+        <v>0.3793827055957764</v>
       </c>
       <c r="T88">
-        <v>5.222920530720287</v>
+        <v>5.624683648468001</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2148594939749449</v>
+        <v>0.212389844618911</v>
       </c>
       <c r="W88">
-        <v>0.1152586262844781</v>
+        <v>0.1156211708099439</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8952478915622704</v>
+        <v>0.8849576859121291</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1499101703321021</v>
+        <v>0.1509201703321021</v>
       </c>
       <c r="C89">
-        <v>-23.25362855195111</v>
+        <v>-24.17295159643844</v>
       </c>
       <c r="D89">
-        <v>28.55137144804889</v>
+        <v>28.27704840356155</v>
       </c>
       <c r="E89">
-        <v>23.415</v>
+        <v>24.06</v>
       </c>
       <c r="F89">
-        <v>56.115</v>
+        <v>56.76</v>
       </c>
       <c r="G89">
         <v>4.31</v>
@@ -8579,37 +8579,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M89">
-        <v>8.237682000000001</v>
+        <v>8.332368000000001</v>
       </c>
       <c r="N89">
-        <v>-0.9476820000000004</v>
+        <v>-1.042368</v>
       </c>
       <c r="O89">
-        <v>-0.2274436800000001</v>
+        <v>-0.2501683199999999</v>
       </c>
       <c r="P89">
-        <v>-0.7202383200000003</v>
+        <v>-0.7921996799999997</v>
       </c>
       <c r="Q89">
-        <v>4.339761680000001</v>
+        <v>4.267800320000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3793827055957764</v>
+        <v>0.4071812643954245</v>
       </c>
       <c r="T89">
-        <v>5.624683648468001</v>
+        <v>6.093407285840335</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.212389844618911</v>
+        <v>0.2099763236573325</v>
       </c>
       <c r="W89">
-        <v>0.1156211708099439</v>
+        <v>0.1159754756871036</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8849576859121291</v>
+        <v>0.8749013485722187</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1509201703321021</v>
+        <v>0.1519301703321021</v>
       </c>
       <c r="C90">
-        <v>-24.17295159643844</v>
+        <v>-25.08705338717551</v>
       </c>
       <c r="D90">
-        <v>28.27704840356155</v>
+        <v>28.00794661282449</v>
       </c>
       <c r="E90">
-        <v>24.06</v>
+        <v>24.705</v>
       </c>
       <c r="F90">
-        <v>56.76</v>
+        <v>57.405</v>
       </c>
       <c r="G90">
         <v>4.31</v>
@@ -8661,37 +8661,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M90">
-        <v>8.332368000000001</v>
+        <v>8.427054000000002</v>
       </c>
       <c r="N90">
-        <v>-1.042368</v>
+        <v>-1.137054000000001</v>
       </c>
       <c r="O90">
-        <v>-0.2501683199999999</v>
+        <v>-0.2728929600000002</v>
       </c>
       <c r="P90">
-        <v>-0.7921996799999997</v>
+        <v>-0.8641610400000007</v>
       </c>
       <c r="Q90">
-        <v>4.267800320000001</v>
+        <v>4.19583896</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4071812643954245</v>
+        <v>0.4400341066131904</v>
       </c>
       <c r="T90">
-        <v>6.093407285840335</v>
+        <v>6.647353402734912</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2099763236573325</v>
+        <v>0.2076170391218568</v>
       </c>
       <c r="W90">
-        <v>0.1159754756871036</v>
+        <v>0.1163218186569114</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8749013485722187</v>
+        <v>0.86507099634107</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1519301703321021</v>
+        <v>0.1529401703321021</v>
       </c>
       <c r="C91">
-        <v>-25.08705338717551</v>
+        <v>-25.99608158492121</v>
       </c>
       <c r="D91">
-        <v>28.00794661282449</v>
+        <v>27.7439184150788</v>
       </c>
       <c r="E91">
-        <v>24.705</v>
+        <v>25.35</v>
       </c>
       <c r="F91">
-        <v>57.405</v>
+        <v>58.05</v>
       </c>
       <c r="G91">
         <v>4.31</v>
@@ -8743,37 +8743,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M91">
-        <v>8.427054000000002</v>
+        <v>8.521740000000001</v>
       </c>
       <c r="N91">
-        <v>-1.137054000000001</v>
+        <v>-1.23174</v>
       </c>
       <c r="O91">
-        <v>-0.2728929600000002</v>
+        <v>-0.2956176</v>
       </c>
       <c r="P91">
-        <v>-0.8641610400000007</v>
+        <v>-0.9361224000000002</v>
       </c>
       <c r="Q91">
-        <v>4.19583896</v>
+        <v>4.1238776</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4400341066131904</v>
+        <v>0.4794575172745094</v>
       </c>
       <c r="T91">
-        <v>6.647353402734912</v>
+        <v>7.312088743008403</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2076170391218568</v>
+        <v>0.2053101831316139</v>
       </c>
       <c r="W91">
-        <v>0.1163218186569114</v>
+        <v>0.1166604651162791</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.86507099634107</v>
+        <v>0.8554590963817248</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1529401703321021</v>
+        <v>0.1539501703321021</v>
       </c>
       <c r="C92">
-        <v>-25.99608158492121</v>
+        <v>-26.90017833449805</v>
       </c>
       <c r="D92">
-        <v>27.7439184150788</v>
+        <v>27.48482166550195</v>
       </c>
       <c r="E92">
-        <v>25.35</v>
+        <v>25.995</v>
       </c>
       <c r="F92">
-        <v>58.05</v>
+        <v>58.695</v>
       </c>
       <c r="G92">
         <v>4.31</v>
@@ -8825,37 +8825,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M92">
-        <v>8.521740000000001</v>
+        <v>8.616426000000001</v>
       </c>
       <c r="N92">
-        <v>-1.23174</v>
+        <v>-1.326426</v>
       </c>
       <c r="O92">
-        <v>-0.2956176</v>
+        <v>-0.3183422399999999</v>
       </c>
       <c r="P92">
-        <v>-0.9361224000000002</v>
+        <v>-1.00808376</v>
       </c>
       <c r="Q92">
-        <v>4.1238776</v>
+        <v>4.051916240000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4794575172745094</v>
+        <v>0.527641685860566</v>
       </c>
       <c r="T92">
-        <v>7.312088743008403</v>
+        <v>8.124543047787116</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2053101831316139</v>
+        <v>0.2030540272730248</v>
       </c>
       <c r="W92">
-        <v>0.1166604651162791</v>
+        <v>0.11699166879632</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8554590963817248</v>
+        <v>0.8460584469709367</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1539501703321021</v>
+        <v>0.1549601703321021</v>
       </c>
       <c r="C93">
-        <v>-26.90017833449805</v>
+        <v>-27.79948051997195</v>
       </c>
       <c r="D93">
-        <v>27.48482166550195</v>
+        <v>27.23051948002805</v>
       </c>
       <c r="E93">
-        <v>25.995</v>
+        <v>26.64</v>
       </c>
       <c r="F93">
-        <v>58.695</v>
+        <v>59.34</v>
       </c>
       <c r="G93">
         <v>4.31</v>
@@ -8907,37 +8907,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M93">
-        <v>8.616426000000001</v>
+        <v>8.711112000000002</v>
       </c>
       <c r="N93">
-        <v>-1.326426</v>
+        <v>-1.421112000000001</v>
       </c>
       <c r="O93">
-        <v>-0.3183422399999999</v>
+        <v>-0.3410668800000002</v>
       </c>
       <c r="P93">
-        <v>-1.00808376</v>
+        <v>-1.080045120000001</v>
       </c>
       <c r="Q93">
-        <v>4.051916240000001</v>
+        <v>3.97995488</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.527641685860566</v>
+        <v>0.5878718965931369</v>
       </c>
       <c r="T93">
-        <v>8.124543047787116</v>
+        <v>9.140110928760507</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2030540272730248</v>
+        <v>0.2008469182809267</v>
       </c>
       <c r="W93">
-        <v>0.11699166879632</v>
+        <v>0.11731567239636</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8460584469709367</v>
+        <v>0.8368621595038612</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1549601703321021</v>
+        <v>0.1559701703321021</v>
       </c>
       <c r="C94">
-        <v>-27.79948051997195</v>
+        <v>-28.69412000579577</v>
       </c>
       <c r="D94">
-        <v>27.23051948002805</v>
+        <v>26.98087999420424</v>
       </c>
       <c r="E94">
-        <v>26.64</v>
+        <v>27.285</v>
       </c>
       <c r="F94">
-        <v>59.34</v>
+        <v>59.98500000000001</v>
       </c>
       <c r="G94">
         <v>4.31</v>
@@ -8989,37 +8989,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M94">
-        <v>8.711112000000002</v>
+        <v>8.805798000000001</v>
       </c>
       <c r="N94">
-        <v>-1.421112000000001</v>
+        <v>-1.515798</v>
       </c>
       <c r="O94">
-        <v>-0.3410668800000002</v>
+        <v>-0.36379152</v>
       </c>
       <c r="P94">
-        <v>-1.080045120000001</v>
+        <v>-1.15200648</v>
       </c>
       <c r="Q94">
-        <v>3.97995488</v>
+        <v>3.90799352</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5878718965931369</v>
+        <v>0.6653107389635851</v>
       </c>
       <c r="T94">
-        <v>9.140110928760507</v>
+        <v>10.44584106144058</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2008469182809267</v>
+        <v>0.1986872739983361</v>
       </c>
       <c r="W94">
-        <v>0.11731567239636</v>
+        <v>0.1176327081770443</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8368621595038612</v>
+        <v>0.8278636416597337</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1559701703321021</v>
+        <v>0.1569801703321021</v>
       </c>
       <c r="C95">
-        <v>-28.69412000579577</v>
+        <v>-29.584223864809</v>
       </c>
       <c r="D95">
-        <v>26.98087999420424</v>
+        <v>26.73577613519101</v>
       </c>
       <c r="E95">
-        <v>27.285</v>
+        <v>27.93</v>
       </c>
       <c r="F95">
-        <v>59.98500000000001</v>
+        <v>60.63</v>
       </c>
       <c r="G95">
         <v>4.31</v>
@@ -9071,37 +9071,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M95">
-        <v>8.805798000000001</v>
+        <v>8.900484000000001</v>
       </c>
       <c r="N95">
-        <v>-1.515798</v>
+        <v>-1.610484</v>
       </c>
       <c r="O95">
-        <v>-0.36379152</v>
+        <v>-0.3865161599999999</v>
       </c>
       <c r="P95">
-        <v>-1.15200648</v>
+        <v>-1.22396784</v>
       </c>
       <c r="Q95">
-        <v>3.90799352</v>
+        <v>3.836032160000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6653107389635851</v>
+        <v>0.7685625287908494</v>
       </c>
       <c r="T95">
-        <v>10.44584106144058</v>
+        <v>12.18681457168068</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1986872739983361</v>
+        <v>0.1965735795940985</v>
       </c>
       <c r="W95">
-        <v>0.1176327081770443</v>
+        <v>0.1179429985155864</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8278636416597337</v>
+        <v>0.8190565816420771</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1569801703321021</v>
+        <v>0.1579901703321021</v>
       </c>
       <c r="C96">
-        <v>-29.584223864809</v>
+        <v>-30.46991459392198</v>
       </c>
       <c r="D96">
-        <v>26.73577613519101</v>
+        <v>26.49508540607802</v>
       </c>
       <c r="E96">
-        <v>27.93</v>
+        <v>28.575</v>
       </c>
       <c r="F96">
-        <v>60.63</v>
+        <v>61.27500000000001</v>
       </c>
       <c r="G96">
         <v>4.31</v>
@@ -9153,37 +9153,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M96">
-        <v>8.900484000000001</v>
+        <v>8.995170000000002</v>
       </c>
       <c r="N96">
-        <v>-1.610484</v>
+        <v>-1.705170000000001</v>
       </c>
       <c r="O96">
-        <v>-0.3865161599999999</v>
+        <v>-0.4092408000000002</v>
       </c>
       <c r="P96">
-        <v>-1.22396784</v>
+        <v>-1.295929200000001</v>
       </c>
       <c r="Q96">
-        <v>3.836032160000001</v>
+        <v>3.7640708</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7685625287908494</v>
+        <v>0.9131150345490197</v>
       </c>
       <c r="T96">
-        <v>12.18681457168068</v>
+        <v>14.62417748601682</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1965735795940985</v>
+        <v>0.1945043840194237</v>
       </c>
       <c r="W96">
-        <v>0.1179429985155864</v>
+        <v>0.1182467564259486</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8190565816420771</v>
+        <v>0.8104349334142656</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1579901703321021</v>
+        <v>0.1590001703321021</v>
       </c>
       <c r="C97">
-        <v>-30.46991459392198</v>
+        <v>-31.35131031825376</v>
       </c>
       <c r="D97">
-        <v>26.49508540607802</v>
+        <v>26.25868968174624</v>
       </c>
       <c r="E97">
-        <v>28.575</v>
+        <v>29.22</v>
       </c>
       <c r="F97">
-        <v>61.27500000000001</v>
+        <v>61.92</v>
       </c>
       <c r="G97">
         <v>4.31</v>
@@ -9235,37 +9235,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M97">
-        <v>8.995170000000002</v>
+        <v>9.089856000000001</v>
       </c>
       <c r="N97">
-        <v>-1.705170000000001</v>
+        <v>-1.799856</v>
       </c>
       <c r="O97">
-        <v>-0.4092408000000002</v>
+        <v>-0.43196544</v>
       </c>
       <c r="P97">
-        <v>-1.295929200000001</v>
+        <v>-1.36789056</v>
       </c>
       <c r="Q97">
-        <v>3.7640708</v>
+        <v>3.69210944</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9131150345490197</v>
+        <v>1.129943793186275</v>
       </c>
       <c r="T97">
-        <v>14.62417748601682</v>
+        <v>18.28022185752104</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1945043840194237</v>
+        <v>0.1924782966858881</v>
       </c>
       <c r="W97">
-        <v>0.1182467564259486</v>
+        <v>0.1185441860465116</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8104349334142656</v>
+        <v>0.8019929028578671</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1590001703321021</v>
+        <v>0.2150335202631247</v>
       </c>
       <c r="C98">
-        <v>-31.35131031825376</v>
+        <v>-40.69058285586771</v>
       </c>
       <c r="D98">
-        <v>26.25868968174624</v>
+        <v>17.56441714413229</v>
       </c>
       <c r="E98">
-        <v>29.21999999999999</v>
+        <v>29.86499999999999</v>
       </c>
       <c r="F98">
-        <v>61.91999999999999</v>
+        <v>62.565</v>
       </c>
       <c r="G98">
         <v>4.31</v>
@@ -9317,45 +9317,45 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M98">
-        <v>9.089855999999999</v>
+        <v>12.563052</v>
       </c>
       <c r="N98">
-        <v>-1.799855999999998</v>
+        <v>-5.273052</v>
       </c>
       <c r="O98">
-        <v>-0.4319654399999996</v>
+        <v>-1.26553248</v>
       </c>
       <c r="P98">
-        <v>-1.367890559999999</v>
+        <v>-4.00751952</v>
       </c>
       <c r="Q98">
-        <v>3.692109440000002</v>
+        <v>1.052480480000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.129943793186272</v>
+        <v>1.579436721949118</v>
       </c>
       <c r="T98">
-        <v>18.28022185752099</v>
+        <v>25.85931838771707</v>
       </c>
       <c r="U98">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1924782966858881</v>
+        <v>0.1392655224224177</v>
       </c>
       <c r="W98">
-        <v>0.1185441860465116</v>
+        <v>0.1728354830975785</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.8019929028578672</v>
+        <v>0.5802730100934073</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2150335202631247</v>
+        <v>0.2165835202631247</v>
       </c>
       <c r="C99">
-        <v>-40.69058285586771</v>
+        <v>-41.49499429399395</v>
       </c>
       <c r="D99">
-        <v>17.56441714413229</v>
+        <v>17.40500570600605</v>
       </c>
       <c r="E99">
-        <v>29.86499999999999</v>
+        <v>30.51</v>
       </c>
       <c r="F99">
-        <v>62.565</v>
+        <v>63.21</v>
       </c>
       <c r="G99">
         <v>4.31</v>
@@ -9399,37 +9399,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M99">
-        <v>12.563052</v>
+        <v>12.692568</v>
       </c>
       <c r="N99">
-        <v>-5.273052</v>
+        <v>-5.402568</v>
       </c>
       <c r="O99">
-        <v>-1.26553248</v>
+        <v>-1.29661632</v>
       </c>
       <c r="P99">
-        <v>-4.00751952</v>
+        <v>-4.10595168</v>
       </c>
       <c r="Q99">
-        <v>1.052480480000001</v>
+        <v>0.9540483200000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.579436721949118</v>
+        <v>2.346255082923677</v>
       </c>
       <c r="T99">
-        <v>25.85931838771707</v>
+        <v>38.7889775815756</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1392655224224177</v>
+        <v>0.1378444456630053</v>
       </c>
       <c r="W99">
-        <v>0.1728354830975785</v>
+        <v>0.1731208353108686</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5802730100934073</v>
+        <v>0.5743518569291888</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2165835202631247</v>
+        <v>0.2181335202631247</v>
       </c>
       <c r="C100">
-        <v>-41.49499429399395</v>
+        <v>-42.29653817938037</v>
       </c>
       <c r="D100">
-        <v>17.40500570600605</v>
+        <v>17.24846182061963</v>
       </c>
       <c r="E100">
-        <v>30.51</v>
+        <v>31.15499999999999</v>
       </c>
       <c r="F100">
-        <v>63.21</v>
+        <v>63.855</v>
       </c>
       <c r="G100">
         <v>4.31</v>
@@ -9481,37 +9481,37 @@
         <v>7.290000000000001</v>
       </c>
       <c r="M100">
-        <v>12.692568</v>
+        <v>12.822084</v>
       </c>
       <c r="N100">
-        <v>-5.402568</v>
+        <v>-5.532083999999999</v>
       </c>
       <c r="O100">
-        <v>-1.29661632</v>
+        <v>-1.32770016</v>
       </c>
       <c r="P100">
-        <v>-4.10595168</v>
+        <v>-4.204383839999999</v>
       </c>
       <c r="Q100">
-        <v>0.9540483200000001</v>
+        <v>0.8556161600000012</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.346255082923677</v>
+        <v>4.646710165847353</v>
       </c>
       <c r="T100">
-        <v>38.7889775815756</v>
+        <v>77.5779551631512</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1378444456630053</v>
+        <v>0.1364520775249952</v>
       </c>
       <c r="W100">
-        <v>0.1731208353108686</v>
+        <v>0.173400422832981</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5743518569291888</v>
+        <v>0.5685503230208132</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2181335202631247</v>
-      </c>
-      <c r="C101">
-        <v>-42.29653817938037</v>
-      </c>
-      <c r="D101">
-        <v>17.24846182061963</v>
-      </c>
-      <c r="E101">
-        <v>31.15499999999999</v>
-      </c>
-      <c r="F101">
-        <v>63.855</v>
-      </c>
-      <c r="G101">
-        <v>4.31</v>
-      </c>
-      <c r="H101">
-        <v>31.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.35</v>
-      </c>
-      <c r="K101">
-        <v>5.06</v>
-      </c>
-      <c r="L101">
-        <v>7.290000000000001</v>
-      </c>
-      <c r="M101">
-        <v>12.822084</v>
-      </c>
-      <c r="N101">
-        <v>-5.532083999999999</v>
-      </c>
-      <c r="O101">
-        <v>-1.32770016</v>
-      </c>
-      <c r="P101">
-        <v>-4.204383839999999</v>
-      </c>
-      <c r="Q101">
-        <v>0.8556161600000012</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.646710165847353</v>
-      </c>
-      <c r="T101">
-        <v>77.5779551631512</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1364520775249952</v>
-      </c>
-      <c r="W101">
-        <v>0.173400422832981</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5685503230208132</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
